--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -2058,7 +2058,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120476675</v>
+        <v>120480588</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574614</v>
+        <v>575008</v>
       </c>
       <c r="R13" t="n">
-        <v>7013128</v>
+        <v>7012970</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,19 +2158,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120476541</v>
+        <v>120479683</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2206,7 +2206,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574609</v>
+        <v>574981</v>
       </c>
       <c r="R14" t="n">
-        <v>7013099</v>
+        <v>7012954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2260,12 +2260,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2292,10 +2287,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120478128</v>
+        <v>120477524</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2304,25 +2299,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2332,13 +2327,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574815</v>
+        <v>574538</v>
       </c>
       <c r="R15" t="n">
-        <v>7012976</v>
+        <v>7013034</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2362,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2377,7 +2372,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,22 +2387,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120478226</v>
+        <v>120477919</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,21 +2415,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574839</v>
+        <v>574682</v>
       </c>
       <c r="R16" t="n">
-        <v>7013100</v>
+        <v>7012947</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2479,7 +2474,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2489,7 +2484,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2504,19 +2504,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120477938</v>
+        <v>120478039</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2550,19 +2550,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574747</v>
+        <v>574700</v>
       </c>
       <c r="R17" t="n">
-        <v>7013128</v>
+        <v>7013066</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2589,24 +2594,14 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2621,22 +2616,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120478245</v>
+        <v>120475719</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2649,37 +2644,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574661</v>
+        <v>574557</v>
       </c>
       <c r="R18" t="n">
-        <v>7013070</v>
+        <v>7013335</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2706,9 +2706,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,22 +2733,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120478804</v>
+        <v>120482873</v>
       </c>
       <c r="B19" t="n">
-        <v>74654</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2751,21 +2761,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2775,10 +2785,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574916</v>
+        <v>575178</v>
       </c>
       <c r="R19" t="n">
-        <v>7012988</v>
+        <v>7012952</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2810,7 +2820,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2820,7 +2830,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2835,22 +2845,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120483505</v>
+        <v>120477951</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2859,41 +2869,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574552</v>
+        <v>574667</v>
       </c>
       <c r="R20" t="n">
-        <v>7013338</v>
+        <v>7012956</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2920,9 +2944,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,22 +2971,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120476791</v>
+        <v>120478900</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2965,21 +2999,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2989,10 +3023,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574551</v>
+        <v>574883</v>
       </c>
       <c r="R21" t="n">
-        <v>7013059</v>
+        <v>7013078</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3024,7 +3058,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3034,12 +3068,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,22 +3083,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120476175</v>
+        <v>120477985</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3082,39 +3111,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574595</v>
+        <v>574701</v>
       </c>
       <c r="R22" t="n">
-        <v>7013170</v>
+        <v>7013141</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3173,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120476839</v>
+        <v>120478206</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3189,39 +3213,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574549</v>
+        <v>574815</v>
       </c>
       <c r="R23" t="n">
-        <v>7012993</v>
+        <v>7013085</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3253,7 +3272,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3263,7 +3282,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,10 +3309,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120479650</v>
+        <v>120476091</v>
       </c>
       <c r="B24" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3302,41 +3321,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575030</v>
+        <v>574596</v>
       </c>
       <c r="R24" t="n">
-        <v>7012916</v>
+        <v>7013168</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3363,19 +3382,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3390,22 +3399,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120479575</v>
+        <v>120483116</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3418,37 +3427,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575015</v>
+        <v>574701</v>
       </c>
       <c r="R25" t="n">
-        <v>7012924</v>
+        <v>7013268</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3475,19 +3484,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3502,22 +3501,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120479509</v>
+        <v>120482861</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3530,37 +3529,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574766</v>
+        <v>575181</v>
       </c>
       <c r="R26" t="n">
-        <v>7013045</v>
+        <v>7012951</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3587,9 +3591,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3604,22 +3618,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120478207</v>
+        <v>120482987</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>90781</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3628,46 +3642,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574661</v>
+        <v>575188</v>
       </c>
       <c r="R27" t="n">
-        <v>7013070</v>
+        <v>7012937</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3694,14 +3703,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,22 +3730,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120477524</v>
+        <v>120476541</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3744,37 +3758,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574538</v>
+        <v>574609</v>
       </c>
       <c r="R28" t="n">
-        <v>7013034</v>
+        <v>7013099</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3803,7 +3822,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3813,7 +3832,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3828,22 +3852,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120477975</v>
+        <v>120475714</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3852,38 +3876,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574700</v>
+        <v>574557</v>
       </c>
       <c r="R29" t="n">
-        <v>7012966</v>
+        <v>7013335</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3915,7 +3939,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3925,12 +3949,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3945,12 +3964,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4074,10 +4093,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120483136</v>
+        <v>120477573</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4090,21 +4109,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4114,10 +4133,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575076</v>
+        <v>574666</v>
       </c>
       <c r="R31" t="n">
-        <v>7012962</v>
+        <v>7013074</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4149,7 +4168,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4159,7 +4178,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4186,10 +4210,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120482920</v>
+        <v>120478091</v>
       </c>
       <c r="B32" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4202,34 +4226,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575178</v>
+        <v>574814</v>
       </c>
       <c r="R32" t="n">
-        <v>7012946</v>
+        <v>7012964</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4261,7 +4290,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4271,7 +4300,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4298,10 +4327,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120482757</v>
+        <v>120483538</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4314,42 +4343,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575161</v>
+        <v>574567</v>
       </c>
       <c r="R33" t="n">
-        <v>7012940</v>
+        <v>7013325</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4376,19 +4400,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,22 +4417,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120475679</v>
+        <v>120483166</v>
       </c>
       <c r="B34" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4427,25 +4441,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4455,10 +4469,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574558</v>
+        <v>574637</v>
       </c>
       <c r="R34" t="n">
-        <v>7013348</v>
+        <v>7013303</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4517,10 +4531,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120483636</v>
+        <v>120478200</v>
       </c>
       <c r="B35" t="n">
-        <v>90598</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4529,38 +4543,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574559</v>
+        <v>574704</v>
       </c>
       <c r="R35" t="n">
-        <v>7013332</v>
+        <v>7013044</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4619,10 +4633,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120476542</v>
+        <v>120479013</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4635,16 +4649,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4653,16 +4667,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574624</v>
+        <v>574894</v>
       </c>
       <c r="R36" t="n">
-        <v>7013126</v>
+        <v>7013031</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4694,7 +4713,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4704,12 +4723,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4724,22 +4738,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120478253</v>
+        <v>120479650</v>
       </c>
       <c r="B37" t="n">
-        <v>82321</v>
+        <v>90545</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4748,25 +4762,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4776,10 +4790,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574917</v>
+        <v>575030</v>
       </c>
       <c r="R37" t="n">
-        <v>7013009</v>
+        <v>7012916</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4811,7 +4825,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4821,7 +4835,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4848,10 +4862,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120481387</v>
+        <v>120475858</v>
       </c>
       <c r="B38" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4864,16 +4878,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4882,24 +4896,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574762</v>
+        <v>574570</v>
       </c>
       <c r="R38" t="n">
-        <v>7012995</v>
+        <v>7013265</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4926,9 +4935,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4943,22 +4967,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120477919</v>
+        <v>120475397</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4971,34 +4995,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574682</v>
+        <v>574558</v>
       </c>
       <c r="R39" t="n">
-        <v>7012947</v>
+        <v>7013337</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5030,7 +5054,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5040,12 +5064,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5060,22 +5079,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120477989</v>
+        <v>120475679</v>
       </c>
       <c r="B40" t="n">
-        <v>79527</v>
+        <v>79652</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5088,34 +5107,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574700</v>
+        <v>574558</v>
       </c>
       <c r="R40" t="n">
-        <v>7013142</v>
+        <v>7013348</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5174,10 +5193,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120482434</v>
+        <v>120482317</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>96891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5186,25 +5205,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5214,10 +5233,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574754</v>
+        <v>574773</v>
       </c>
       <c r="R41" t="n">
-        <v>7012970</v>
+        <v>7013002</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5276,10 +5295,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120482861</v>
+        <v>120482863</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90527</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5292,39 +5311,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575181</v>
+        <v>575173</v>
       </c>
       <c r="R42" t="n">
-        <v>7012951</v>
+        <v>7012956</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5356,7 +5370,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5366,7 +5380,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5381,22 +5395,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120482540</v>
+        <v>120480946</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5409,21 +5423,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5433,10 +5447,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575091</v>
+        <v>575006</v>
       </c>
       <c r="R43" t="n">
-        <v>7012974</v>
+        <v>7012970</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5468,7 +5482,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5478,7 +5492,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn och gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5493,22 +5512,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120483114</v>
+        <v>120478431</v>
       </c>
       <c r="B44" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5521,34 +5540,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574704</v>
+        <v>574745</v>
       </c>
       <c r="R44" t="n">
-        <v>7013264</v>
+        <v>7013030</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5607,10 +5626,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120475740</v>
+        <v>120478207</v>
       </c>
       <c r="B45" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5623,37 +5642,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574557</v>
+        <v>574661</v>
       </c>
       <c r="R45" t="n">
-        <v>7013323</v>
+        <v>7013070</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5680,19 +5704,14 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:21</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5707,22 +5726,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120477715</v>
+        <v>120477787</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5735,34 +5754,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574645</v>
+        <v>574673</v>
       </c>
       <c r="R46" t="n">
-        <v>7013075</v>
+        <v>7013097</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5794,7 +5818,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5804,7 +5828,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5819,22 +5843,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120475921</v>
+        <v>120478036</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5843,43 +5867,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574585</v>
+        <v>574778</v>
       </c>
       <c r="R47" t="n">
-        <v>7013246</v>
+        <v>7012962</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5911,7 +5930,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5921,7 +5940,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5936,22 +5955,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120478597</v>
+        <v>120476675</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5964,21 +5983,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5988,10 +6007,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574914</v>
+        <v>574614</v>
       </c>
       <c r="R48" t="n">
-        <v>7013012</v>
+        <v>7013128</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6023,7 +6042,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6033,12 +6052,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6053,22 +6067,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120478039</v>
+        <v>120476831</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6081,42 +6095,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574700</v>
+        <v>574561</v>
       </c>
       <c r="R49" t="n">
-        <v>7013066</v>
+        <v>7013070</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6143,14 +6152,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6165,22 +6179,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120478210</v>
+        <v>120482763</v>
       </c>
       <c r="B50" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6193,21 +6207,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6217,10 +6231,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574881</v>
+        <v>575128</v>
       </c>
       <c r="R50" t="n">
-        <v>7012991</v>
+        <v>7012966</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6252,7 +6266,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6262,7 +6276,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6277,22 +6291,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120482317</v>
+        <v>120476791</v>
       </c>
       <c r="B51" t="n">
-        <v>96891</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6301,25 +6315,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6329,13 +6343,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574773</v>
+        <v>574551</v>
       </c>
       <c r="R51" t="n">
-        <v>7013002</v>
+        <v>7013059</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6362,9 +6376,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6379,22 +6408,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120478274</v>
+        <v>120483636</v>
       </c>
       <c r="B52" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6403,41 +6432,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574884</v>
+        <v>574559</v>
       </c>
       <c r="R52" t="n">
-        <v>7013094</v>
+        <v>7013332</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6464,19 +6493,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6491,19 +6510,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120478069</v>
+        <v>120479509</v>
       </c>
       <c r="B53" t="n">
         <v>90580</v>
@@ -6543,13 +6562,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574798</v>
+        <v>574766</v>
       </c>
       <c r="R53" t="n">
-        <v>7012940</v>
+        <v>7013045</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6576,19 +6595,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6603,22 +6612,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120477619</v>
+        <v>120478597</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6631,21 +6640,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6664,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574657</v>
+        <v>574914</v>
       </c>
       <c r="R54" t="n">
-        <v>7013067</v>
+        <v>7013012</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6690,7 +6699,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6700,7 +6709,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6715,22 +6729,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120482763</v>
+        <v>120477678</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6743,34 +6757,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575128</v>
+        <v>574542</v>
       </c>
       <c r="R55" t="n">
-        <v>7012966</v>
+        <v>7013136</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6802,7 +6816,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6812,7 +6826,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6827,22 +6846,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120476831</v>
+        <v>120477886</v>
       </c>
       <c r="B56" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6855,34 +6874,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574561</v>
+        <v>574719</v>
       </c>
       <c r="R56" t="n">
-        <v>7013070</v>
+        <v>7013107</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6914,7 +6938,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6924,7 +6948,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6939,22 +6968,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120482864</v>
+        <v>120477400</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6963,41 +6992,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574700</v>
+        <v>574552</v>
       </c>
       <c r="R57" t="n">
-        <v>7013007</v>
+        <v>7013013</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7024,9 +7057,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7041,22 +7084,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120483118</v>
+        <v>120476955</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>5169</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7065,38 +7108,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575141</v>
+        <v>574526</v>
       </c>
       <c r="R58" t="n">
-        <v>7012926</v>
+        <v>7013059</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7128,7 +7176,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7138,7 +7186,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7165,10 +7213,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120483092</v>
+        <v>120481907</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7181,21 +7229,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7205,13 +7253,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575166</v>
+        <v>574773</v>
       </c>
       <c r="R59" t="n">
-        <v>7012887</v>
+        <v>7013002</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7238,24 +7286,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7270,19 +7303,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120482411</v>
+        <v>120483092</v>
       </c>
       <c r="B60" t="n">
         <v>57320</v>
@@ -7316,21 +7349,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575051</v>
+        <v>575166</v>
       </c>
       <c r="R60" t="n">
-        <v>7012995</v>
+        <v>7012887</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7362,7 +7390,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7372,7 +7400,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7387,19 +7420,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120478767</v>
+        <v>120479582</v>
       </c>
       <c r="B61" t="n">
         <v>90580</v>
@@ -7439,10 +7472,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574761</v>
+        <v>574748</v>
       </c>
       <c r="R61" t="n">
-        <v>7013035</v>
+        <v>7013002</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7501,10 +7534,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120478206</v>
+        <v>120479575</v>
       </c>
       <c r="B62" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7517,21 +7550,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7541,10 +7574,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574815</v>
+        <v>575015</v>
       </c>
       <c r="R62" t="n">
-        <v>7013085</v>
+        <v>7012924</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7576,7 +7609,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7586,7 +7619,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7601,22 +7634,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120476601</v>
+        <v>120482540</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7629,21 +7662,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7653,10 +7686,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574573</v>
+        <v>575091</v>
       </c>
       <c r="R63" t="n">
-        <v>7013042</v>
+        <v>7012974</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7688,7 +7721,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7698,12 +7731,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7718,22 +7746,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120475397</v>
+        <v>120477619</v>
       </c>
       <c r="B64" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7746,34 +7774,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574558</v>
+        <v>574657</v>
       </c>
       <c r="R64" t="n">
-        <v>7013337</v>
+        <v>7013067</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7805,7 +7833,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7815,7 +7843,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7830,22 +7858,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120480946</v>
+        <v>120476584</v>
       </c>
       <c r="B65" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7858,21 +7886,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7882,10 +7910,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>575006</v>
+        <v>574621</v>
       </c>
       <c r="R65" t="n">
-        <v>7012970</v>
+        <v>7013153</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7917,7 +7945,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7927,12 +7955,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Lunglav på rönn och gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7947,22 +7975,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120482523</v>
+        <v>120482411</v>
       </c>
       <c r="B66" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7975,37 +8003,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574779</v>
+        <v>575051</v>
       </c>
       <c r="R66" t="n">
-        <v>7012971</v>
+        <v>7012995</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8032,9 +8065,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8049,12 +8092,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8173,10 +8216,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120483119</v>
+        <v>120483427</v>
       </c>
       <c r="B68" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8189,16 +8232,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8207,16 +8250,21 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575114</v>
+        <v>574893</v>
       </c>
       <c r="R68" t="n">
-        <v>7012928</v>
+        <v>7013053</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8248,7 +8296,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8258,12 +8306,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8290,10 +8333,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120478035</v>
+        <v>120475802</v>
       </c>
       <c r="B69" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8302,47 +8345,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574785</v>
+        <v>574568</v>
       </c>
       <c r="R69" t="n">
-        <v>7013205</v>
+        <v>7013313</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8374,7 +8408,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8384,7 +8418,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8399,22 +8433,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120476914</v>
+        <v>120483505</v>
       </c>
       <c r="B70" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8427,37 +8461,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574547</v>
+        <v>574552</v>
       </c>
       <c r="R70" t="n">
-        <v>7013045</v>
+        <v>7013338</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8484,19 +8518,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8511,22 +8535,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120482873</v>
+        <v>120477938</v>
       </c>
       <c r="B71" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8539,21 +8563,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8563,10 +8587,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>575178</v>
+        <v>574747</v>
       </c>
       <c r="R71" t="n">
-        <v>7012952</v>
+        <v>7013128</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8598,7 +8622,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8608,7 +8632,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8635,10 +8664,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120482863</v>
+        <v>120478210</v>
       </c>
       <c r="B72" t="n">
-        <v>90527</v>
+        <v>79623</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8651,21 +8680,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8675,10 +8704,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>575173</v>
+        <v>574881</v>
       </c>
       <c r="R72" t="n">
-        <v>7012956</v>
+        <v>7012991</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8710,7 +8739,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8720,7 +8749,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8747,10 +8776,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120479582</v>
+        <v>120475921</v>
       </c>
       <c r="B73" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8763,37 +8792,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574748</v>
+        <v>574585</v>
       </c>
       <c r="R73" t="n">
-        <v>7013002</v>
+        <v>7013246</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8820,9 +8854,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8837,22 +8881,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120483116</v>
+        <v>120482434</v>
       </c>
       <c r="B74" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8865,34 +8909,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574701</v>
+        <v>574754</v>
       </c>
       <c r="R74" t="n">
-        <v>7013268</v>
+        <v>7012970</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8951,10 +8995,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120483155</v>
+        <v>120478767</v>
       </c>
       <c r="B75" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8967,34 +9011,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574641</v>
+        <v>574761</v>
       </c>
       <c r="R75" t="n">
-        <v>7013295</v>
+        <v>7013035</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -9053,10 +9097,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120477886</v>
+        <v>120478804</v>
       </c>
       <c r="B76" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9069,39 +9113,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574719</v>
+        <v>574916</v>
       </c>
       <c r="R76" t="n">
-        <v>7013107</v>
+        <v>7012988</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9133,7 +9172,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9143,12 +9182,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9163,22 +9197,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120478900</v>
+        <v>120478253</v>
       </c>
       <c r="B77" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9191,21 +9225,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9215,10 +9249,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574883</v>
+        <v>574917</v>
       </c>
       <c r="R77" t="n">
-        <v>7013078</v>
+        <v>7013009</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9250,7 +9284,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9260,7 +9294,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9275,19 +9309,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120483518</v>
+        <v>120478428</v>
       </c>
       <c r="B78" t="n">
         <v>78542</v>
@@ -9323,17 +9357,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>574570</v>
+        <v>574922</v>
       </c>
       <c r="R78" t="n">
-        <v>7013321</v>
+        <v>7012993</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9360,9 +9394,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9377,22 +9421,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120483538</v>
+        <v>120478069</v>
       </c>
       <c r="B79" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9405,37 +9449,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>574567</v>
+        <v>574798</v>
       </c>
       <c r="R79" t="n">
-        <v>7013325</v>
+        <v>7012940</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9462,9 +9506,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9479,22 +9533,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120482660</v>
+        <v>120477989</v>
       </c>
       <c r="B80" t="n">
-        <v>90864</v>
+        <v>79527</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9503,25 +9557,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9531,10 +9585,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>574772</v>
+        <v>574700</v>
       </c>
       <c r="R80" t="n">
-        <v>7012971</v>
+        <v>7013142</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9593,10 +9647,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120475677</v>
+        <v>120482523</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9609,37 +9663,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>574559</v>
+        <v>574779</v>
       </c>
       <c r="R81" t="n">
-        <v>7013337</v>
+        <v>7012971</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9666,19 +9720,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9693,19 +9737,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120482599</v>
+        <v>120478974</v>
       </c>
       <c r="B82" t="n">
         <v>90580</v>
@@ -9745,10 +9789,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>574771</v>
+        <v>574753</v>
       </c>
       <c r="R82" t="n">
-        <v>7012977</v>
+        <v>7013026</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9807,10 +9851,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120479013</v>
+        <v>120476542</v>
       </c>
       <c r="B83" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9823,16 +9867,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9841,21 +9885,16 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>574894</v>
+        <v>574624</v>
       </c>
       <c r="R83" t="n">
-        <v>7013031</v>
+        <v>7013126</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9887,7 +9926,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9897,7 +9936,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9912,22 +9956,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120475719</v>
+        <v>120482660</v>
       </c>
       <c r="B84" t="n">
-        <v>57336</v>
+        <v>90864</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9940,42 +9984,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>574557</v>
+        <v>574772</v>
       </c>
       <c r="R84" t="n">
-        <v>7013335</v>
+        <v>7012971</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10002,19 +10041,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10029,22 +10058,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120478036</v>
+        <v>120483155</v>
       </c>
       <c r="B85" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10053,41 +10082,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>574778</v>
+        <v>574641</v>
       </c>
       <c r="R85" t="n">
-        <v>7012962</v>
+        <v>7013295</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10114,19 +10143,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:58</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10141,22 +10160,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120478428</v>
+        <v>120483136</v>
       </c>
       <c r="B86" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10169,21 +10188,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10193,10 +10212,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>574922</v>
+        <v>575076</v>
       </c>
       <c r="R86" t="n">
-        <v>7012993</v>
+        <v>7012962</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10228,7 +10247,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10238,7 +10257,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10253,22 +10272,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120477828</v>
+        <v>120476784</v>
       </c>
       <c r="B87" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10281,21 +10300,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10305,10 +10324,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>574688</v>
+        <v>574525</v>
       </c>
       <c r="R87" t="n">
-        <v>7012983</v>
+        <v>7013029</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10340,7 +10359,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10350,7 +10369,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10365,22 +10384,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120477787</v>
+        <v>120477401</v>
       </c>
       <c r="B88" t="n">
-        <v>57336</v>
+        <v>90781</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10389,43 +10408,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>1106</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>574673</v>
+        <v>574646</v>
       </c>
       <c r="R88" t="n">
-        <v>7013097</v>
+        <v>7013031</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10457,7 +10471,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10467,7 +10481,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10494,10 +10508,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120483166</v>
+        <v>120478878</v>
       </c>
       <c r="B89" t="n">
-        <v>79624</v>
+        <v>90864</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10510,34 +10524,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>574637</v>
+        <v>574759</v>
       </c>
       <c r="R89" t="n">
-        <v>7013303</v>
+        <v>7013028</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -10596,10 +10610,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120482642</v>
+        <v>120481387</v>
       </c>
       <c r="B90" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10612,37 +10626,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>575068</v>
+        <v>574762</v>
       </c>
       <c r="R90" t="n">
-        <v>7013015</v>
+        <v>7012995</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10669,19 +10688,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10696,19 +10705,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120479001</v>
+        <v>120477715</v>
       </c>
       <c r="B91" t="n">
         <v>78542</v>
@@ -10748,10 +10757,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>574918</v>
+        <v>574645</v>
       </c>
       <c r="R91" t="n">
-        <v>7012974</v>
+        <v>7013075</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10783,7 +10792,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10793,7 +10802,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10820,10 +10829,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120477573</v>
+        <v>120478002</v>
       </c>
       <c r="B92" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10836,21 +10845,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10860,10 +10869,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>574666</v>
+        <v>574766</v>
       </c>
       <c r="R92" t="n">
-        <v>7013074</v>
+        <v>7012936</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10895,7 +10904,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10905,12 +10914,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10925,19 +10929,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120476091</v>
+        <v>120478245</v>
       </c>
       <c r="B93" t="n">
         <v>79623</v>
@@ -10973,14 +10977,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>574596</v>
+        <v>574661</v>
       </c>
       <c r="R93" t="n">
-        <v>7013168</v>
+        <v>7013070</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -11039,10 +11043,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120483141</v>
+        <v>120478035</v>
       </c>
       <c r="B94" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11051,41 +11055,50 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>574645</v>
+        <v>574785</v>
       </c>
       <c r="R94" t="n">
-        <v>7013293</v>
+        <v>7013205</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11112,9 +11125,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11129,22 +11152,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120477678</v>
+        <v>120482599</v>
       </c>
       <c r="B95" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11157,37 +11180,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>574542</v>
+        <v>574771</v>
       </c>
       <c r="R95" t="n">
-        <v>7013136</v>
+        <v>7012977</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11214,24 +11237,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11246,22 +11254,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120478232</v>
+        <v>120482864</v>
       </c>
       <c r="B96" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11270,25 +11278,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11298,13 +11306,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>574911</v>
+        <v>574700</v>
       </c>
       <c r="R96" t="n">
-        <v>7013004</v>
+        <v>7013007</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11331,19 +11339,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11358,22 +11356,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120478200</v>
+        <v>120477975</v>
       </c>
       <c r="B97" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11382,25 +11380,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11410,13 +11408,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>574704</v>
+        <v>574700</v>
       </c>
       <c r="R97" t="n">
-        <v>7013044</v>
+        <v>7012966</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11443,9 +11441,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11460,22 +11473,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120478431</v>
+        <v>120478232</v>
       </c>
       <c r="B98" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11484,25 +11497,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11512,13 +11525,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>574745</v>
+        <v>574911</v>
       </c>
       <c r="R98" t="n">
-        <v>7013030</v>
+        <v>7013004</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11545,9 +11558,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11562,22 +11585,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120483427</v>
+        <v>120478274</v>
       </c>
       <c r="B99" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11586,43 +11609,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>574893</v>
+        <v>574884</v>
       </c>
       <c r="R99" t="n">
-        <v>7013053</v>
+        <v>7013094</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11654,7 +11672,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11664,7 +11682,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11691,10 +11709,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120482987</v>
+        <v>120476601</v>
       </c>
       <c r="B100" t="n">
-        <v>90781</v>
+        <v>57320</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11703,25 +11721,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11731,10 +11749,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>575188</v>
+        <v>574573</v>
       </c>
       <c r="R100" t="n">
-        <v>7012937</v>
+        <v>7013042</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11766,7 +11784,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11776,7 +11794,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11791,22 +11814,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120477401</v>
+        <v>120476175</v>
       </c>
       <c r="B101" t="n">
-        <v>90781</v>
+        <v>57336</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11815,41 +11838,46 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1106</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>574646</v>
+        <v>574595</v>
       </c>
       <c r="R101" t="n">
-        <v>7013031</v>
+        <v>7013170</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11876,19 +11904,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11903,22 +11921,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120475741</v>
+        <v>120483114</v>
       </c>
       <c r="B102" t="n">
-        <v>5169</v>
+        <v>79623</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11927,46 +11945,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>574556</v>
+        <v>574704</v>
       </c>
       <c r="R102" t="n">
-        <v>7013327</v>
+        <v>7013264</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11993,19 +12006,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12020,22 +12023,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120476454</v>
+        <v>120482757</v>
       </c>
       <c r="B103" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12048,37 +12051,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>574577</v>
+        <v>575161</v>
       </c>
       <c r="R103" t="n">
-        <v>7013274</v>
+        <v>7012940</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12105,9 +12113,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12122,22 +12140,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120477985</v>
+        <v>120482920</v>
       </c>
       <c r="B104" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12150,21 +12168,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12174,13 +12192,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>574701</v>
+        <v>575178</v>
       </c>
       <c r="R104" t="n">
-        <v>7013141</v>
+        <v>7012946</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12207,9 +12225,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12224,22 +12252,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120477743</v>
+        <v>120483118</v>
       </c>
       <c r="B105" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12252,21 +12280,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12276,10 +12304,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>574597</v>
+        <v>575141</v>
       </c>
       <c r="R105" t="n">
-        <v>7013088</v>
+        <v>7012926</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12311,7 +12339,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12321,12 +12349,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12341,22 +12364,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120480588</v>
+        <v>120483141</v>
       </c>
       <c r="B106" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12365,41 +12388,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>575008</v>
+        <v>574645</v>
       </c>
       <c r="R106" t="n">
-        <v>7012970</v>
+        <v>7013293</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12426,19 +12449,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12453,22 +12466,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120477974</v>
+        <v>120479001</v>
       </c>
       <c r="B107" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12481,39 +12494,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>574762</v>
+        <v>574918</v>
       </c>
       <c r="R107" t="n">
-        <v>7013134</v>
+        <v>7012974</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12545,7 +12553,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12555,7 +12563,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12570,19 +12578,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120478091</v>
+        <v>120477974</v>
       </c>
       <c r="B108" t="n">
         <v>57320</v>
@@ -12627,10 +12635,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>574814</v>
+        <v>574762</v>
       </c>
       <c r="R108" t="n">
-        <v>7012964</v>
+        <v>7013134</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12662,7 +12670,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12672,7 +12680,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12687,22 +12695,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120475858</v>
+        <v>120478407</v>
       </c>
       <c r="B109" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12711,41 +12719,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>574570</v>
+        <v>574733</v>
       </c>
       <c r="R109" t="n">
-        <v>7013265</v>
+        <v>7013036</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12772,24 +12780,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12804,22 +12797,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120479683</v>
+        <v>120476454</v>
       </c>
       <c r="B110" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12832,42 +12825,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>574981</v>
+        <v>574577</v>
       </c>
       <c r="R110" t="n">
-        <v>7012954</v>
+        <v>7013274</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12894,19 +12882,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12921,22 +12899,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120477400</v>
+        <v>120476914</v>
       </c>
       <c r="B111" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12945,42 +12923,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>574552</v>
+        <v>574547</v>
       </c>
       <c r="R111" t="n">
-        <v>7013013</v>
+        <v>7013045</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13012,7 +12986,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13022,7 +12996,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13049,10 +13023,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120477951</v>
+        <v>120475677</v>
       </c>
       <c r="B112" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13061,52 +13035,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>574667</v>
+        <v>574559</v>
       </c>
       <c r="R112" t="n">
-        <v>7012956</v>
+        <v>7013337</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13138,7 +13098,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13148,7 +13108,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13175,10 +13135,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120478878</v>
+        <v>120483518</v>
       </c>
       <c r="B113" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13191,34 +13151,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>574759</v>
+        <v>574570</v>
       </c>
       <c r="R113" t="n">
-        <v>7013028</v>
+        <v>7013321</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -13277,10 +13237,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120478407</v>
+        <v>120478226</v>
       </c>
       <c r="B114" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13289,25 +13249,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13317,13 +13277,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>574733</v>
+        <v>574839</v>
       </c>
       <c r="R114" t="n">
-        <v>7013036</v>
+        <v>7013100</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13350,9 +13310,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13367,22 +13337,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120478002</v>
+        <v>120477743</v>
       </c>
       <c r="B115" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13395,21 +13365,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13419,10 +13389,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>574766</v>
+        <v>574597</v>
       </c>
       <c r="R115" t="n">
-        <v>7012936</v>
+        <v>7013088</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13454,7 +13424,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13464,7 +13434,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13479,22 +13454,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120475714</v>
+        <v>120477828</v>
       </c>
       <c r="B116" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13503,38 +13478,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>574557</v>
+        <v>574688</v>
       </c>
       <c r="R116" t="n">
-        <v>7013335</v>
+        <v>7012983</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13566,7 +13541,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13576,7 +13551,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13591,22 +13566,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120475802</v>
+        <v>120482642</v>
       </c>
       <c r="B117" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13619,34 +13594,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>574568</v>
+        <v>575068</v>
       </c>
       <c r="R117" t="n">
-        <v>7013313</v>
+        <v>7013015</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13678,7 +13653,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13688,7 +13663,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13703,22 +13678,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120476784</v>
+        <v>120476839</v>
       </c>
       <c r="B118" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13731,34 +13706,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>574525</v>
+        <v>574549</v>
       </c>
       <c r="R118" t="n">
-        <v>7013029</v>
+        <v>7012993</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13790,7 +13770,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13800,7 +13780,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13827,10 +13807,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120476584</v>
+        <v>120475740</v>
       </c>
       <c r="B119" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13843,34 +13823,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>574621</v>
+        <v>574557</v>
       </c>
       <c r="R119" t="n">
-        <v>7013153</v>
+        <v>7013323</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13902,7 +13882,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13912,12 +13892,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13932,19 +13907,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120476955</v>
+        <v>120475741</v>
       </c>
       <c r="B120" t="n">
         <v>5169</v>
@@ -13980,19 +13955,19 @@
       <c r="I120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>574526</v>
+        <v>574556</v>
       </c>
       <c r="R120" t="n">
-        <v>7013059</v>
+        <v>7013327</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14024,7 +13999,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14034,7 +14009,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14061,10 +14036,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120478974</v>
+        <v>120483119</v>
       </c>
       <c r="B121" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14077,21 +14052,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14101,13 +14076,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>574753</v>
+        <v>575114</v>
       </c>
       <c r="R121" t="n">
-        <v>7013026</v>
+        <v>7012928</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14134,9 +14109,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14151,22 +14141,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120478239</v>
+        <v>120483096</v>
       </c>
       <c r="B122" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14179,37 +14169,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>574847</v>
+        <v>574707</v>
       </c>
       <c r="R122" t="n">
-        <v>7013095</v>
+        <v>7013260</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14236,19 +14226,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14263,22 +14243,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120483096</v>
+        <v>120478239</v>
       </c>
       <c r="B123" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14291,37 +14271,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>574707</v>
+        <v>574847</v>
       </c>
       <c r="R123" t="n">
-        <v>7013260</v>
+        <v>7013095</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14348,9 +14328,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14365,22 +14355,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120481907</v>
+        <v>120478128</v>
       </c>
       <c r="B124" t="n">
-        <v>82321</v>
+        <v>90545</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14389,25 +14379,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14417,13 +14407,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574773</v>
+        <v>574815</v>
       </c>
       <c r="R124" t="n">
-        <v>7013002</v>
+        <v>7012976</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14450,9 +14440,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14467,12 +14467,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -2399,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120477919</v>
+        <v>120475719</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2415,16 +2415,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2433,16 +2433,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574682</v>
+        <v>574557</v>
       </c>
       <c r="R16" t="n">
-        <v>7012947</v>
+        <v>7013335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2474,7 +2479,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2484,12 +2489,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2504,22 +2504,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120478039</v>
+        <v>120482873</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2532,42 +2532,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574700</v>
+        <v>575178</v>
       </c>
       <c r="R17" t="n">
-        <v>7013066</v>
+        <v>7012952</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2594,14 +2589,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2616,22 +2616,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120475719</v>
+        <v>120477951</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>57431</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2640,20 +2640,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2661,22 +2661,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574557</v>
+        <v>574667</v>
       </c>
       <c r="R18" t="n">
-        <v>7013335</v>
+        <v>7012956</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2708,7 +2717,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2718,7 +2727,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,22 +2742,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120482873</v>
+        <v>120477919</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2761,21 +2770,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2785,10 +2794,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575178</v>
+        <v>574682</v>
       </c>
       <c r="R19" t="n">
-        <v>7012952</v>
+        <v>7012947</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,7 +2829,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2830,7 +2839,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2845,22 +2859,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120477951</v>
+        <v>120478039</v>
       </c>
       <c r="B20" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2869,20 +2883,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2890,19 +2904,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2911,13 +2916,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574667</v>
+        <v>574700</v>
       </c>
       <c r="R20" t="n">
-        <v>7012956</v>
+        <v>7013066</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2944,19 +2949,14 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2971,12 +2971,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3095,10 +3095,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120477985</v>
+        <v>120483116</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3111,34 +3111,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
         <v>574701</v>
       </c>
       <c r="R22" t="n">
-        <v>7013141</v>
+        <v>7013268</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120478206</v>
+        <v>120482861</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3213,34 +3213,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574815</v>
+        <v>575181</v>
       </c>
       <c r="R23" t="n">
-        <v>7013085</v>
+        <v>7012951</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3272,7 +3277,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3282,7 +3287,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3309,10 +3314,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120476091</v>
+        <v>120482987</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>90781</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3321,41 +3326,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1106</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574596</v>
+        <v>575188</v>
       </c>
       <c r="R24" t="n">
-        <v>7013168</v>
+        <v>7012937</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3382,9 +3387,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,22 +3414,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120483116</v>
+        <v>120477985</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,34 +3442,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
         <v>574701</v>
       </c>
       <c r="R25" t="n">
-        <v>7013268</v>
+        <v>7013141</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3513,10 +3528,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120482861</v>
+        <v>120478206</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,39 +3544,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575181</v>
+        <v>574815</v>
       </c>
       <c r="R26" t="n">
-        <v>7012951</v>
+        <v>7013085</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3593,7 +3603,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3603,7 +3613,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3630,10 +3640,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120482987</v>
+        <v>120476091</v>
       </c>
       <c r="B27" t="n">
-        <v>90781</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3642,41 +3652,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575188</v>
+        <v>574596</v>
       </c>
       <c r="R27" t="n">
-        <v>7012937</v>
+        <v>7013168</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3703,19 +3713,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3730,12 +3730,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120478200</v>
+        <v>120479013</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4543,41 +4543,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574704</v>
+        <v>574894</v>
       </c>
       <c r="R35" t="n">
-        <v>7013044</v>
+        <v>7013031</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4604,9 +4609,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4621,22 +4636,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120479013</v>
+        <v>120479650</v>
       </c>
       <c r="B36" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4645,43 +4660,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574894</v>
+        <v>575030</v>
       </c>
       <c r="R36" t="n">
-        <v>7013031</v>
+        <v>7012916</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4713,7 +4723,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4723,7 +4733,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4738,19 +4748,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120479650</v>
+        <v>120478200</v>
       </c>
       <c r="B37" t="n">
         <v>90545</v>
@@ -4790,13 +4800,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575030</v>
+        <v>574704</v>
       </c>
       <c r="R37" t="n">
-        <v>7012916</v>
+        <v>7013044</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4823,19 +4833,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4850,22 +4850,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120475858</v>
+        <v>120482863</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>90527</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4878,34 +4878,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574570</v>
+        <v>575173</v>
       </c>
       <c r="R38" t="n">
-        <v>7013265</v>
+        <v>7012956</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4947,12 +4947,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4967,12 +4962,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5295,10 +5290,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120482863</v>
+        <v>120475858</v>
       </c>
       <c r="B42" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5311,34 +5306,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575173</v>
+        <v>574570</v>
       </c>
       <c r="R42" t="n">
-        <v>7012956</v>
+        <v>7013265</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5370,7 +5365,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5380,7 +5375,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5395,12 +5395,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5855,10 +5855,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120478036</v>
+        <v>120476675</v>
       </c>
       <c r="B47" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5867,25 +5867,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574778</v>
+        <v>574614</v>
       </c>
       <c r="R47" t="n">
-        <v>7012962</v>
+        <v>7013128</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5967,7 +5967,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120476675</v>
+        <v>120476831</v>
       </c>
       <c r="B48" t="n">
         <v>79623</v>
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574614</v>
+        <v>574561</v>
       </c>
       <c r="R48" t="n">
-        <v>7013128</v>
+        <v>7013070</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6079,10 +6079,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120476831</v>
+        <v>120482763</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6095,21 +6095,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6119,10 +6119,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574561</v>
+        <v>575128</v>
       </c>
       <c r="R49" t="n">
-        <v>7013070</v>
+        <v>7012966</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6179,22 +6179,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120482763</v>
+        <v>120478036</v>
       </c>
       <c r="B50" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6203,25 +6203,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575128</v>
+        <v>574778</v>
       </c>
       <c r="R50" t="n">
-        <v>7012966</v>
+        <v>7012962</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6291,22 +6291,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120476791</v>
+        <v>120479509</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6319,21 +6319,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6343,13 +6343,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574551</v>
+        <v>574766</v>
       </c>
       <c r="R51" t="n">
-        <v>7013059</v>
+        <v>7013045</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6376,24 +6376,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6408,22 +6393,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120483636</v>
+        <v>120478597</v>
       </c>
       <c r="B52" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6436,37 +6421,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574559</v>
+        <v>574914</v>
       </c>
       <c r="R52" t="n">
-        <v>7013332</v>
+        <v>7013012</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6493,9 +6478,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6510,22 +6510,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120479509</v>
+        <v>120477678</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6538,37 +6538,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574766</v>
+        <v>574542</v>
       </c>
       <c r="R53" t="n">
-        <v>7013045</v>
+        <v>7013136</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6595,9 +6595,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6612,22 +6627,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120478597</v>
+        <v>120483636</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6640,37 +6655,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574914</v>
+        <v>574559</v>
       </c>
       <c r="R54" t="n">
-        <v>7013012</v>
+        <v>7013332</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6697,24 +6712,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6729,19 +6729,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120477678</v>
+        <v>120476791</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6777,14 +6777,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574542</v>
+        <v>574551</v>
       </c>
       <c r="R55" t="n">
-        <v>7013136</v>
+        <v>7013059</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6858,10 +6858,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120477886</v>
+        <v>120477400</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6870,31 +6870,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6903,10 +6902,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574719</v>
+        <v>574552</v>
       </c>
       <c r="R56" t="n">
-        <v>7013107</v>
+        <v>7013013</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6938,7 +6937,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6948,12 +6947,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6968,22 +6962,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120477400</v>
+        <v>120476955</v>
       </c>
       <c r="B57" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6992,30 +6986,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7024,10 +7019,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574552</v>
+        <v>574526</v>
       </c>
       <c r="R57" t="n">
-        <v>7013013</v>
+        <v>7013059</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7059,7 +7054,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7069,7 +7064,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7096,10 +7091,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120476955</v>
+        <v>120481907</v>
       </c>
       <c r="B58" t="n">
-        <v>5169</v>
+        <v>82321</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7108,46 +7103,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574526</v>
+        <v>574773</v>
       </c>
       <c r="R58" t="n">
-        <v>7013059</v>
+        <v>7013002</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7174,19 +7164,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7201,22 +7181,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120481907</v>
+        <v>120483092</v>
       </c>
       <c r="B59" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7229,21 +7209,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7253,13 +7233,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574773</v>
+        <v>575166</v>
       </c>
       <c r="R59" t="n">
-        <v>7013002</v>
+        <v>7012887</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7286,9 +7266,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7303,22 +7298,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120483092</v>
+        <v>120479582</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7331,21 +7326,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7355,13 +7350,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575166</v>
+        <v>574748</v>
       </c>
       <c r="R60" t="n">
-        <v>7012887</v>
+        <v>7013002</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7388,24 +7383,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7420,22 +7400,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120479582</v>
+        <v>120479575</v>
       </c>
       <c r="B61" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7448,21 +7428,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7472,13 +7452,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574748</v>
+        <v>575015</v>
       </c>
       <c r="R61" t="n">
-        <v>7013002</v>
+        <v>7012924</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7505,9 +7485,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7522,22 +7512,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120479575</v>
+        <v>120477886</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7550,34 +7540,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575015</v>
+        <v>574719</v>
       </c>
       <c r="R62" t="n">
-        <v>7012924</v>
+        <v>7013107</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7609,7 +7604,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7619,7 +7614,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7634,12 +7634,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8104,10 +8104,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120483094</v>
+        <v>120477938</v>
       </c>
       <c r="B67" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8116,25 +8116,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575168</v>
+        <v>574747</v>
       </c>
       <c r="R67" t="n">
-        <v>7012937</v>
+        <v>7013128</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8189,7 +8189,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8204,22 +8209,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120483427</v>
+        <v>120478210</v>
       </c>
       <c r="B68" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8232,39 +8237,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574893</v>
+        <v>574881</v>
       </c>
       <c r="R68" t="n">
-        <v>7013053</v>
+        <v>7012991</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8321,12 +8321,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120483505</v>
+        <v>120483094</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8457,41 +8457,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574552</v>
+        <v>575168</v>
       </c>
       <c r="R70" t="n">
-        <v>7013338</v>
+        <v>7012937</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8518,9 +8518,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8535,22 +8545,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120477938</v>
+        <v>120483427</v>
       </c>
       <c r="B71" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8563,16 +8573,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8581,16 +8591,21 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574747</v>
+        <v>574893</v>
       </c>
       <c r="R71" t="n">
-        <v>7013128</v>
+        <v>7013053</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8622,7 +8637,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8632,12 +8647,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8664,10 +8674,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120478210</v>
+        <v>120483505</v>
       </c>
       <c r="B72" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8680,37 +8690,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574881</v>
+        <v>574552</v>
       </c>
       <c r="R72" t="n">
-        <v>7012991</v>
+        <v>7013338</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8737,19 +8747,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8764,12 +8764,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120476784</v>
+        <v>120481387</v>
       </c>
       <c r="B87" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10300,37 +10300,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>574525</v>
+        <v>574762</v>
       </c>
       <c r="R87" t="n">
-        <v>7013029</v>
+        <v>7012995</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10357,19 +10362,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10384,22 +10379,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120477401</v>
+        <v>120478878</v>
       </c>
       <c r="B88" t="n">
-        <v>90781</v>
+        <v>90864</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10408,25 +10403,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1106</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10436,13 +10431,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>574646</v>
+        <v>574759</v>
       </c>
       <c r="R88" t="n">
-        <v>7013031</v>
+        <v>7013028</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10469,19 +10464,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10496,22 +10481,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120478878</v>
+        <v>120477715</v>
       </c>
       <c r="B89" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10524,21 +10509,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10548,13 +10533,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>574759</v>
+        <v>574645</v>
       </c>
       <c r="R89" t="n">
-        <v>7013028</v>
+        <v>7013075</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10581,9 +10566,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10598,22 +10593,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120481387</v>
+        <v>120478002</v>
       </c>
       <c r="B90" t="n">
-        <v>57336</v>
+        <v>90864</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10626,42 +10621,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>574762</v>
+        <v>574766</v>
       </c>
       <c r="R90" t="n">
-        <v>7012995</v>
+        <v>7012936</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10688,9 +10678,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10705,22 +10705,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120477715</v>
+        <v>120478245</v>
       </c>
       <c r="B91" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10733,21 +10733,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10757,13 +10757,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>574645</v>
+        <v>574661</v>
       </c>
       <c r="R91" t="n">
-        <v>7013075</v>
+        <v>7013070</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10790,19 +10790,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:37</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10817,22 +10807,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120478002</v>
+        <v>120478035</v>
       </c>
       <c r="B92" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10841,38 +10831,47 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>574766</v>
+        <v>574785</v>
       </c>
       <c r="R92" t="n">
-        <v>7012936</v>
+        <v>7013205</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10904,7 +10903,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10914,7 +10913,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10929,22 +10928,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120478245</v>
+        <v>120482599</v>
       </c>
       <c r="B93" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10957,21 +10956,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10981,10 +10980,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>574661</v>
+        <v>574771</v>
       </c>
       <c r="R93" t="n">
-        <v>7013070</v>
+        <v>7012977</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -11043,10 +11042,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120478035</v>
+        <v>120476784</v>
       </c>
       <c r="B94" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11055,47 +11054,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>574785</v>
+        <v>574525</v>
       </c>
       <c r="R94" t="n">
-        <v>7013205</v>
+        <v>7013029</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11127,7 +11117,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11137,7 +11127,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11164,10 +11154,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120482599</v>
+        <v>120477401</v>
       </c>
       <c r="B95" t="n">
-        <v>90580</v>
+        <v>90781</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11176,25 +11166,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11204,13 +11194,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>574771</v>
+        <v>574646</v>
       </c>
       <c r="R95" t="n">
-        <v>7012977</v>
+        <v>7013031</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11237,9 +11227,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11254,19 +11254,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120482864</v>
+        <v>120477975</v>
       </c>
       <c r="B96" t="n">
         <v>57320</v>
@@ -11309,10 +11309,10 @@
         <v>574700</v>
       </c>
       <c r="R96" t="n">
-        <v>7013007</v>
+        <v>7012966</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11339,9 +11339,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11356,22 +11371,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120477975</v>
+        <v>120478232</v>
       </c>
       <c r="B97" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11380,25 +11395,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11408,10 +11423,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>574700</v>
+        <v>574911</v>
       </c>
       <c r="R97" t="n">
-        <v>7012966</v>
+        <v>7013004</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11443,7 +11458,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11453,12 +11468,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11485,7 +11495,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120478232</v>
+        <v>120478274</v>
       </c>
       <c r="B98" t="n">
         <v>90545</v>
@@ -11525,10 +11535,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>574911</v>
+        <v>574884</v>
       </c>
       <c r="R98" t="n">
-        <v>7013004</v>
+        <v>7013094</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11560,7 +11570,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11570,7 +11580,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11585,22 +11595,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120478274</v>
+        <v>120476601</v>
       </c>
       <c r="B99" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11609,25 +11619,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11637,10 +11647,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>574884</v>
+        <v>574573</v>
       </c>
       <c r="R99" t="n">
-        <v>7013094</v>
+        <v>7013042</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11672,7 +11682,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11682,7 +11692,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11709,10 +11724,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120476601</v>
+        <v>120476175</v>
       </c>
       <c r="B100" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11725,16 +11740,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11743,19 +11758,24 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>574573</v>
+        <v>574595</v>
       </c>
       <c r="R100" t="n">
-        <v>7013042</v>
+        <v>7013170</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11782,24 +11802,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11814,22 +11819,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120476175</v>
+        <v>120482864</v>
       </c>
       <c r="B101" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11842,16 +11847,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11860,21 +11865,16 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>574595</v>
+        <v>574700</v>
       </c>
       <c r="R101" t="n">
-        <v>7013170</v>
+        <v>7013007</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -12809,10 +12809,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120476454</v>
+        <v>120478226</v>
       </c>
       <c r="B110" t="n">
-        <v>86895</v>
+        <v>79623</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12825,37 +12825,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>574577</v>
+        <v>574839</v>
       </c>
       <c r="R110" t="n">
-        <v>7013274</v>
+        <v>7013100</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12882,9 +12882,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12899,22 +12909,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120476914</v>
+        <v>120477743</v>
       </c>
       <c r="B111" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12927,21 +12937,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12951,10 +12961,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>574547</v>
+        <v>574597</v>
       </c>
       <c r="R111" t="n">
-        <v>7013045</v>
+        <v>7013088</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12986,7 +12996,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12996,7 +13006,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13011,19 +13026,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120475677</v>
+        <v>120477828</v>
       </c>
       <c r="B112" t="n">
         <v>78542</v>
@@ -13059,14 +13074,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>574559</v>
+        <v>574688</v>
       </c>
       <c r="R112" t="n">
-        <v>7013337</v>
+        <v>7012983</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13098,7 +13113,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13108,7 +13123,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13135,10 +13150,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120483518</v>
+        <v>120482642</v>
       </c>
       <c r="B113" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13151,37 +13166,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>574570</v>
+        <v>575068</v>
       </c>
       <c r="R113" t="n">
-        <v>7013321</v>
+        <v>7013015</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13208,9 +13223,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13225,22 +13250,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120478226</v>
+        <v>120476454</v>
       </c>
       <c r="B114" t="n">
-        <v>79623</v>
+        <v>86895</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13253,37 +13278,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>574839</v>
+        <v>574577</v>
       </c>
       <c r="R114" t="n">
-        <v>7013100</v>
+        <v>7013274</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13310,19 +13335,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13337,22 +13352,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120477743</v>
+        <v>120476914</v>
       </c>
       <c r="B115" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13365,21 +13380,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13389,10 +13404,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>574597</v>
+        <v>574547</v>
       </c>
       <c r="R115" t="n">
-        <v>7013088</v>
+        <v>7013045</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13424,7 +13439,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13434,12 +13449,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13454,19 +13464,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120477828</v>
+        <v>120475677</v>
       </c>
       <c r="B116" t="n">
         <v>78542</v>
@@ -13502,14 +13512,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>574688</v>
+        <v>574559</v>
       </c>
       <c r="R116" t="n">
-        <v>7012983</v>
+        <v>7013337</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13541,7 +13551,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13551,7 +13561,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13578,10 +13588,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120482642</v>
+        <v>120483518</v>
       </c>
       <c r="B117" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13594,37 +13604,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>575068</v>
+        <v>574570</v>
       </c>
       <c r="R117" t="n">
-        <v>7013015</v>
+        <v>7013321</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13651,19 +13661,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13678,12 +13678,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120480588</v>
+        <v>120475921</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2074,34 +2074,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575008</v>
+        <v>574585</v>
       </c>
       <c r="R13" t="n">
-        <v>7012970</v>
+        <v>7013246</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2133,7 +2138,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2143,7 +2148,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2170,7 +2175,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120479683</v>
+        <v>120482864</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2204,24 +2209,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574981</v>
+        <v>574700</v>
       </c>
       <c r="R14" t="n">
-        <v>7012954</v>
+        <v>7013007</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,19 +2248,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2275,22 +2265,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120477524</v>
+        <v>120476541</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2303,37 +2293,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574538</v>
+        <v>574609</v>
       </c>
       <c r="R15" t="n">
-        <v>7013034</v>
+        <v>7013099</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2362,7 +2357,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2372,7 +2367,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,22 +2387,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120475719</v>
+        <v>120479509</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2415,42 +2415,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574557</v>
+        <v>574766</v>
       </c>
       <c r="R16" t="n">
-        <v>7013335</v>
+        <v>7013045</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2477,19 +2472,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2504,22 +2489,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120482873</v>
+        <v>120478274</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2528,25 +2513,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2556,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575178</v>
+        <v>574884</v>
       </c>
       <c r="R17" t="n">
-        <v>7012952</v>
+        <v>7013094</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2591,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2601,7 +2586,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,10 +2613,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120477951</v>
+        <v>120478900</v>
       </c>
       <c r="B18" t="n">
-        <v>57431</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2640,52 +2625,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574667</v>
+        <v>574883</v>
       </c>
       <c r="R18" t="n">
-        <v>7012956</v>
+        <v>7013078</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2717,7 +2688,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2727,7 +2698,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2742,22 +2713,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120477919</v>
+        <v>120478804</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2770,21 +2741,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2794,10 +2765,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574682</v>
+        <v>574916</v>
       </c>
       <c r="R19" t="n">
-        <v>7012947</v>
+        <v>7012988</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2829,7 +2800,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2839,12 +2810,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2871,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120478039</v>
+        <v>120476914</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2887,42 +2853,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574700</v>
+        <v>574547</v>
       </c>
       <c r="R20" t="n">
-        <v>7013066</v>
+        <v>7013045</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2949,14 +2910,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2971,22 +2937,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120478900</v>
+        <v>120476955</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>5169</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2995,38 +2961,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574883</v>
+        <v>574526</v>
       </c>
       <c r="R21" t="n">
-        <v>7013078</v>
+        <v>7013059</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3058,7 +3029,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3068,7 +3039,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3083,22 +3054,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120483116</v>
+        <v>120477787</v>
       </c>
       <c r="B22" t="n">
-        <v>79624</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3111,37 +3082,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574701</v>
+        <v>574673</v>
       </c>
       <c r="R22" t="n">
-        <v>7013268</v>
+        <v>7013097</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3168,9 +3144,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3185,22 +3171,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120482861</v>
+        <v>120483538</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3213,42 +3199,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575181</v>
+        <v>574567</v>
       </c>
       <c r="R23" t="n">
-        <v>7012951</v>
+        <v>7013325</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3275,19 +3256,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3302,22 +3273,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120482987</v>
+        <v>120478091</v>
       </c>
       <c r="B24" t="n">
-        <v>90781</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3326,38 +3297,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575188</v>
+        <v>574814</v>
       </c>
       <c r="R24" t="n">
-        <v>7012937</v>
+        <v>7012964</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3389,7 +3365,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3399,7 +3375,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3426,10 +3402,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120477985</v>
+        <v>120482861</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3442,37 +3418,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574701</v>
+        <v>575181</v>
       </c>
       <c r="R25" t="n">
-        <v>7013141</v>
+        <v>7012951</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3499,9 +3480,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3516,22 +3507,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120478206</v>
+        <v>120475802</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3544,34 +3535,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574815</v>
+        <v>574568</v>
       </c>
       <c r="R26" t="n">
-        <v>7013085</v>
+        <v>7013313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3603,7 +3594,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3613,7 +3604,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3628,19 +3619,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120476091</v>
+        <v>120478206</v>
       </c>
       <c r="B27" t="n">
         <v>79623</v>
@@ -3676,17 +3667,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574596</v>
+        <v>574815</v>
       </c>
       <c r="R27" t="n">
-        <v>7013168</v>
+        <v>7013085</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3713,9 +3704,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3730,22 +3731,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120476541</v>
+        <v>120478245</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3758,42 +3759,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574609</v>
+        <v>574661</v>
       </c>
       <c r="R28" t="n">
-        <v>7013099</v>
+        <v>7013070</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3820,24 +3816,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3852,22 +3833,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120475714</v>
+        <v>120475741</v>
       </c>
       <c r="B29" t="n">
-        <v>90545</v>
+        <v>5169</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3880,34 +3861,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574557</v>
+        <v>574556</v>
       </c>
       <c r="R29" t="n">
-        <v>7013335</v>
+        <v>7013327</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3939,7 +3925,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3949,7 +3935,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3964,22 +3950,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120483075</v>
+        <v>120475719</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3992,16 +3978,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4010,16 +3996,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575155</v>
+        <v>574557</v>
       </c>
       <c r="R30" t="n">
-        <v>7012893</v>
+        <v>7013335</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4051,7 +4042,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4061,12 +4052,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4093,7 +4079,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120477573</v>
+        <v>120482411</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -4127,16 +4113,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574666</v>
+        <v>575051</v>
       </c>
       <c r="R31" t="n">
-        <v>7013074</v>
+        <v>7012995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4168,7 +4159,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4178,12 +4169,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4198,22 +4184,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120478091</v>
+        <v>120483505</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4226,42 +4212,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574814</v>
+        <v>574552</v>
       </c>
       <c r="R32" t="n">
-        <v>7012964</v>
+        <v>7013338</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4288,19 +4269,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4315,22 +4286,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120483538</v>
+        <v>120479575</v>
       </c>
       <c r="B33" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4343,37 +4314,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574567</v>
+        <v>575015</v>
       </c>
       <c r="R33" t="n">
-        <v>7013325</v>
+        <v>7012924</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4400,9 +4371,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4417,22 +4398,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120483166</v>
+        <v>120477975</v>
       </c>
       <c r="B34" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4445,37 +4426,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574637</v>
+        <v>574700</v>
       </c>
       <c r="R34" t="n">
-        <v>7013303</v>
+        <v>7012966</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4502,9 +4483,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4519,22 +4515,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120479013</v>
+        <v>120477573</v>
       </c>
       <c r="B35" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4547,16 +4543,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4565,21 +4561,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574894</v>
+        <v>574666</v>
       </c>
       <c r="R35" t="n">
-        <v>7013031</v>
+        <v>7013074</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4611,7 +4602,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4621,7 +4612,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4648,10 +4644,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120479650</v>
+        <v>120477619</v>
       </c>
       <c r="B36" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4660,25 +4656,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4688,10 +4684,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575030</v>
+        <v>574657</v>
       </c>
       <c r="R36" t="n">
-        <v>7012916</v>
+        <v>7013067</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4723,7 +4719,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4733,7 +4729,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4760,10 +4756,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120478200</v>
+        <v>120477989</v>
       </c>
       <c r="B37" t="n">
-        <v>90545</v>
+        <v>79527</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4776,21 +4772,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4800,10 +4796,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574704</v>
+        <v>574700</v>
       </c>
       <c r="R37" t="n">
-        <v>7013044</v>
+        <v>7013142</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4862,10 +4858,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120482863</v>
+        <v>120477743</v>
       </c>
       <c r="B38" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4878,21 +4874,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4902,10 +4898,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575173</v>
+        <v>574597</v>
       </c>
       <c r="R38" t="n">
-        <v>7012956</v>
+        <v>7013088</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4937,7 +4933,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4947,7 +4943,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4962,22 +4963,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120475397</v>
+        <v>120477938</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4990,34 +4991,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574558</v>
+        <v>574747</v>
       </c>
       <c r="R39" t="n">
-        <v>7013337</v>
+        <v>7013128</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5049,7 +5050,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5059,7 +5060,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5086,10 +5092,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120475679</v>
+        <v>120483096</v>
       </c>
       <c r="B40" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5098,25 +5104,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5126,10 +5132,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574558</v>
+        <v>574707</v>
       </c>
       <c r="R40" t="n">
-        <v>7013348</v>
+        <v>7013260</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5188,10 +5194,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120482317</v>
+        <v>120476675</v>
       </c>
       <c r="B41" t="n">
-        <v>96891</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5200,25 +5206,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5228,13 +5234,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574773</v>
+        <v>574614</v>
       </c>
       <c r="R41" t="n">
-        <v>7013002</v>
+        <v>7013128</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5261,9 +5267,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5278,22 +5294,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120475858</v>
+        <v>120477524</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5306,37 +5322,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574570</v>
+        <v>574538</v>
       </c>
       <c r="R42" t="n">
-        <v>7013265</v>
+        <v>7013034</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5381,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5375,12 +5391,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5395,22 +5406,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120480946</v>
+        <v>120478767</v>
       </c>
       <c r="B43" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5423,21 +5434,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5447,13 +5458,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575006</v>
+        <v>574761</v>
       </c>
       <c r="R43" t="n">
-        <v>7012970</v>
+        <v>7013035</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5480,24 +5491,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Lunglav på rönn och gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5512,22 +5508,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120478431</v>
+        <v>120478407</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5536,25 +5532,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5564,10 +5560,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574745</v>
+        <v>574733</v>
       </c>
       <c r="R44" t="n">
-        <v>7013030</v>
+        <v>7013036</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5626,7 +5622,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120478207</v>
+        <v>120477678</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5660,24 +5656,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574661</v>
+        <v>574542</v>
       </c>
       <c r="R45" t="n">
-        <v>7013070</v>
+        <v>7013136</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5704,14 +5695,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5726,22 +5727,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120477787</v>
+        <v>120482599</v>
       </c>
       <c r="B46" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5754,42 +5755,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574673</v>
+        <v>574771</v>
       </c>
       <c r="R46" t="n">
-        <v>7013097</v>
+        <v>7012977</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5816,19 +5812,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5843,22 +5829,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120476675</v>
+        <v>120482987</v>
       </c>
       <c r="B47" t="n">
-        <v>79623</v>
+        <v>90781</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5867,25 +5853,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>1106</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5895,10 +5881,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574614</v>
+        <v>575188</v>
       </c>
       <c r="R47" t="n">
-        <v>7013128</v>
+        <v>7012937</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5930,7 +5916,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5940,7 +5926,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5967,10 +5953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120476831</v>
+        <v>120476839</v>
       </c>
       <c r="B48" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5983,34 +5969,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574561</v>
+        <v>574549</v>
       </c>
       <c r="R48" t="n">
-        <v>7013070</v>
+        <v>7012993</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6042,7 +6033,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6052,7 +6043,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6067,22 +6058,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120482763</v>
+        <v>120477401</v>
       </c>
       <c r="B49" t="n">
-        <v>90580</v>
+        <v>90781</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6091,25 +6082,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6119,10 +6110,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575128</v>
+        <v>574646</v>
       </c>
       <c r="R49" t="n">
-        <v>7012966</v>
+        <v>7013031</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6154,7 +6145,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6164,7 +6155,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6191,10 +6182,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120478036</v>
+        <v>120478232</v>
       </c>
       <c r="B50" t="n">
-        <v>91023</v>
+        <v>90545</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6203,25 +6194,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6231,10 +6222,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574778</v>
+        <v>574911</v>
       </c>
       <c r="R50" t="n">
-        <v>7012962</v>
+        <v>7013004</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6266,7 +6257,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6276,7 +6267,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6303,10 +6294,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120479509</v>
+        <v>120480588</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6319,21 +6310,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6343,13 +6334,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574766</v>
+        <v>575008</v>
       </c>
       <c r="R51" t="n">
-        <v>7013045</v>
+        <v>7012970</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6376,9 +6367,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6393,22 +6394,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120478597</v>
+        <v>120477985</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6421,21 +6422,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6445,13 +6446,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574914</v>
+        <v>574701</v>
       </c>
       <c r="R52" t="n">
-        <v>7013012</v>
+        <v>7013141</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6478,24 +6479,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6510,22 +6496,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120477678</v>
+        <v>120476831</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6538,34 +6524,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574542</v>
+        <v>574561</v>
       </c>
       <c r="R53" t="n">
-        <v>7013136</v>
+        <v>7013070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6597,7 +6583,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6607,12 +6593,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6639,10 +6620,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120483636</v>
+        <v>120476175</v>
       </c>
       <c r="B54" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6655,34 +6636,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574559</v>
+        <v>574595</v>
       </c>
       <c r="R54" t="n">
-        <v>7013332</v>
+        <v>7013170</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6741,10 +6727,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120476791</v>
+        <v>120481907</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6757,21 +6743,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6781,13 +6767,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574551</v>
+        <v>574773</v>
       </c>
       <c r="R55" t="n">
-        <v>7013059</v>
+        <v>7013002</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6814,24 +6800,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6846,22 +6817,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120477400</v>
+        <v>120478597</v>
       </c>
       <c r="B56" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6870,42 +6841,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574552</v>
+        <v>574914</v>
       </c>
       <c r="R56" t="n">
-        <v>7013013</v>
+        <v>7013012</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6937,7 +6904,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6947,7 +6914,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6962,22 +6934,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120476955</v>
+        <v>120475714</v>
       </c>
       <c r="B57" t="n">
-        <v>5169</v>
+        <v>90545</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6990,39 +6962,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574526</v>
+        <v>574557</v>
       </c>
       <c r="R57" t="n">
-        <v>7013059</v>
+        <v>7013335</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7054,7 +7021,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7064,7 +7031,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7079,22 +7046,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120481907</v>
+        <v>120476584</v>
       </c>
       <c r="B58" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7107,21 +7074,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7131,13 +7098,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574773</v>
+        <v>574621</v>
       </c>
       <c r="R58" t="n">
-        <v>7013002</v>
+        <v>7013153</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7164,9 +7131,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7181,19 +7163,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120483092</v>
+        <v>120478207</v>
       </c>
       <c r="B59" t="n">
         <v>57320</v>
@@ -7227,19 +7209,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575166</v>
+        <v>574661</v>
       </c>
       <c r="R59" t="n">
-        <v>7012887</v>
+        <v>7013070</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7266,24 +7253,14 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7298,19 +7275,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120479582</v>
+        <v>120482763</v>
       </c>
       <c r="B60" t="n">
         <v>90580</v>
@@ -7350,13 +7327,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574748</v>
+        <v>575128</v>
       </c>
       <c r="R60" t="n">
-        <v>7013002</v>
+        <v>7012966</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7383,9 +7360,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7400,22 +7387,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120479575</v>
+        <v>120483427</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7428,34 +7415,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575015</v>
+        <v>574893</v>
       </c>
       <c r="R61" t="n">
-        <v>7012924</v>
+        <v>7013053</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7487,7 +7479,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7497,7 +7489,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7512,19 +7504,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120477886</v>
+        <v>120479683</v>
       </c>
       <c r="B62" t="n">
         <v>57320</v>
@@ -7569,10 +7561,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574719</v>
+        <v>574981</v>
       </c>
       <c r="R62" t="n">
-        <v>7013107</v>
+        <v>7012954</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7604,7 +7596,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7614,12 +7606,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7646,10 +7633,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120482540</v>
+        <v>120478039</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7662,37 +7649,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575091</v>
+        <v>574700</v>
       </c>
       <c r="R63" t="n">
-        <v>7012974</v>
+        <v>7013066</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7719,19 +7711,14 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:52</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7746,22 +7733,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120477619</v>
+        <v>120483119</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7774,21 +7761,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7798,10 +7785,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574657</v>
+        <v>575114</v>
       </c>
       <c r="R64" t="n">
-        <v>7013067</v>
+        <v>7012928</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7833,7 +7820,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7843,7 +7830,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7858,19 +7850,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120476584</v>
+        <v>120483075</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7910,10 +7902,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574621</v>
+        <v>575155</v>
       </c>
       <c r="R65" t="n">
-        <v>7013153</v>
+        <v>7012893</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7945,7 +7937,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7955,12 +7947,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7975,22 +7967,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120482411</v>
+        <v>120482660</v>
       </c>
       <c r="B66" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8003,42 +7995,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575051</v>
+        <v>574772</v>
       </c>
       <c r="R66" t="n">
-        <v>7012995</v>
+        <v>7012971</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8065,19 +8052,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8092,22 +8069,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120477938</v>
+        <v>120478069</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8120,21 +8097,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8144,10 +8121,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574747</v>
+        <v>574798</v>
       </c>
       <c r="R67" t="n">
-        <v>7013128</v>
+        <v>7012940</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8179,7 +8156,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8189,12 +8166,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8209,22 +8181,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120478210</v>
+        <v>120478239</v>
       </c>
       <c r="B68" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8237,21 +8209,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8261,10 +8233,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574881</v>
+        <v>574847</v>
       </c>
       <c r="R68" t="n">
-        <v>7012991</v>
+        <v>7013095</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8296,7 +8268,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8306,7 +8278,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8321,22 +8293,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120475802</v>
+        <v>120483114</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8349,21 +8321,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8373,13 +8345,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574568</v>
+        <v>574704</v>
       </c>
       <c r="R69" t="n">
-        <v>7013313</v>
+        <v>7013264</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8406,19 +8378,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8433,22 +8395,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120483094</v>
+        <v>120479001</v>
       </c>
       <c r="B70" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8457,25 +8419,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8485,10 +8447,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>575168</v>
+        <v>574918</v>
       </c>
       <c r="R70" t="n">
-        <v>7012937</v>
+        <v>7012974</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8520,7 +8482,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8530,7 +8492,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8557,10 +8519,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120483427</v>
+        <v>120483518</v>
       </c>
       <c r="B71" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8573,42 +8535,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574893</v>
+        <v>574570</v>
       </c>
       <c r="R71" t="n">
-        <v>7013053</v>
+        <v>7013321</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8635,19 +8592,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8662,22 +8609,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120483505</v>
+        <v>120479013</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8690,37 +8637,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574552</v>
+        <v>574894</v>
       </c>
       <c r="R72" t="n">
-        <v>7013338</v>
+        <v>7013031</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8747,9 +8699,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8764,22 +8726,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120475921</v>
+        <v>120478128</v>
       </c>
       <c r="B73" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8788,43 +8750,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574585</v>
+        <v>574815</v>
       </c>
       <c r="R73" t="n">
-        <v>7013246</v>
+        <v>7012976</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8856,7 +8813,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8866,7 +8823,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8881,22 +8838,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120482434</v>
+        <v>120482317</v>
       </c>
       <c r="B74" t="n">
-        <v>90580</v>
+        <v>96891</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8905,25 +8862,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8933,10 +8890,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574754</v>
+        <v>574773</v>
       </c>
       <c r="R74" t="n">
-        <v>7012970</v>
+        <v>7013002</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8995,10 +8952,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120478767</v>
+        <v>120478036</v>
       </c>
       <c r="B75" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9007,25 +8964,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9035,13 +8992,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574761</v>
+        <v>574778</v>
       </c>
       <c r="R75" t="n">
-        <v>7013035</v>
+        <v>7012962</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9068,9 +9025,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9085,22 +9052,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120478804</v>
+        <v>120476784</v>
       </c>
       <c r="B76" t="n">
-        <v>74654</v>
+        <v>79623</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9113,21 +9080,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9137,10 +9104,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574916</v>
+        <v>574525</v>
       </c>
       <c r="R76" t="n">
-        <v>7012988</v>
+        <v>7013029</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9172,7 +9139,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9182,7 +9149,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9197,22 +9164,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120478253</v>
+        <v>120475397</v>
       </c>
       <c r="B77" t="n">
-        <v>82321</v>
+        <v>79624</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9225,34 +9192,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574917</v>
+        <v>574558</v>
       </c>
       <c r="R77" t="n">
-        <v>7013009</v>
+        <v>7013337</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9284,7 +9251,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9294,7 +9261,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9309,22 +9276,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120478428</v>
+        <v>120482920</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9337,21 +9304,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9361,10 +9328,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>574922</v>
+        <v>575178</v>
       </c>
       <c r="R78" t="n">
-        <v>7012993</v>
+        <v>7012946</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9396,7 +9363,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9406,7 +9373,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9433,10 +9400,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120478069</v>
+        <v>120476601</v>
       </c>
       <c r="B79" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9449,21 +9416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9473,10 +9440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>574798</v>
+        <v>574573</v>
       </c>
       <c r="R79" t="n">
-        <v>7012940</v>
+        <v>7013042</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9508,7 +9475,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9518,7 +9485,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9533,22 +9505,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120477989</v>
+        <v>120478035</v>
       </c>
       <c r="B80" t="n">
-        <v>79527</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9557,41 +9529,50 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>574700</v>
+        <v>574785</v>
       </c>
       <c r="R80" t="n">
-        <v>7013142</v>
+        <v>7013205</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9618,9 +9599,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9635,22 +9626,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120482523</v>
+        <v>120475677</v>
       </c>
       <c r="B81" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9663,37 +9654,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>574779</v>
+        <v>574559</v>
       </c>
       <c r="R81" t="n">
-        <v>7012971</v>
+        <v>7013337</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9720,9 +9711,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9737,22 +9738,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120478974</v>
+        <v>120478226</v>
       </c>
       <c r="B82" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9765,21 +9766,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9789,13 +9790,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>574753</v>
+        <v>574839</v>
       </c>
       <c r="R82" t="n">
-        <v>7013026</v>
+        <v>7013100</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9822,9 +9823,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9839,19 +9850,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120476542</v>
+        <v>120482757</v>
       </c>
       <c r="B83" t="n">
         <v>57320</v>
@@ -9885,16 +9896,21 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>574624</v>
+        <v>575161</v>
       </c>
       <c r="R83" t="n">
-        <v>7013126</v>
+        <v>7012940</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9926,7 +9942,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9936,12 +9952,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9968,10 +9979,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120482660</v>
+        <v>120476454</v>
       </c>
       <c r="B84" t="n">
-        <v>90864</v>
+        <v>86895</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9984,34 +9995,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>574772</v>
+        <v>574577</v>
       </c>
       <c r="R84" t="n">
-        <v>7012971</v>
+        <v>7013274</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -10070,10 +10081,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120483155</v>
+        <v>120477715</v>
       </c>
       <c r="B85" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10086,37 +10097,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>574641</v>
+        <v>574645</v>
       </c>
       <c r="R85" t="n">
-        <v>7013295</v>
+        <v>7013075</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10143,9 +10154,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10160,22 +10181,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120483136</v>
+        <v>120482523</v>
       </c>
       <c r="B86" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10188,21 +10209,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10212,13 +10233,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>575076</v>
+        <v>574779</v>
       </c>
       <c r="R86" t="n">
-        <v>7012962</v>
+        <v>7012971</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10245,19 +10266,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10272,22 +10283,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120481387</v>
+        <v>120482863</v>
       </c>
       <c r="B87" t="n">
-        <v>57336</v>
+        <v>90527</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10300,42 +10311,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>574762</v>
+        <v>575173</v>
       </c>
       <c r="R87" t="n">
-        <v>7012995</v>
+        <v>7012956</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10362,9 +10368,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10379,22 +10395,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120478878</v>
+        <v>120483166</v>
       </c>
       <c r="B88" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10407,34 +10423,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>574759</v>
+        <v>574637</v>
       </c>
       <c r="R88" t="n">
-        <v>7013028</v>
+        <v>7013303</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -10493,10 +10509,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120477715</v>
+        <v>120483636</v>
       </c>
       <c r="B89" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10509,37 +10525,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>574645</v>
+        <v>574559</v>
       </c>
       <c r="R89" t="n">
-        <v>7013075</v>
+        <v>7013332</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10566,19 +10582,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:37</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10593,22 +10599,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120478002</v>
+        <v>120481387</v>
       </c>
       <c r="B90" t="n">
-        <v>90864</v>
+        <v>57336</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10621,37 +10627,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>574766</v>
+        <v>574762</v>
       </c>
       <c r="R90" t="n">
-        <v>7012936</v>
+        <v>7012995</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10678,19 +10689,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10705,22 +10706,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120478245</v>
+        <v>120483094</v>
       </c>
       <c r="B91" t="n">
-        <v>79623</v>
+        <v>91023</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10729,25 +10730,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10757,13 +10758,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>574661</v>
+        <v>575168</v>
       </c>
       <c r="R91" t="n">
-        <v>7013070</v>
+        <v>7012937</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10790,9 +10791,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10807,22 +10818,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120478035</v>
+        <v>120483116</v>
       </c>
       <c r="B92" t="n">
-        <v>97930</v>
+        <v>79624</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10831,50 +10842,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>574785</v>
+        <v>574701</v>
       </c>
       <c r="R92" t="n">
-        <v>7013205</v>
+        <v>7013268</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10901,19 +10903,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10928,22 +10920,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120482599</v>
+        <v>120483141</v>
       </c>
       <c r="B93" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10952,38 +10944,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>574771</v>
+        <v>574645</v>
       </c>
       <c r="R93" t="n">
-        <v>7012977</v>
+        <v>7013293</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -11042,7 +11034,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120476784</v>
+        <v>120480946</v>
       </c>
       <c r="B94" t="n">
         <v>79623</v>
@@ -11082,10 +11074,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>574525</v>
+        <v>575006</v>
       </c>
       <c r="R94" t="n">
-        <v>7013029</v>
+        <v>7012970</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11117,7 +11109,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11127,7 +11119,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn och gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11154,10 +11151,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120477401</v>
+        <v>120483136</v>
       </c>
       <c r="B95" t="n">
-        <v>90781</v>
+        <v>79623</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11166,25 +11163,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11194,10 +11191,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>574646</v>
+        <v>575076</v>
       </c>
       <c r="R95" t="n">
-        <v>7013031</v>
+        <v>7012962</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11229,7 +11226,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11239,7 +11236,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11266,10 +11263,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120477975</v>
+        <v>120477828</v>
       </c>
       <c r="B96" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11282,21 +11279,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11306,10 +11303,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>574700</v>
+        <v>574688</v>
       </c>
       <c r="R96" t="n">
-        <v>7012966</v>
+        <v>7012983</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11341,7 +11338,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11351,12 +11348,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11383,10 +11375,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120478232</v>
+        <v>120477886</v>
       </c>
       <c r="B97" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11395,38 +11387,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>574911</v>
+        <v>574719</v>
       </c>
       <c r="R97" t="n">
-        <v>7013004</v>
+        <v>7013107</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11458,7 +11455,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11468,7 +11465,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11483,22 +11485,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120478274</v>
+        <v>120476791</v>
       </c>
       <c r="B98" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11507,25 +11509,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11535,10 +11537,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>574884</v>
+        <v>574551</v>
       </c>
       <c r="R98" t="n">
-        <v>7013094</v>
+        <v>7013059</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11570,7 +11572,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11580,7 +11582,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11595,22 +11602,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120476601</v>
+        <v>120478002</v>
       </c>
       <c r="B99" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11623,21 +11630,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11647,10 +11654,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>574573</v>
+        <v>574766</v>
       </c>
       <c r="R99" t="n">
-        <v>7013042</v>
+        <v>7012936</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11682,7 +11689,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11692,12 +11699,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11712,22 +11714,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120476175</v>
+        <v>120482873</v>
       </c>
       <c r="B100" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11740,42 +11742,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>574595</v>
+        <v>575178</v>
       </c>
       <c r="R100" t="n">
-        <v>7013170</v>
+        <v>7012952</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11802,9 +11799,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11819,22 +11826,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120482864</v>
+        <v>120483118</v>
       </c>
       <c r="B101" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11847,21 +11854,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11871,13 +11878,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>574700</v>
+        <v>575141</v>
       </c>
       <c r="R101" t="n">
-        <v>7013007</v>
+        <v>7012926</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11904,9 +11911,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11921,22 +11938,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120483114</v>
+        <v>120478253</v>
       </c>
       <c r="B102" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11949,37 +11966,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>574704</v>
+        <v>574917</v>
       </c>
       <c r="R102" t="n">
-        <v>7013264</v>
+        <v>7013009</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12006,9 +12023,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12023,22 +12050,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120482757</v>
+        <v>120482540</v>
       </c>
       <c r="B103" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12051,39 +12078,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>575161</v>
+        <v>575091</v>
       </c>
       <c r="R103" t="n">
-        <v>7012940</v>
+        <v>7012974</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12115,7 +12137,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12125,7 +12147,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12152,10 +12174,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120482920</v>
+        <v>120478428</v>
       </c>
       <c r="B104" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12168,21 +12190,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12192,10 +12214,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>575178</v>
+        <v>574922</v>
       </c>
       <c r="R104" t="n">
-        <v>7012946</v>
+        <v>7012993</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12227,7 +12249,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12237,7 +12259,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12264,10 +12286,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120483118</v>
+        <v>120483155</v>
       </c>
       <c r="B105" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12280,37 +12302,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>575141</v>
+        <v>574641</v>
       </c>
       <c r="R105" t="n">
-        <v>7012926</v>
+        <v>7013295</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12337,19 +12359,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>16:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12364,22 +12376,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120483141</v>
+        <v>120477951</v>
       </c>
       <c r="B106" t="n">
-        <v>96885</v>
+        <v>57431</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12392,37 +12404,51 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>574645</v>
+        <v>574667</v>
       </c>
       <c r="R106" t="n">
-        <v>7013293</v>
+        <v>7012956</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12449,9 +12475,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12466,22 +12502,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120479001</v>
+        <v>120482434</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12494,21 +12530,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12518,13 +12554,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>574918</v>
+        <v>574754</v>
       </c>
       <c r="R107" t="n">
-        <v>7012974</v>
+        <v>7012970</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12551,19 +12587,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:31</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12578,22 +12604,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120477974</v>
+        <v>120478878</v>
       </c>
       <c r="B108" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12606,42 +12632,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>574762</v>
+        <v>574759</v>
       </c>
       <c r="R108" t="n">
-        <v>7013134</v>
+        <v>7013028</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12668,19 +12689,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>14:41</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12695,22 +12706,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120478407</v>
+        <v>120479582</v>
       </c>
       <c r="B109" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12719,25 +12730,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12747,10 +12758,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>574733</v>
+        <v>574748</v>
       </c>
       <c r="R109" t="n">
-        <v>7013036</v>
+        <v>7013002</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12809,10 +12820,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120478226</v>
+        <v>120477974</v>
       </c>
       <c r="B110" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12825,34 +12836,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>574839</v>
+        <v>574762</v>
       </c>
       <c r="R110" t="n">
-        <v>7013100</v>
+        <v>7013134</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12884,7 +12900,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12894,7 +12910,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12921,10 +12937,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120477743</v>
+        <v>120478200</v>
       </c>
       <c r="B111" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12933,25 +12949,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12961,13 +12977,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>574597</v>
+        <v>574704</v>
       </c>
       <c r="R111" t="n">
-        <v>7013088</v>
+        <v>7013044</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12994,24 +13010,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13026,22 +13027,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120477828</v>
+        <v>120479650</v>
       </c>
       <c r="B112" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13050,25 +13051,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13078,10 +13079,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>574688</v>
+        <v>575030</v>
       </c>
       <c r="R112" t="n">
-        <v>7012983</v>
+        <v>7012916</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13113,7 +13114,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13123,7 +13124,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13150,10 +13151,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120482642</v>
+        <v>120475679</v>
       </c>
       <c r="B113" t="n">
-        <v>82321</v>
+        <v>79652</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13162,41 +13163,41 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>575068</v>
+        <v>574558</v>
       </c>
       <c r="R113" t="n">
-        <v>7013015</v>
+        <v>7013348</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13223,19 +13224,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13250,22 +13241,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120476454</v>
+        <v>120478210</v>
       </c>
       <c r="B114" t="n">
-        <v>86895</v>
+        <v>79623</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13278,37 +13269,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>574577</v>
+        <v>574881</v>
       </c>
       <c r="R114" t="n">
-        <v>7013274</v>
+        <v>7012991</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13335,9 +13326,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13352,22 +13353,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120476914</v>
+        <v>120477400</v>
       </c>
       <c r="B115" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13376,38 +13377,42 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>574547</v>
+        <v>574552</v>
       </c>
       <c r="R115" t="n">
-        <v>7013045</v>
+        <v>7013013</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13439,7 +13444,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13449,7 +13454,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13476,10 +13481,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120475677</v>
+        <v>120483092</v>
       </c>
       <c r="B116" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13492,34 +13497,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>574559</v>
+        <v>575166</v>
       </c>
       <c r="R116" t="n">
-        <v>7013337</v>
+        <v>7012887</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13551,7 +13556,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13561,7 +13566,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13576,22 +13586,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120483518</v>
+        <v>120476542</v>
       </c>
       <c r="B117" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13604,37 +13614,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>574570</v>
+        <v>574624</v>
       </c>
       <c r="R117" t="n">
-        <v>7013321</v>
+        <v>7013126</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13661,9 +13671,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13678,22 +13703,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120476839</v>
+        <v>120475858</v>
       </c>
       <c r="B118" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13706,16 +13731,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -13724,21 +13749,16 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>574549</v>
+        <v>574570</v>
       </c>
       <c r="R118" t="n">
-        <v>7012993</v>
+        <v>7013265</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13770,7 +13790,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13780,7 +13800,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13807,10 +13832,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120475740</v>
+        <v>120478431</v>
       </c>
       <c r="B119" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13823,37 +13848,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>574557</v>
+        <v>574745</v>
       </c>
       <c r="R119" t="n">
-        <v>7013323</v>
+        <v>7013030</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13880,19 +13905,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13907,22 +13922,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120475741</v>
+        <v>120478974</v>
       </c>
       <c r="B120" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13931,46 +13946,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>574556</v>
+        <v>574753</v>
       </c>
       <c r="R120" t="n">
-        <v>7013327</v>
+        <v>7013026</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13997,19 +14007,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14024,22 +14024,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120483119</v>
+        <v>120475740</v>
       </c>
       <c r="B121" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14052,34 +14052,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>575114</v>
+        <v>574557</v>
       </c>
       <c r="R121" t="n">
-        <v>7012928</v>
+        <v>7013323</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14121,12 +14121,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14153,7 +14148,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120483096</v>
+        <v>120476091</v>
       </c>
       <c r="B122" t="n">
         <v>79623</v>
@@ -14193,10 +14188,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>574707</v>
+        <v>574596</v>
       </c>
       <c r="R122" t="n">
-        <v>7013260</v>
+        <v>7013168</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -14255,10 +14250,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120478239</v>
+        <v>120482642</v>
       </c>
       <c r="B123" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14271,21 +14266,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14295,10 +14290,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>574847</v>
+        <v>575068</v>
       </c>
       <c r="R123" t="n">
-        <v>7013095</v>
+        <v>7013015</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14330,7 +14325,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14340,7 +14335,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14367,10 +14362,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120478128</v>
+        <v>120477919</v>
       </c>
       <c r="B124" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14379,25 +14374,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14407,10 +14402,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574815</v>
+        <v>574682</v>
       </c>
       <c r="R124" t="n">
-        <v>7012976</v>
+        <v>7012947</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14442,7 +14437,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14452,7 +14447,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120475921</v>
+        <v>120478407</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2070,46 +2070,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574585</v>
+        <v>574733</v>
       </c>
       <c r="R13" t="n">
-        <v>7013246</v>
+        <v>7013036</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2136,19 +2131,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,22 +2148,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120482864</v>
+        <v>120475397</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2191,37 +2176,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574700</v>
+        <v>574558</v>
       </c>
       <c r="R14" t="n">
-        <v>7013007</v>
+        <v>7013337</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,9 +2233,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2265,22 +2260,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120476541</v>
+        <v>120478804</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2293,39 +2288,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574609</v>
+        <v>574916</v>
       </c>
       <c r="R15" t="n">
-        <v>7013099</v>
+        <v>7012988</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2357,7 +2347,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2367,12 +2357,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,22 +2372,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120479509</v>
+        <v>120476791</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2415,21 +2400,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2439,13 +2424,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574766</v>
+        <v>574551</v>
       </c>
       <c r="R16" t="n">
-        <v>7013045</v>
+        <v>7013059</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2472,9 +2457,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,22 +2489,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120478274</v>
+        <v>120483119</v>
       </c>
       <c r="B17" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,25 +2513,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574884</v>
+        <v>575114</v>
       </c>
       <c r="R17" t="n">
-        <v>7013094</v>
+        <v>7012928</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2586,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2613,10 +2618,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120478900</v>
+        <v>120476542</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2629,21 +2634,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574883</v>
+        <v>574624</v>
       </c>
       <c r="R18" t="n">
-        <v>7013078</v>
+        <v>7013126</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2688,7 +2693,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2698,7 +2703,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,22 +2723,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120478804</v>
+        <v>120477400</v>
       </c>
       <c r="B19" t="n">
-        <v>74654</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2737,38 +2747,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574916</v>
+        <v>574552</v>
       </c>
       <c r="R19" t="n">
-        <v>7012988</v>
+        <v>7013013</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2800,7 +2814,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2810,7 +2824,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120476914</v>
+        <v>120475802</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,34 +2867,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574547</v>
+        <v>574568</v>
       </c>
       <c r="R20" t="n">
-        <v>7013045</v>
+        <v>7013313</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2912,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2922,7 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2949,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120476955</v>
+        <v>120477919</v>
       </c>
       <c r="B21" t="n">
-        <v>5169</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2961,43 +2975,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574526</v>
+        <v>574682</v>
       </c>
       <c r="R21" t="n">
-        <v>7013059</v>
+        <v>7012947</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3029,7 +3038,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3039,7 +3048,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3066,10 +3080,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120477787</v>
+        <v>120483094</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>91023</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3078,43 +3092,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574673</v>
+        <v>575168</v>
       </c>
       <c r="R22" t="n">
-        <v>7013097</v>
+        <v>7012937</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3146,7 +3155,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3156,7 +3165,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,22 +3180,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120483538</v>
+        <v>120475679</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>79652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3195,25 +3204,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3223,10 +3232,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574567</v>
+        <v>574558</v>
       </c>
       <c r="R23" t="n">
-        <v>7013325</v>
+        <v>7013348</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3285,7 +3294,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120478091</v>
+        <v>120482411</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3330,10 +3339,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574814</v>
+        <v>575051</v>
       </c>
       <c r="R24" t="n">
-        <v>7012964</v>
+        <v>7012995</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3365,7 +3374,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3375,7 +3384,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3402,7 +3411,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120482861</v>
+        <v>120478597</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3436,21 +3445,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575181</v>
+        <v>574914</v>
       </c>
       <c r="R25" t="n">
-        <v>7012951</v>
+        <v>7013012</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3482,7 +3486,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3492,7 +3496,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3519,10 +3528,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120475802</v>
+        <v>120482434</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3535,37 +3544,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574568</v>
+        <v>574754</v>
       </c>
       <c r="R26" t="n">
-        <v>7013313</v>
+        <v>7012970</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3592,19 +3601,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3619,22 +3618,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120478206</v>
+        <v>120482540</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3647,21 +3646,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3671,10 +3670,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574815</v>
+        <v>575091</v>
       </c>
       <c r="R27" t="n">
-        <v>7013085</v>
+        <v>7012974</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3706,7 +3705,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3716,7 +3715,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3731,22 +3730,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120478245</v>
+        <v>120482317</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>96891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3755,25 +3754,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3783,10 +3782,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574661</v>
+        <v>574773</v>
       </c>
       <c r="R28" t="n">
-        <v>7013070</v>
+        <v>7013002</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3845,10 +3844,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120475741</v>
+        <v>120478036</v>
       </c>
       <c r="B29" t="n">
-        <v>5169</v>
+        <v>91023</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3857,43 +3856,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574556</v>
+        <v>574778</v>
       </c>
       <c r="R29" t="n">
-        <v>7013327</v>
+        <v>7012962</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3925,7 +3919,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3935,7 +3929,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3962,10 +3956,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120475719</v>
+        <v>120478069</v>
       </c>
       <c r="B30" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3978,39 +3972,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574557</v>
+        <v>574798</v>
       </c>
       <c r="R30" t="n">
-        <v>7013335</v>
+        <v>7012940</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4042,7 +4031,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4052,7 +4041,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4067,22 +4056,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120482411</v>
+        <v>120483427</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4095,16 +4084,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4115,7 +4104,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4124,10 +4113,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575051</v>
+        <v>574893</v>
       </c>
       <c r="R31" t="n">
-        <v>7012995</v>
+        <v>7013053</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4159,7 +4148,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4169,7 +4158,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4184,22 +4173,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120483505</v>
+        <v>120476601</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4212,37 +4201,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574552</v>
+        <v>574573</v>
       </c>
       <c r="R32" t="n">
-        <v>7013338</v>
+        <v>7013042</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4269,9 +4258,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4286,19 +4290,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120479575</v>
+        <v>120478239</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -4338,10 +4342,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575015</v>
+        <v>574847</v>
       </c>
       <c r="R33" t="n">
-        <v>7012924</v>
+        <v>7013095</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4373,7 +4377,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4383,7 +4387,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4398,22 +4402,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120477975</v>
+        <v>120478206</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4426,21 +4430,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4450,10 +4454,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574700</v>
+        <v>574815</v>
       </c>
       <c r="R34" t="n">
-        <v>7012966</v>
+        <v>7013085</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4485,7 +4489,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4495,12 +4499,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4515,22 +4514,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120477573</v>
+        <v>120477951</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4539,20 +4538,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4560,17 +4559,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574666</v>
+        <v>574667</v>
       </c>
       <c r="R35" t="n">
-        <v>7013074</v>
+        <v>7012956</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4602,7 +4615,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4612,12 +4625,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4632,22 +4640,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120477619</v>
+        <v>120480588</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4660,21 +4668,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4684,10 +4692,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574657</v>
+        <v>575008</v>
       </c>
       <c r="R36" t="n">
-        <v>7013067</v>
+        <v>7012970</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4719,7 +4727,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4729,7 +4737,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4744,22 +4752,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120477989</v>
+        <v>120478900</v>
       </c>
       <c r="B37" t="n">
-        <v>79527</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4768,25 +4776,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4796,13 +4804,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574700</v>
+        <v>574883</v>
       </c>
       <c r="R37" t="n">
-        <v>7013142</v>
+        <v>7013078</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4829,9 +4837,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4846,22 +4864,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120477743</v>
+        <v>120477715</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4874,21 +4892,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4898,10 +4916,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574597</v>
+        <v>574645</v>
       </c>
       <c r="R38" t="n">
-        <v>7013088</v>
+        <v>7013075</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4933,7 +4951,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4943,12 +4961,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4963,22 +4976,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120477938</v>
+        <v>120482873</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4991,21 +5004,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5015,10 +5028,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574747</v>
+        <v>575178</v>
       </c>
       <c r="R39" t="n">
-        <v>7013128</v>
+        <v>7012952</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5050,7 +5063,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5060,12 +5073,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,10 +5100,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120483096</v>
+        <v>120475719</v>
       </c>
       <c r="B40" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5108,37 +5116,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574707</v>
+        <v>574557</v>
       </c>
       <c r="R40" t="n">
-        <v>7013260</v>
+        <v>7013335</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5165,9 +5178,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5182,22 +5205,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120476675</v>
+        <v>120475741</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>5169</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5206,38 +5229,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574614</v>
+        <v>574556</v>
       </c>
       <c r="R41" t="n">
-        <v>7013128</v>
+        <v>7013327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5269,7 +5297,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5279,7 +5307,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5306,7 +5334,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120477524</v>
+        <v>120476675</v>
       </c>
       <c r="B42" t="n">
         <v>79623</v>
@@ -5346,13 +5374,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574538</v>
+        <v>574614</v>
       </c>
       <c r="R42" t="n">
-        <v>7013034</v>
+        <v>7013128</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5381,7 +5409,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5391,7 +5419,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5406,22 +5434,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120478767</v>
+        <v>120483096</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5434,34 +5462,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574761</v>
+        <v>574707</v>
       </c>
       <c r="R43" t="n">
-        <v>7013035</v>
+        <v>7013260</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5520,10 +5548,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120478407</v>
+        <v>120478128</v>
       </c>
       <c r="B44" t="n">
-        <v>91023</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5532,25 +5560,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5560,13 +5588,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574733</v>
+        <v>574815</v>
       </c>
       <c r="R44" t="n">
-        <v>7013036</v>
+        <v>7012976</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5593,9 +5621,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5610,22 +5648,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120477678</v>
+        <v>120478210</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5638,34 +5676,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574542</v>
+        <v>574881</v>
       </c>
       <c r="R45" t="n">
-        <v>7013136</v>
+        <v>7012991</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5697,7 +5735,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5707,12 +5745,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5739,10 +5772,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120482599</v>
+        <v>120476839</v>
       </c>
       <c r="B46" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5755,37 +5788,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574771</v>
+        <v>574549</v>
       </c>
       <c r="R46" t="n">
-        <v>7012977</v>
+        <v>7012993</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5812,9 +5850,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5829,22 +5877,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120482987</v>
+        <v>120482757</v>
       </c>
       <c r="B47" t="n">
-        <v>90781</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5853,38 +5901,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575188</v>
+        <v>575161</v>
       </c>
       <c r="R47" t="n">
-        <v>7012937</v>
+        <v>7012940</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5916,7 +5969,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5926,7 +5979,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5953,10 +6006,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120476839</v>
+        <v>120483538</v>
       </c>
       <c r="B48" t="n">
-        <v>57336</v>
+        <v>82321</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5969,42 +6022,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574549</v>
+        <v>574567</v>
       </c>
       <c r="R48" t="n">
-        <v>7012993</v>
+        <v>7013325</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6031,19 +6079,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6058,12 +6096,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6182,10 +6220,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120478232</v>
+        <v>120483166</v>
       </c>
       <c r="B50" t="n">
-        <v>90545</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6194,41 +6232,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574911</v>
+        <v>574637</v>
       </c>
       <c r="R50" t="n">
-        <v>7013004</v>
+        <v>7013303</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6255,19 +6293,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6282,19 +6310,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120480588</v>
+        <v>120476091</v>
       </c>
       <c r="B51" t="n">
         <v>79623</v>
@@ -6330,17 +6358,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575008</v>
+        <v>574596</v>
       </c>
       <c r="R51" t="n">
-        <v>7012970</v>
+        <v>7013168</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6367,19 +6395,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6394,22 +6412,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120477985</v>
+        <v>120478428</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6422,21 +6440,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6446,13 +6464,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574701</v>
+        <v>574922</v>
       </c>
       <c r="R52" t="n">
-        <v>7013141</v>
+        <v>7012993</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6479,9 +6497,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6496,22 +6524,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120476831</v>
+        <v>120482599</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6524,21 +6552,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6548,13 +6576,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574561</v>
+        <v>574771</v>
       </c>
       <c r="R53" t="n">
-        <v>7013070</v>
+        <v>7012977</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6581,19 +6609,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6608,22 +6626,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120476175</v>
+        <v>120478226</v>
       </c>
       <c r="B54" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6636,42 +6654,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574595</v>
+        <v>574839</v>
       </c>
       <c r="R54" t="n">
-        <v>7013170</v>
+        <v>7013100</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6698,9 +6711,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6715,22 +6738,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120481907</v>
+        <v>120476175</v>
       </c>
       <c r="B55" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6743,34 +6766,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574773</v>
+        <v>574595</v>
       </c>
       <c r="R55" t="n">
-        <v>7013002</v>
+        <v>7013170</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6829,7 +6857,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120478597</v>
+        <v>120476584</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6869,10 +6897,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574914</v>
+        <v>574621</v>
       </c>
       <c r="R56" t="n">
-        <v>7013012</v>
+        <v>7013153</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6904,7 +6932,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6914,12 +6942,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6934,22 +6962,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120475714</v>
+        <v>120478002</v>
       </c>
       <c r="B57" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6958,38 +6986,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574557</v>
+        <v>574766</v>
       </c>
       <c r="R57" t="n">
-        <v>7013335</v>
+        <v>7012936</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7021,7 +7049,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7031,7 +7059,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7046,22 +7074,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120476584</v>
+        <v>120482763</v>
       </c>
       <c r="B58" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7074,21 +7102,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7098,10 +7126,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574621</v>
+        <v>575128</v>
       </c>
       <c r="R58" t="n">
-        <v>7013153</v>
+        <v>7012966</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7133,7 +7161,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7143,12 +7171,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7163,22 +7186,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120478207</v>
+        <v>120475740</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7191,42 +7214,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574661</v>
+        <v>574557</v>
       </c>
       <c r="R59" t="n">
-        <v>7013070</v>
+        <v>7013323</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7253,14 +7271,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7275,22 +7298,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120482763</v>
+        <v>120478232</v>
       </c>
       <c r="B60" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7299,25 +7322,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7327,10 +7350,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575128</v>
+        <v>574911</v>
       </c>
       <c r="R60" t="n">
-        <v>7012966</v>
+        <v>7013004</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7362,7 +7385,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7372,7 +7395,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7387,22 +7410,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120483427</v>
+        <v>120475714</v>
       </c>
       <c r="B61" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7411,43 +7434,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574893</v>
+        <v>574557</v>
       </c>
       <c r="R61" t="n">
-        <v>7013053</v>
+        <v>7013335</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7479,7 +7497,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7489,7 +7507,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7516,10 +7534,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120479683</v>
+        <v>120482920</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7532,39 +7550,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574981</v>
+        <v>575178</v>
       </c>
       <c r="R62" t="n">
-        <v>7012954</v>
+        <v>7012946</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7596,7 +7609,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7606,7 +7619,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7621,22 +7634,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120478039</v>
+        <v>120479582</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7649,39 +7662,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574700</v>
+        <v>574748</v>
       </c>
       <c r="R63" t="n">
-        <v>7013066</v>
+        <v>7013002</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7714,11 +7722,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7745,10 +7748,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120483119</v>
+        <v>120482642</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7761,21 +7764,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7785,10 +7788,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575114</v>
+        <v>575068</v>
       </c>
       <c r="R64" t="n">
-        <v>7012928</v>
+        <v>7013015</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7820,7 +7823,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7830,12 +7833,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7862,10 +7860,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120483075</v>
+        <v>120477828</v>
       </c>
       <c r="B65" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7878,21 +7876,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7902,10 +7900,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>575155</v>
+        <v>574688</v>
       </c>
       <c r="R65" t="n">
-        <v>7012893</v>
+        <v>7012983</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7937,7 +7935,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7947,12 +7945,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7967,22 +7960,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120482660</v>
+        <v>120477975</v>
       </c>
       <c r="B66" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7995,21 +7988,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8019,13 +8012,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574772</v>
+        <v>574700</v>
       </c>
       <c r="R66" t="n">
-        <v>7012971</v>
+        <v>7012966</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8052,9 +8045,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8069,22 +8077,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120478069</v>
+        <v>120475858</v>
       </c>
       <c r="B67" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8097,34 +8105,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574798</v>
+        <v>574570</v>
       </c>
       <c r="R67" t="n">
-        <v>7012940</v>
+        <v>7013265</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8156,7 +8164,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8166,7 +8174,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8181,22 +8194,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120478239</v>
+        <v>120476955</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>5169</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8205,38 +8218,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574847</v>
+        <v>574526</v>
       </c>
       <c r="R68" t="n">
-        <v>7013095</v>
+        <v>7013059</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8268,7 +8286,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8278,7 +8296,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8293,22 +8311,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120483114</v>
+        <v>120478274</v>
       </c>
       <c r="B69" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8317,41 +8335,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574704</v>
+        <v>574884</v>
       </c>
       <c r="R69" t="n">
-        <v>7013264</v>
+        <v>7013094</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8378,9 +8396,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8395,22 +8423,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120479001</v>
+        <v>120479650</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8419,25 +8447,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8447,10 +8475,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574918</v>
+        <v>575030</v>
       </c>
       <c r="R70" t="n">
-        <v>7012974</v>
+        <v>7012916</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8482,7 +8510,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8492,7 +8520,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8519,7 +8547,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120483518</v>
+        <v>120483118</v>
       </c>
       <c r="B71" t="n">
         <v>78542</v>
@@ -8555,17 +8583,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574570</v>
+        <v>575141</v>
       </c>
       <c r="R71" t="n">
-        <v>7013321</v>
+        <v>7012926</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8592,9 +8620,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8609,22 +8647,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120479013</v>
+        <v>120482863</v>
       </c>
       <c r="B72" t="n">
-        <v>57336</v>
+        <v>90527</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8637,39 +8675,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574894</v>
+        <v>575173</v>
       </c>
       <c r="R72" t="n">
-        <v>7013031</v>
+        <v>7012956</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8701,7 +8734,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8711,7 +8744,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8726,22 +8759,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120478128</v>
+        <v>120479509</v>
       </c>
       <c r="B73" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8750,25 +8783,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8778,13 +8811,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574815</v>
+        <v>574766</v>
       </c>
       <c r="R73" t="n">
-        <v>7012976</v>
+        <v>7013045</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8811,19 +8844,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8838,22 +8861,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120482317</v>
+        <v>120483141</v>
       </c>
       <c r="B74" t="n">
-        <v>96891</v>
+        <v>96885</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8866,16 +8889,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8886,14 +8909,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574773</v>
+        <v>574645</v>
       </c>
       <c r="R74" t="n">
-        <v>7013002</v>
+        <v>7013293</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8952,10 +8975,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120478036</v>
+        <v>120482864</v>
       </c>
       <c r="B75" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8964,25 +8987,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8992,13 +9015,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574778</v>
+        <v>574700</v>
       </c>
       <c r="R75" t="n">
-        <v>7012962</v>
+        <v>7013007</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9025,19 +9048,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9052,22 +9065,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120476784</v>
+        <v>120478200</v>
       </c>
       <c r="B76" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9076,25 +9089,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9104,13 +9117,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574525</v>
+        <v>574704</v>
       </c>
       <c r="R76" t="n">
-        <v>7013029</v>
+        <v>7013044</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9137,19 +9150,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9164,22 +9167,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120475397</v>
+        <v>120478767</v>
       </c>
       <c r="B77" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9192,37 +9195,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574558</v>
+        <v>574761</v>
       </c>
       <c r="R77" t="n">
-        <v>7013337</v>
+        <v>7013035</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9249,19 +9252,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9276,22 +9269,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120482920</v>
+        <v>120477524</v>
       </c>
       <c r="B78" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9304,21 +9297,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9328,13 +9321,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>575178</v>
+        <v>574538</v>
       </c>
       <c r="R78" t="n">
-        <v>7012946</v>
+        <v>7013034</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9363,7 +9356,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9373,7 +9366,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9388,22 +9381,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120476601</v>
+        <v>120481387</v>
       </c>
       <c r="B79" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9416,16 +9409,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9434,19 +9427,24 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>574573</v>
+        <v>574762</v>
       </c>
       <c r="R79" t="n">
-        <v>7013042</v>
+        <v>7012995</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9473,24 +9471,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9505,22 +9488,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120478035</v>
+        <v>120477787</v>
       </c>
       <c r="B80" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9529,35 +9512,31 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9566,10 +9545,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>574785</v>
+        <v>574673</v>
       </c>
       <c r="R80" t="n">
-        <v>7013205</v>
+        <v>7013097</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9601,7 +9580,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9611,7 +9590,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9638,10 +9617,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120475677</v>
+        <v>120475921</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9654,34 +9633,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>574559</v>
+        <v>574585</v>
       </c>
       <c r="R81" t="n">
-        <v>7013337</v>
+        <v>7013246</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9713,7 +9697,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9723,7 +9707,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9738,22 +9722,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120478226</v>
+        <v>120483075</v>
       </c>
       <c r="B82" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9766,21 +9750,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9790,10 +9774,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>574839</v>
+        <v>575155</v>
       </c>
       <c r="R82" t="n">
-        <v>7013100</v>
+        <v>7012893</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9825,7 +9809,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9835,7 +9819,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9862,10 +9851,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120482757</v>
+        <v>120482523</v>
       </c>
       <c r="B83" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9878,42 +9867,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>575161</v>
+        <v>574779</v>
       </c>
       <c r="R83" t="n">
-        <v>7012940</v>
+        <v>7012971</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9940,19 +9924,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9967,22 +9941,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120476454</v>
+        <v>120478878</v>
       </c>
       <c r="B84" t="n">
-        <v>86895</v>
+        <v>90864</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9995,34 +9969,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>574577</v>
+        <v>574759</v>
       </c>
       <c r="R84" t="n">
-        <v>7013274</v>
+        <v>7013028</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -10081,10 +10055,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120477715</v>
+        <v>120482987</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>90781</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10093,25 +10067,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1106</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10121,10 +10095,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>574645</v>
+        <v>575188</v>
       </c>
       <c r="R85" t="n">
-        <v>7013075</v>
+        <v>7012937</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10156,7 +10130,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10166,7 +10140,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10193,10 +10167,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120482523</v>
+        <v>120476831</v>
       </c>
       <c r="B86" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10209,21 +10183,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10233,13 +10207,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>574779</v>
+        <v>574561</v>
       </c>
       <c r="R86" t="n">
-        <v>7012971</v>
+        <v>7013070</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10266,9 +10240,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10283,22 +10267,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120482863</v>
+        <v>120483505</v>
       </c>
       <c r="B87" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10311,37 +10295,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>575173</v>
+        <v>574552</v>
       </c>
       <c r="R87" t="n">
-        <v>7012956</v>
+        <v>7013338</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10368,19 +10352,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10395,22 +10369,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120483166</v>
+        <v>120475677</v>
       </c>
       <c r="B88" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10423,21 +10397,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10447,13 +10421,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>574637</v>
+        <v>574559</v>
       </c>
       <c r="R88" t="n">
-        <v>7013303</v>
+        <v>7013337</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10480,9 +10454,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10497,22 +10481,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120483636</v>
+        <v>120483155</v>
       </c>
       <c r="B89" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10525,21 +10509,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10549,10 +10533,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>574559</v>
+        <v>574641</v>
       </c>
       <c r="R89" t="n">
-        <v>7013332</v>
+        <v>7013295</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -10611,10 +10595,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120481387</v>
+        <v>120480946</v>
       </c>
       <c r="B90" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10627,42 +10611,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>574762</v>
+        <v>575006</v>
       </c>
       <c r="R90" t="n">
-        <v>7012995</v>
+        <v>7012970</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10689,9 +10668,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn och gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10706,22 +10700,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120483094</v>
+        <v>120477938</v>
       </c>
       <c r="B91" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10730,25 +10724,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10758,10 +10752,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>575168</v>
+        <v>574747</v>
       </c>
       <c r="R91" t="n">
-        <v>7012937</v>
+        <v>7013128</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10793,7 +10787,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10803,7 +10797,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10818,22 +10817,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120483116</v>
+        <v>120477974</v>
       </c>
       <c r="B92" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10846,37 +10845,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>574701</v>
+        <v>574762</v>
       </c>
       <c r="R92" t="n">
-        <v>7013268</v>
+        <v>7013134</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10903,9 +10907,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10920,22 +10934,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120483141</v>
+        <v>120478207</v>
       </c>
       <c r="B93" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10944,38 +10958,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>574645</v>
+        <v>574661</v>
       </c>
       <c r="R93" t="n">
-        <v>7013293</v>
+        <v>7013070</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -11008,6 +11027,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11034,10 +11058,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120480946</v>
+        <v>120477886</v>
       </c>
       <c r="B94" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11050,34 +11074,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>575006</v>
+        <v>574719</v>
       </c>
       <c r="R94" t="n">
-        <v>7012970</v>
+        <v>7013107</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11109,7 +11138,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11119,12 +11148,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Lunglav på rönn och gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11151,10 +11180,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120483136</v>
+        <v>120479683</v>
       </c>
       <c r="B95" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11167,34 +11196,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>575076</v>
+        <v>574981</v>
       </c>
       <c r="R95" t="n">
-        <v>7012962</v>
+        <v>7012954</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11226,7 +11260,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11236,7 +11270,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11263,10 +11297,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120477828</v>
+        <v>120476541</v>
       </c>
       <c r="B96" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11279,34 +11313,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>574688</v>
+        <v>574609</v>
       </c>
       <c r="R96" t="n">
-        <v>7012983</v>
+        <v>7013099</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11338,7 +11377,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11348,7 +11387,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11363,19 +11407,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120477886</v>
+        <v>120477678</v>
       </c>
       <c r="B97" t="n">
         <v>57320</v>
@@ -11409,21 +11453,16 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>574719</v>
+        <v>574542</v>
       </c>
       <c r="R97" t="n">
-        <v>7013107</v>
+        <v>7013136</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11455,7 +11494,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11465,12 +11504,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11485,22 +11524,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120476791</v>
+        <v>120477989</v>
       </c>
       <c r="B98" t="n">
-        <v>57320</v>
+        <v>79527</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11509,25 +11548,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11537,13 +11576,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>574551</v>
+        <v>574700</v>
       </c>
       <c r="R98" t="n">
-        <v>7013059</v>
+        <v>7013142</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11570,24 +11609,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11602,22 +11626,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120478002</v>
+        <v>120482861</v>
       </c>
       <c r="B99" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11630,34 +11654,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>574766</v>
+        <v>575181</v>
       </c>
       <c r="R99" t="n">
-        <v>7012936</v>
+        <v>7012951</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11689,7 +11718,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11699,7 +11728,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11714,19 +11743,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120482873</v>
+        <v>120476914</v>
       </c>
       <c r="B100" t="n">
         <v>79623</v>
@@ -11766,10 +11795,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>575178</v>
+        <v>574547</v>
       </c>
       <c r="R100" t="n">
-        <v>7012952</v>
+        <v>7013045</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11801,7 +11830,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11811,7 +11840,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11826,22 +11855,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120483118</v>
+        <v>120483136</v>
       </c>
       <c r="B101" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11854,21 +11883,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11878,10 +11907,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>575141</v>
+        <v>575076</v>
       </c>
       <c r="R101" t="n">
-        <v>7012926</v>
+        <v>7012962</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11913,7 +11942,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11923,7 +11952,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11938,22 +11967,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120478253</v>
+        <v>120477619</v>
       </c>
       <c r="B102" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11966,21 +11995,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11990,10 +12019,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>574917</v>
+        <v>574657</v>
       </c>
       <c r="R102" t="n">
-        <v>7013009</v>
+        <v>7013067</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12025,7 +12054,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12035,7 +12064,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12062,10 +12091,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120482540</v>
+        <v>120478431</v>
       </c>
       <c r="B103" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12078,21 +12107,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12102,13 +12131,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>575091</v>
+        <v>574745</v>
       </c>
       <c r="R103" t="n">
-        <v>7012974</v>
+        <v>7013030</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12135,19 +12164,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>15:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12162,22 +12181,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120478428</v>
+        <v>120478253</v>
       </c>
       <c r="B104" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12190,21 +12209,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12214,10 +12233,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>574922</v>
+        <v>574917</v>
       </c>
       <c r="R104" t="n">
-        <v>7012993</v>
+        <v>7013009</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12249,7 +12268,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12259,7 +12278,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12286,10 +12305,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120483155</v>
+        <v>120477573</v>
       </c>
       <c r="B105" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12302,37 +12321,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>574641</v>
+        <v>574666</v>
       </c>
       <c r="R105" t="n">
-        <v>7013295</v>
+        <v>7013074</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12359,9 +12378,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12376,22 +12410,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120477951</v>
+        <v>120477743</v>
       </c>
       <c r="B106" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12400,20 +12434,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12421,31 +12455,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>574667</v>
+        <v>574597</v>
       </c>
       <c r="R106" t="n">
-        <v>7012956</v>
+        <v>7013088</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12477,7 +12497,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12487,7 +12507,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12502,22 +12527,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120482434</v>
+        <v>120479001</v>
       </c>
       <c r="B107" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12530,21 +12555,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12554,13 +12579,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>574754</v>
+        <v>574918</v>
       </c>
       <c r="R107" t="n">
-        <v>7012970</v>
+        <v>7012974</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12587,9 +12612,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12604,22 +12639,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120478878</v>
+        <v>120479013</v>
       </c>
       <c r="B108" t="n">
-        <v>90864</v>
+        <v>57336</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12632,37 +12667,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>574759</v>
+        <v>574894</v>
       </c>
       <c r="R108" t="n">
-        <v>7013028</v>
+        <v>7013031</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12689,9 +12729,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12706,22 +12756,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120479582</v>
+        <v>120476454</v>
       </c>
       <c r="B109" t="n">
-        <v>90580</v>
+        <v>86895</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12734,34 +12784,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>574748</v>
+        <v>574577</v>
       </c>
       <c r="R109" t="n">
-        <v>7013002</v>
+        <v>7013274</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12820,10 +12870,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120477974</v>
+        <v>120483636</v>
       </c>
       <c r="B110" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12836,42 +12886,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>574762</v>
+        <v>574559</v>
       </c>
       <c r="R110" t="n">
-        <v>7013134</v>
+        <v>7013332</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12898,19 +12943,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>14:41</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12925,22 +12960,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120478200</v>
+        <v>120483092</v>
       </c>
       <c r="B111" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12949,25 +12984,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12977,13 +13012,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>574704</v>
+        <v>575166</v>
       </c>
       <c r="R111" t="n">
-        <v>7013044</v>
+        <v>7012887</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13010,9 +13045,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13027,22 +13077,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120479650</v>
+        <v>120478039</v>
       </c>
       <c r="B112" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13051,41 +13101,46 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>575030</v>
+        <v>574700</v>
       </c>
       <c r="R112" t="n">
-        <v>7012916</v>
+        <v>7013066</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13112,19 +13167,14 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13139,22 +13189,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120475679</v>
+        <v>120483116</v>
       </c>
       <c r="B113" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13163,25 +13213,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13191,10 +13241,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>574558</v>
+        <v>574701</v>
       </c>
       <c r="R113" t="n">
-        <v>7013348</v>
+        <v>7013268</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -13253,10 +13303,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120478210</v>
+        <v>120482660</v>
       </c>
       <c r="B114" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13269,21 +13319,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13293,13 +13343,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>574881</v>
+        <v>574772</v>
       </c>
       <c r="R114" t="n">
-        <v>7012991</v>
+        <v>7012971</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13326,19 +13376,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13353,22 +13393,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120477400</v>
+        <v>120476784</v>
       </c>
       <c r="B115" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13377,42 +13417,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>574552</v>
+        <v>574525</v>
       </c>
       <c r="R115" t="n">
-        <v>7013013</v>
+        <v>7013029</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13444,7 +13480,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13454,7 +13490,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13469,22 +13505,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120483092</v>
+        <v>120479575</v>
       </c>
       <c r="B116" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13497,21 +13533,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13521,10 +13557,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>575166</v>
+        <v>575015</v>
       </c>
       <c r="R116" t="n">
-        <v>7012887</v>
+        <v>7012924</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13556,7 +13592,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13566,12 +13602,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13586,22 +13617,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120476542</v>
+        <v>120478974</v>
       </c>
       <c r="B117" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13614,21 +13645,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13638,13 +13669,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>574624</v>
+        <v>574753</v>
       </c>
       <c r="R117" t="n">
-        <v>7013126</v>
+        <v>7013026</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13671,24 +13702,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13703,22 +13719,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120475858</v>
+        <v>120481907</v>
       </c>
       <c r="B118" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13731,37 +13747,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>574570</v>
+        <v>574773</v>
       </c>
       <c r="R118" t="n">
-        <v>7013265</v>
+        <v>7013002</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13788,24 +13804,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13820,22 +13821,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120478431</v>
+        <v>120478091</v>
       </c>
       <c r="B119" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13848,37 +13849,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>574745</v>
+        <v>574814</v>
       </c>
       <c r="R119" t="n">
-        <v>7013030</v>
+        <v>7012964</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13905,9 +13911,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13922,22 +13938,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120478974</v>
+        <v>120483114</v>
       </c>
       <c r="B120" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13950,34 +13966,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>574753</v>
+        <v>574704</v>
       </c>
       <c r="R120" t="n">
-        <v>7013026</v>
+        <v>7013264</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -14036,7 +14052,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120475740</v>
+        <v>120477985</v>
       </c>
       <c r="B121" t="n">
         <v>79623</v>
@@ -14072,17 +14088,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>574557</v>
+        <v>574701</v>
       </c>
       <c r="R121" t="n">
-        <v>7013323</v>
+        <v>7013141</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14109,19 +14125,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14136,19 +14142,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120476091</v>
+        <v>120478245</v>
       </c>
       <c r="B122" t="n">
         <v>79623</v>
@@ -14184,14 +14190,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>574596</v>
+        <v>574661</v>
       </c>
       <c r="R122" t="n">
-        <v>7013168</v>
+        <v>7013070</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -14250,10 +14256,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120482642</v>
+        <v>120483518</v>
       </c>
       <c r="B123" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14266,37 +14272,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>575068</v>
+        <v>574570</v>
       </c>
       <c r="R123" t="n">
-        <v>7013015</v>
+        <v>7013321</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14323,19 +14329,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14350,22 +14346,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120477919</v>
+        <v>120478035</v>
       </c>
       <c r="B124" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14374,38 +14370,47 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574682</v>
+        <v>574785</v>
       </c>
       <c r="R124" t="n">
-        <v>7012947</v>
+        <v>7013205</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14437,7 +14442,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14447,12 +14452,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14467,12 +14467,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -4526,10 +4526,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120477951</v>
+        <v>120480588</v>
       </c>
       <c r="B35" t="n">
-        <v>57431</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4538,52 +4538,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574667</v>
+        <v>575008</v>
       </c>
       <c r="R35" t="n">
-        <v>7012956</v>
+        <v>7012970</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4615,7 +4601,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4625,7 +4611,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4640,19 +4626,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120480588</v>
+        <v>120478900</v>
       </c>
       <c r="B36" t="n">
         <v>79623</v>
@@ -4692,10 +4678,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575008</v>
+        <v>574883</v>
       </c>
       <c r="R36" t="n">
-        <v>7012970</v>
+        <v>7013078</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4727,7 +4713,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4737,7 +4723,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4764,10 +4750,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120478900</v>
+        <v>120477715</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4780,21 +4766,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4804,10 +4790,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574883</v>
+        <v>574645</v>
       </c>
       <c r="R37" t="n">
-        <v>7013078</v>
+        <v>7013075</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4839,7 +4825,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4849,7 +4835,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4864,22 +4850,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120477715</v>
+        <v>120475719</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4892,34 +4878,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574645</v>
+        <v>574557</v>
       </c>
       <c r="R38" t="n">
-        <v>7013075</v>
+        <v>7013335</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4951,7 +4942,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4961,7 +4952,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4976,22 +4967,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120482873</v>
+        <v>120475741</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>5169</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5000,38 +4991,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575178</v>
+        <v>574556</v>
       </c>
       <c r="R39" t="n">
-        <v>7012952</v>
+        <v>7013327</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5063,7 +5059,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5073,7 +5069,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5088,22 +5084,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120475719</v>
+        <v>120477951</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>57431</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5112,20 +5108,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5133,22 +5129,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574557</v>
+        <v>574667</v>
       </c>
       <c r="R40" t="n">
-        <v>7013335</v>
+        <v>7012956</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5180,7 +5185,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5190,7 +5195,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5205,22 +5210,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120475741</v>
+        <v>120482873</v>
       </c>
       <c r="B41" t="n">
-        <v>5169</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5229,43 +5234,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574556</v>
+        <v>575178</v>
       </c>
       <c r="R41" t="n">
-        <v>7013327</v>
+        <v>7012952</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5322,12 +5322,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120477401</v>
+        <v>120476091</v>
       </c>
       <c r="B49" t="n">
-        <v>90781</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6120,41 +6120,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574646</v>
+        <v>574596</v>
       </c>
       <c r="R49" t="n">
-        <v>7013031</v>
+        <v>7013168</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6181,19 +6181,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6208,22 +6198,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120483166</v>
+        <v>120477401</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>90781</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,41 +6222,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>1106</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574637</v>
+        <v>574646</v>
       </c>
       <c r="R50" t="n">
-        <v>7013303</v>
+        <v>7013031</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6293,9 +6283,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6310,22 +6310,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120476091</v>
+        <v>120483166</v>
       </c>
       <c r="B51" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574596</v>
+        <v>574637</v>
       </c>
       <c r="R51" t="n">
-        <v>7013168</v>
+        <v>7013303</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7086,10 +7086,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120482763</v>
+        <v>120475740</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7102,34 +7102,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575128</v>
+        <v>574557</v>
       </c>
       <c r="R58" t="n">
-        <v>7012966</v>
+        <v>7013323</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7198,10 +7198,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120475740</v>
+        <v>120478232</v>
       </c>
       <c r="B59" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7210,38 +7210,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574557</v>
+        <v>574911</v>
       </c>
       <c r="R59" t="n">
-        <v>7013323</v>
+        <v>7013004</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7298,22 +7298,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120478232</v>
+        <v>120482763</v>
       </c>
       <c r="B60" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7322,25 +7322,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574911</v>
+        <v>575128</v>
       </c>
       <c r="R60" t="n">
-        <v>7013004</v>
+        <v>7012966</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7410,22 +7410,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120475714</v>
+        <v>120476955</v>
       </c>
       <c r="B61" t="n">
-        <v>90545</v>
+        <v>5169</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7438,34 +7438,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574557</v>
+        <v>574526</v>
       </c>
       <c r="R61" t="n">
-        <v>7013335</v>
+        <v>7013059</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7497,7 +7502,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7507,7 +7512,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7522,22 +7527,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120482920</v>
+        <v>120475714</v>
       </c>
       <c r="B62" t="n">
-        <v>79624</v>
+        <v>90545</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7546,38 +7551,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575178</v>
+        <v>574557</v>
       </c>
       <c r="R62" t="n">
-        <v>7012946</v>
+        <v>7013335</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7609,7 +7614,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7619,7 +7624,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7634,22 +7639,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120479582</v>
+        <v>120482920</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7662,21 +7667,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7686,13 +7691,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574748</v>
+        <v>575178</v>
       </c>
       <c r="R63" t="n">
-        <v>7013002</v>
+        <v>7012946</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7719,9 +7724,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7736,22 +7751,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120482642</v>
+        <v>120479582</v>
       </c>
       <c r="B64" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7764,21 +7779,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7788,13 +7803,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575068</v>
+        <v>574748</v>
       </c>
       <c r="R64" t="n">
-        <v>7013015</v>
+        <v>7013002</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7821,19 +7836,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7848,22 +7853,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120477828</v>
+        <v>120482642</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7876,21 +7881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7900,10 +7905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574688</v>
+        <v>575068</v>
       </c>
       <c r="R65" t="n">
-        <v>7012983</v>
+        <v>7013015</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7935,7 +7940,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7945,7 +7950,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7960,22 +7965,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120477975</v>
+        <v>120477828</v>
       </c>
       <c r="B66" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7988,21 +7993,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8012,10 +8017,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574700</v>
+        <v>574688</v>
       </c>
       <c r="R66" t="n">
-        <v>7012966</v>
+        <v>7012983</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8047,7 +8052,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8057,12 +8062,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8089,7 +8089,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120475858</v>
+        <v>120477975</v>
       </c>
       <c r="B67" t="n">
         <v>57320</v>
@@ -8125,14 +8125,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574570</v>
+        <v>574700</v>
       </c>
       <c r="R67" t="n">
-        <v>7013265</v>
+        <v>7012966</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8194,22 +8194,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120476955</v>
+        <v>120475858</v>
       </c>
       <c r="B68" t="n">
-        <v>5169</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8218,43 +8218,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574526</v>
+        <v>574570</v>
       </c>
       <c r="R68" t="n">
-        <v>7013059</v>
+        <v>7013265</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8286,7 +8281,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8296,7 +8291,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8311,12 +8311,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8975,10 +8975,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120482864</v>
+        <v>120478767</v>
       </c>
       <c r="B75" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574700</v>
+        <v>574761</v>
       </c>
       <c r="R75" t="n">
-        <v>7013007</v>
+        <v>7013035</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -9179,10 +9179,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120478767</v>
+        <v>120482864</v>
       </c>
       <c r="B77" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9195,21 +9195,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574761</v>
+        <v>574700</v>
       </c>
       <c r="R77" t="n">
-        <v>7013035</v>
+        <v>7013007</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -9281,10 +9281,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120477524</v>
+        <v>120482523</v>
       </c>
       <c r="B78" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9321,13 +9321,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>574538</v>
+        <v>574779</v>
       </c>
       <c r="R78" t="n">
-        <v>7013034</v>
+        <v>7012971</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9354,19 +9354,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9381,22 +9371,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120481387</v>
+        <v>120478878</v>
       </c>
       <c r="B79" t="n">
-        <v>57336</v>
+        <v>90864</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9409,39 +9399,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>574762</v>
+        <v>574759</v>
       </c>
       <c r="R79" t="n">
-        <v>7012995</v>
+        <v>7013028</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9500,10 +9485,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120477787</v>
+        <v>120477524</v>
       </c>
       <c r="B80" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9516,42 +9501,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>574673</v>
+        <v>574538</v>
       </c>
       <c r="R80" t="n">
-        <v>7013097</v>
+        <v>7013034</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9580,7 +9560,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9590,7 +9570,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9605,22 +9585,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120475921</v>
+        <v>120481387</v>
       </c>
       <c r="B81" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9633,16 +9613,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9653,22 +9633,22 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>574585</v>
+        <v>574762</v>
       </c>
       <c r="R81" t="n">
-        <v>7013246</v>
+        <v>7012995</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9695,19 +9675,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9722,22 +9692,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120483075</v>
+        <v>120477787</v>
       </c>
       <c r="B82" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9750,16 +9720,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9768,16 +9738,21 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>575155</v>
+        <v>574673</v>
       </c>
       <c r="R82" t="n">
-        <v>7012893</v>
+        <v>7013097</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9809,7 +9784,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9819,12 +9794,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9851,10 +9821,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120482523</v>
+        <v>120475921</v>
       </c>
       <c r="B83" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9867,37 +9837,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>574779</v>
+        <v>574585</v>
       </c>
       <c r="R83" t="n">
-        <v>7012971</v>
+        <v>7013246</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9924,9 +9899,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9941,22 +9926,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120478878</v>
+        <v>120483075</v>
       </c>
       <c r="B84" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9969,21 +9954,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9993,13 +9978,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>574759</v>
+        <v>575155</v>
       </c>
       <c r="R84" t="n">
-        <v>7013028</v>
+        <v>7012893</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10026,9 +10011,24 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10043,12 +10043,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120478431</v>
+        <v>120479001</v>
       </c>
       <c r="B103" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12107,21 +12107,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12131,13 +12131,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>574745</v>
+        <v>574918</v>
       </c>
       <c r="R103" t="n">
-        <v>7013030</v>
+        <v>7012974</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12164,9 +12164,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12181,22 +12191,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120478253</v>
+        <v>120479013</v>
       </c>
       <c r="B104" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12209,34 +12219,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>574917</v>
+        <v>574894</v>
       </c>
       <c r="R104" t="n">
-        <v>7013009</v>
+        <v>7013031</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12268,7 +12283,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12278,7 +12293,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12293,12 +12308,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12539,10 +12554,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120479001</v>
+        <v>120478431</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12555,21 +12570,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12579,13 +12594,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>574918</v>
+        <v>574745</v>
       </c>
       <c r="R107" t="n">
-        <v>7012974</v>
+        <v>7013030</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12612,19 +12627,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:31</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12639,22 +12644,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120479013</v>
+        <v>120478253</v>
       </c>
       <c r="B108" t="n">
-        <v>57336</v>
+        <v>82321</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12667,39 +12672,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>574894</v>
+        <v>574917</v>
       </c>
       <c r="R108" t="n">
-        <v>7013031</v>
+        <v>7013009</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12756,12 +12756,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13629,10 +13629,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120478974</v>
+        <v>120483114</v>
       </c>
       <c r="B117" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13645,34 +13645,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflon, Prästflon, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>574753</v>
+        <v>574704</v>
       </c>
       <c r="R117" t="n">
-        <v>7013026</v>
+        <v>7013264</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13731,10 +13731,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120481907</v>
+        <v>120477985</v>
       </c>
       <c r="B118" t="n">
-        <v>82321</v>
+        <v>79623</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13747,21 +13747,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13771,10 +13771,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>574773</v>
+        <v>574701</v>
       </c>
       <c r="R118" t="n">
-        <v>7013002</v>
+        <v>7013141</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13833,10 +13833,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120478091</v>
+        <v>120478245</v>
       </c>
       <c r="B119" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13849,42 +13849,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>574814</v>
+        <v>574661</v>
       </c>
       <c r="R119" t="n">
-        <v>7012964</v>
+        <v>7013070</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13911,19 +13906,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13938,22 +13923,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120483114</v>
+        <v>120483518</v>
       </c>
       <c r="B120" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13966,21 +13951,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13990,10 +13975,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>574704</v>
+        <v>574570</v>
       </c>
       <c r="R120" t="n">
-        <v>7013264</v>
+        <v>7013321</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -14052,10 +14037,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120477985</v>
+        <v>120478974</v>
       </c>
       <c r="B121" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14068,21 +14053,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14092,10 +14077,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>574701</v>
+        <v>574753</v>
       </c>
       <c r="R121" t="n">
-        <v>7013141</v>
+        <v>7013026</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -14154,10 +14139,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120478245</v>
+        <v>120481907</v>
       </c>
       <c r="B122" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14170,21 +14155,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14194,10 +14179,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>574661</v>
+        <v>574773</v>
       </c>
       <c r="R122" t="n">
-        <v>7013070</v>
+        <v>7013002</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -14256,10 +14241,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120483518</v>
+        <v>120478091</v>
       </c>
       <c r="B123" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14272,37 +14257,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Prästflon, Prästflon, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>574570</v>
+        <v>574814</v>
       </c>
       <c r="R123" t="n">
-        <v>7013321</v>
+        <v>7012964</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14329,9 +14319,19 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14346,12 +14346,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14367,10 +14367,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121217724</v>
+        <v>120758611</v>
       </c>
       <c r="B124" t="n">
-        <v>90687</v>
+        <v>79682</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14383,21 +14383,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14407,10 +14407,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574579</v>
+        <v>574659</v>
       </c>
       <c r="R124" t="n">
-        <v>7013036</v>
+        <v>7012911</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121217742</v>
+        <v>121217724</v>
       </c>
       <c r="B125" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14485,21 +14485,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>575004</v>
+        <v>574579</v>
       </c>
       <c r="R125" t="n">
-        <v>7013092</v>
+        <v>7013036</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120758611</v>
+        <v>121217764</v>
       </c>
       <c r="B126" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>574659</v>
+        <v>574587</v>
       </c>
       <c r="R126" t="n">
-        <v>7012911</v>
+        <v>7013277</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217763</v>
+        <v>121217742</v>
       </c>
       <c r="B127" t="n">
-        <v>79679</v>
+        <v>57351</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>574617</v>
+        <v>575004</v>
       </c>
       <c r="R127" t="n">
-        <v>7012907</v>
+        <v>7013092</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120758613</v>
+        <v>120758610</v>
       </c>
       <c r="B128" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>574587</v>
+        <v>574798</v>
       </c>
       <c r="R128" t="n">
-        <v>7013277</v>
+        <v>7012916</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121217729</v>
+        <v>121217723</v>
       </c>
       <c r="B129" t="n">
-        <v>79680</v>
+        <v>90697</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>574659</v>
+        <v>574662</v>
       </c>
       <c r="R129" t="n">
-        <v>7012913</v>
+        <v>7012905</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121217761</v>
+        <v>120758612</v>
       </c>
       <c r="B130" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>574798</v>
+        <v>574617</v>
       </c>
       <c r="R130" t="n">
-        <v>7012916</v>
+        <v>7012907</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121217723</v>
+        <v>121217729</v>
       </c>
       <c r="B131" t="n">
-        <v>90687</v>
+        <v>79683</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15097,21 +15097,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>574662</v>
+        <v>574659</v>
       </c>
       <c r="R131" t="n">
-        <v>7012905</v>
+        <v>7012913</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14367,7 +14367,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120758611</v>
+        <v>121217761</v>
       </c>
       <c r="B124" t="n">
         <v>79682</v>
@@ -14407,10 +14407,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574659</v>
+        <v>574798</v>
       </c>
       <c r="R124" t="n">
-        <v>7012911</v>
+        <v>7012916</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121217724</v>
+        <v>121217763</v>
       </c>
       <c r="B125" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14485,21 +14485,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>574579</v>
+        <v>574617</v>
       </c>
       <c r="R125" t="n">
-        <v>7013036</v>
+        <v>7012907</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -14571,7 +14571,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121217764</v>
+        <v>120758613</v>
       </c>
       <c r="B126" t="n">
         <v>79682</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217742</v>
+        <v>121217724</v>
       </c>
       <c r="B127" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>575004</v>
+        <v>574579</v>
       </c>
       <c r="R127" t="n">
-        <v>7013092</v>
+        <v>7013036</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14775,7 +14775,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120758610</v>
+        <v>121217762</v>
       </c>
       <c r="B128" t="n">
         <v>79682</v>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>574798</v>
+        <v>574659</v>
       </c>
       <c r="R128" t="n">
-        <v>7012916</v>
+        <v>7012911</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121217723</v>
+        <v>121217742</v>
       </c>
       <c r="B129" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>574662</v>
+        <v>575004</v>
       </c>
       <c r="R129" t="n">
-        <v>7012905</v>
+        <v>7013092</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120758612</v>
+        <v>121217723</v>
       </c>
       <c r="B130" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14995,21 +14995,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>574617</v>
+        <v>574662</v>
       </c>
       <c r="R130" t="n">
-        <v>7012907</v>
+        <v>7012905</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AY142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14367,10 +14367,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121217761</v>
+        <v>121217729</v>
       </c>
       <c r="B124" t="n">
-        <v>79682</v>
+        <v>79686</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14383,21 +14383,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14407,10 +14407,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574798</v>
+        <v>574659</v>
       </c>
       <c r="R124" t="n">
-        <v>7012916</v>
+        <v>7012913</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -14472,7 +14472,7 @@
         <v>121217763</v>
       </c>
       <c r="B125" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120758613</v>
+        <v>121217724</v>
       </c>
       <c r="B126" t="n">
-        <v>79682</v>
+        <v>90709</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>574587</v>
+        <v>574579</v>
       </c>
       <c r="R126" t="n">
-        <v>7013277</v>
+        <v>7013036</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217724</v>
+        <v>121217764</v>
       </c>
       <c r="B127" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>574579</v>
+        <v>574587</v>
       </c>
       <c r="R127" t="n">
-        <v>7013036</v>
+        <v>7013277</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121217762</v>
+        <v>121217742</v>
       </c>
       <c r="B128" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14791,21 +14791,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>574659</v>
+        <v>575004</v>
       </c>
       <c r="R128" t="n">
-        <v>7012911</v>
+        <v>7013092</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121217742</v>
+        <v>121217761</v>
       </c>
       <c r="B129" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>575004</v>
+        <v>574798</v>
       </c>
       <c r="R129" t="n">
-        <v>7013092</v>
+        <v>7012916</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121217723</v>
+        <v>121217762</v>
       </c>
       <c r="B130" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14995,21 +14995,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>574662</v>
+        <v>574659</v>
       </c>
       <c r="R130" t="n">
-        <v>7012905</v>
+        <v>7012911</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121217729</v>
+        <v>121217723</v>
       </c>
       <c r="B131" t="n">
-        <v>79683</v>
+        <v>90709</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15097,21 +15097,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>574659</v>
+        <v>574662</v>
       </c>
       <c r="R131" t="n">
-        <v>7012913</v>
+        <v>7012905</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -15180,6 +15180,1218 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>121478180</v>
+      </c>
+      <c r="B132" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>574621</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7013135</v>
+      </c>
+      <c r="S132" t="n">
+        <v>15</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>121478177</v>
+      </c>
+      <c r="B133" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>575062</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7012904</v>
+      </c>
+      <c r="S133" t="n">
+        <v>15</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>121478176</v>
+      </c>
+      <c r="B134" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>575007</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7012910</v>
+      </c>
+      <c r="S134" t="n">
+        <v>15</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>121478171</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>574767</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7012883</v>
+      </c>
+      <c r="S135" t="n">
+        <v>15</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>121478170</v>
+      </c>
+      <c r="B136" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>574837</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7013028</v>
+      </c>
+      <c r="S136" t="n">
+        <v>15</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>121478181</v>
+      </c>
+      <c r="B137" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>574923</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7013012</v>
+      </c>
+      <c r="S137" t="n">
+        <v>15</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>121478173</v>
+      </c>
+      <c r="B138" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>575033</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7012975</v>
+      </c>
+      <c r="S138" t="n">
+        <v>15</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>121478178</v>
+      </c>
+      <c r="B139" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>575154</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7012925</v>
+      </c>
+      <c r="S139" t="n">
+        <v>15</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>121478169</v>
+      </c>
+      <c r="B140" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>574914</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7012937</v>
+      </c>
+      <c r="S140" t="n">
+        <v>15</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>121478179</v>
+      </c>
+      <c r="B141" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>575047</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7012991</v>
+      </c>
+      <c r="S141" t="n">
+        <v>15</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>121478174</v>
+      </c>
+      <c r="B142" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>574694</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7013073</v>
+      </c>
+      <c r="S142" t="n">
+        <v>15</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14367,10 +14367,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121217729</v>
+        <v>120758611</v>
       </c>
       <c r="B124" t="n">
-        <v>79686</v>
+        <v>79685</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14383,21 +14383,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14410,7 +14410,7 @@
         <v>574659</v>
       </c>
       <c r="R124" t="n">
-        <v>7012913</v>
+        <v>7012911</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121217724</v>
+        <v>121217742</v>
       </c>
       <c r="B126" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>574579</v>
+        <v>575004</v>
       </c>
       <c r="R126" t="n">
-        <v>7013036</v>
+        <v>7013092</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217764</v>
+        <v>121217724</v>
       </c>
       <c r="B127" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>574587</v>
+        <v>574579</v>
       </c>
       <c r="R127" t="n">
-        <v>7013277</v>
+        <v>7013036</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121217742</v>
+        <v>121217761</v>
       </c>
       <c r="B128" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14791,21 +14791,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>575004</v>
+        <v>574798</v>
       </c>
       <c r="R128" t="n">
-        <v>7013092</v>
+        <v>7012916</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14877,7 +14877,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121217761</v>
+        <v>120758613</v>
       </c>
       <c r="B129" t="n">
         <v>79685</v>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>574798</v>
+        <v>574587</v>
       </c>
       <c r="R129" t="n">
-        <v>7012916</v>
+        <v>7013277</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121217762</v>
+        <v>121217723</v>
       </c>
       <c r="B130" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14995,21 +14995,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>574659</v>
+        <v>574662</v>
       </c>
       <c r="R130" t="n">
-        <v>7012911</v>
+        <v>7012905</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121217723</v>
+        <v>121217729</v>
       </c>
       <c r="B131" t="n">
-        <v>90709</v>
+        <v>79686</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15097,21 +15097,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>574662</v>
+        <v>574659</v>
       </c>
       <c r="R131" t="n">
-        <v>7012905</v>
+        <v>7012913</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -15183,10 +15183,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121478180</v>
+        <v>121478171</v>
       </c>
       <c r="B132" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15199,39 +15199,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>574621</v>
+        <v>574767</v>
       </c>
       <c r="R132" t="n">
-        <v>7013135</v>
+        <v>7012883</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15258,17 +15253,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15295,7 +15285,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478177</v>
+        <v>121478179</v>
       </c>
       <c r="B133" t="n">
         <v>57351</v>
@@ -15340,10 +15330,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>575062</v>
+        <v>575047</v>
       </c>
       <c r="R133" t="n">
-        <v>7012904</v>
+        <v>7012991</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15407,7 +15397,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121478176</v>
+        <v>121478177</v>
       </c>
       <c r="B134" t="n">
         <v>57351</v>
@@ -15452,10 +15442,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>575007</v>
+        <v>575062</v>
       </c>
       <c r="R134" t="n">
-        <v>7012910</v>
+        <v>7012904</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15519,10 +15509,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478171</v>
+        <v>121478169</v>
       </c>
       <c r="B135" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15535,21 +15525,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15559,10 +15549,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>574767</v>
+        <v>574914</v>
       </c>
       <c r="R135" t="n">
-        <v>7012883</v>
+        <v>7012937</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15621,7 +15611,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478170</v>
+        <v>121478181</v>
       </c>
       <c r="B136" t="n">
         <v>57351</v>
@@ -15666,10 +15656,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>574837</v>
+        <v>574923</v>
       </c>
       <c r="R136" t="n">
-        <v>7013028</v>
+        <v>7013012</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15696,12 +15686,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -15733,7 +15723,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478181</v>
+        <v>121478174</v>
       </c>
       <c r="B137" t="n">
         <v>57351</v>
@@ -15769,7 +15759,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -15778,10 +15768,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>574923</v>
+        <v>574694</v>
       </c>
       <c r="R137" t="n">
-        <v>7013012</v>
+        <v>7013073</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15808,17 +15798,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15957,7 +15947,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478178</v>
+        <v>121478170</v>
       </c>
       <c r="B139" t="n">
         <v>57351</v>
@@ -16002,10 +15992,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>575154</v>
+        <v>574837</v>
       </c>
       <c r="R139" t="n">
-        <v>7012925</v>
+        <v>7013028</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16069,10 +16059,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478169</v>
+        <v>121478176</v>
       </c>
       <c r="B140" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16085,34 +16075,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>574914</v>
+        <v>575007</v>
       </c>
       <c r="R140" t="n">
-        <v>7012937</v>
+        <v>7012910</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16145,6 +16140,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16171,7 +16171,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478179</v>
+        <v>121478178</v>
       </c>
       <c r="B141" t="n">
         <v>57351</v>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>575047</v>
+        <v>575154</v>
       </c>
       <c r="R141" t="n">
-        <v>7012991</v>
+        <v>7012925</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16283,7 +16283,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478174</v>
+        <v>121478180</v>
       </c>
       <c r="B142" t="n">
         <v>57351</v>
@@ -16319,7 +16319,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>574694</v>
+        <v>574621</v>
       </c>
       <c r="R142" t="n">
-        <v>7013073</v>
+        <v>7013135</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16358,17 +16358,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14367,10 +14367,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120758611</v>
+        <v>121217764</v>
       </c>
       <c r="B124" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14407,10 +14407,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574659</v>
+        <v>574587</v>
       </c>
       <c r="R124" t="n">
-        <v>7012911</v>
+        <v>7013277</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121217763</v>
+        <v>121217742</v>
       </c>
       <c r="B125" t="n">
-        <v>79685</v>
+        <v>57354</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14485,21 +14485,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>574617</v>
+        <v>575004</v>
       </c>
       <c r="R125" t="n">
-        <v>7012907</v>
+        <v>7013092</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121217742</v>
+        <v>120758610</v>
       </c>
       <c r="B126" t="n">
-        <v>57351</v>
+        <v>79688</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>575004</v>
+        <v>574798</v>
       </c>
       <c r="R126" t="n">
-        <v>7013092</v>
+        <v>7012916</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217724</v>
+        <v>120758611</v>
       </c>
       <c r="B127" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>574579</v>
+        <v>574659</v>
       </c>
       <c r="R127" t="n">
-        <v>7013036</v>
+        <v>7012911</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121217761</v>
+        <v>121217724</v>
       </c>
       <c r="B128" t="n">
-        <v>79685</v>
+        <v>90713</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14791,21 +14791,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>574798</v>
+        <v>574579</v>
       </c>
       <c r="R128" t="n">
-        <v>7012916</v>
+        <v>7013036</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120758613</v>
+        <v>121217729</v>
       </c>
       <c r="B129" t="n">
-        <v>79685</v>
+        <v>79689</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>574587</v>
+        <v>574659</v>
       </c>
       <c r="R129" t="n">
-        <v>7013277</v>
+        <v>7012913</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121217723</v>
+        <v>121217763</v>
       </c>
       <c r="B130" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14995,21 +14995,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>574662</v>
+        <v>574617</v>
       </c>
       <c r="R130" t="n">
-        <v>7012905</v>
+        <v>7012907</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121217729</v>
+        <v>121217723</v>
       </c>
       <c r="B131" t="n">
-        <v>79686</v>
+        <v>90713</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15097,21 +15097,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>574659</v>
+        <v>574662</v>
       </c>
       <c r="R131" t="n">
-        <v>7012913</v>
+        <v>7012905</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -15186,7 +15186,7 @@
         <v>121478171</v>
       </c>
       <c r="B132" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15285,10 +15285,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478179</v>
+        <v>121478169</v>
       </c>
       <c r="B133" t="n">
-        <v>57351</v>
+        <v>90713</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15301,39 +15301,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>575047</v>
+        <v>574914</v>
       </c>
       <c r="R133" t="n">
-        <v>7012991</v>
+        <v>7012937</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15366,11 +15361,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15397,10 +15387,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121478177</v>
+        <v>121478181</v>
       </c>
       <c r="B134" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15442,10 +15432,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>575062</v>
+        <v>574923</v>
       </c>
       <c r="R134" t="n">
-        <v>7012904</v>
+        <v>7013012</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15472,12 +15462,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -15509,10 +15499,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478169</v>
+        <v>121478170</v>
       </c>
       <c r="B135" t="n">
-        <v>90710</v>
+        <v>57354</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15525,34 +15515,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>574914</v>
+        <v>574837</v>
       </c>
       <c r="R135" t="n">
-        <v>7012937</v>
+        <v>7013028</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15585,6 +15580,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15611,10 +15611,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478181</v>
+        <v>121478174</v>
       </c>
       <c r="B136" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15656,10 +15656,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>574923</v>
+        <v>574694</v>
       </c>
       <c r="R136" t="n">
-        <v>7013012</v>
+        <v>7013073</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15686,17 +15686,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15723,10 +15723,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478174</v>
+        <v>121478178</v>
       </c>
       <c r="B137" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>574694</v>
+        <v>575154</v>
       </c>
       <c r="R137" t="n">
-        <v>7013073</v>
+        <v>7012925</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15835,10 +15835,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121478173</v>
+        <v>121478177</v>
       </c>
       <c r="B138" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15880,10 +15880,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>575033</v>
+        <v>575062</v>
       </c>
       <c r="R138" t="n">
-        <v>7012975</v>
+        <v>7012904</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15947,10 +15947,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478170</v>
+        <v>121478179</v>
       </c>
       <c r="B139" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15992,10 +15992,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>574837</v>
+        <v>575047</v>
       </c>
       <c r="R139" t="n">
-        <v>7013028</v>
+        <v>7012991</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16059,10 +16059,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478176</v>
+        <v>121478173</v>
       </c>
       <c r="B140" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16104,10 +16104,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>575007</v>
+        <v>575033</v>
       </c>
       <c r="R140" t="n">
-        <v>7012910</v>
+        <v>7012975</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16171,10 +16171,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478178</v>
+        <v>121478180</v>
       </c>
       <c r="B141" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>575154</v>
+        <v>574621</v>
       </c>
       <c r="R141" t="n">
-        <v>7012925</v>
+        <v>7013135</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16246,12 +16246,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -16283,10 +16283,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478180</v>
+        <v>121478176</v>
       </c>
       <c r="B142" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>574621</v>
+        <v>575007</v>
       </c>
       <c r="R142" t="n">
-        <v>7013135</v>
+        <v>7012910</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16358,12 +16358,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14367,10 +14367,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121217764</v>
+        <v>121217724</v>
       </c>
       <c r="B124" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14383,21 +14383,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14407,10 +14407,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574587</v>
+        <v>574579</v>
       </c>
       <c r="R124" t="n">
-        <v>7013277</v>
+        <v>7013036</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121217742</v>
+        <v>120758613</v>
       </c>
       <c r="B125" t="n">
-        <v>57354</v>
+        <v>79688</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14485,21 +14485,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>575004</v>
+        <v>574587</v>
       </c>
       <c r="R125" t="n">
-        <v>7013092</v>
+        <v>7013277</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120758610</v>
+        <v>121217729</v>
       </c>
       <c r="B126" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>574798</v>
+        <v>574659</v>
       </c>
       <c r="R126" t="n">
-        <v>7012916</v>
+        <v>7012913</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,7 +14673,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120758611</v>
+        <v>121217762</v>
       </c>
       <c r="B127" t="n">
         <v>79688</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121217724</v>
+        <v>121217763</v>
       </c>
       <c r="B128" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14791,21 +14791,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>574579</v>
+        <v>574617</v>
       </c>
       <c r="R128" t="n">
-        <v>7013036</v>
+        <v>7012907</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121217729</v>
+        <v>121217742</v>
       </c>
       <c r="B129" t="n">
-        <v>79689</v>
+        <v>57354</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>574659</v>
+        <v>575004</v>
       </c>
       <c r="R129" t="n">
-        <v>7012913</v>
+        <v>7013092</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121217763</v>
+        <v>121217723</v>
       </c>
       <c r="B130" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14995,21 +14995,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>574617</v>
+        <v>574662</v>
       </c>
       <c r="R130" t="n">
-        <v>7012907</v>
+        <v>7012905</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121217723</v>
+        <v>121217761</v>
       </c>
       <c r="B131" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15097,21 +15097,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>574662</v>
+        <v>574798</v>
       </c>
       <c r="R131" t="n">
-        <v>7012905</v>
+        <v>7012916</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -15183,10 +15183,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121478171</v>
+        <v>121478173</v>
       </c>
       <c r="B132" t="n">
-        <v>79688</v>
+        <v>57354</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15199,34 +15199,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>574767</v>
+        <v>575033</v>
       </c>
       <c r="R132" t="n">
-        <v>7012883</v>
+        <v>7012975</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15259,6 +15264,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15387,7 +15397,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121478181</v>
+        <v>121478176</v>
       </c>
       <c r="B134" t="n">
         <v>57354</v>
@@ -15432,10 +15442,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>574923</v>
+        <v>575007</v>
       </c>
       <c r="R134" t="n">
-        <v>7013012</v>
+        <v>7012910</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15462,12 +15472,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -15499,7 +15509,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478170</v>
+        <v>121478178</v>
       </c>
       <c r="B135" t="n">
         <v>57354</v>
@@ -15544,10 +15554,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>574837</v>
+        <v>575154</v>
       </c>
       <c r="R135" t="n">
-        <v>7013028</v>
+        <v>7012925</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15611,10 +15621,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478174</v>
+        <v>121478171</v>
       </c>
       <c r="B136" t="n">
-        <v>57354</v>
+        <v>79688</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15627,39 +15637,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>574694</v>
+        <v>574767</v>
       </c>
       <c r="R136" t="n">
-        <v>7013073</v>
+        <v>7012883</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15692,11 +15697,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15723,7 +15723,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478178</v>
+        <v>121478170</v>
       </c>
       <c r="B137" t="n">
         <v>57354</v>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>575154</v>
+        <v>574837</v>
       </c>
       <c r="R137" t="n">
-        <v>7012925</v>
+        <v>7013028</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15947,7 +15947,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478179</v>
+        <v>121478180</v>
       </c>
       <c r="B139" t="n">
         <v>57354</v>
@@ -15992,10 +15992,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>575047</v>
+        <v>574621</v>
       </c>
       <c r="R139" t="n">
-        <v>7012991</v>
+        <v>7013135</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16022,12 +16022,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -16059,7 +16059,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478173</v>
+        <v>121478181</v>
       </c>
       <c r="B140" t="n">
         <v>57354</v>
@@ -16104,10 +16104,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>575033</v>
+        <v>574923</v>
       </c>
       <c r="R140" t="n">
-        <v>7012975</v>
+        <v>7013012</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16134,12 +16134,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -16171,7 +16171,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478180</v>
+        <v>121478174</v>
       </c>
       <c r="B141" t="n">
         <v>57354</v>
@@ -16207,7 +16207,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>574621</v>
+        <v>574694</v>
       </c>
       <c r="R141" t="n">
-        <v>7013135</v>
+        <v>7013073</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16246,17 +16246,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16283,7 +16283,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478176</v>
+        <v>121478179</v>
       </c>
       <c r="B142" t="n">
         <v>57354</v>
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>575007</v>
+        <v>575047</v>
       </c>
       <c r="R142" t="n">
-        <v>7012910</v>
+        <v>7012991</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121217729</v>
+        <v>121217762</v>
       </c>
       <c r="B126" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14614,7 +14614,7 @@
         <v>574659</v>
       </c>
       <c r="R126" t="n">
-        <v>7012913</v>
+        <v>7012911</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217762</v>
+        <v>121217729</v>
       </c>
       <c r="B127" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
         <v>574659</v>
       </c>
       <c r="R127" t="n">
-        <v>7012911</v>
+        <v>7012913</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121217762</v>
+        <v>121217729</v>
       </c>
       <c r="B126" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14614,7 +14614,7 @@
         <v>574659</v>
       </c>
       <c r="R126" t="n">
-        <v>7012911</v>
+        <v>7012913</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217729</v>
+        <v>121217762</v>
       </c>
       <c r="B127" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
         <v>574659</v>
       </c>
       <c r="R127" t="n">
-        <v>7012913</v>
+        <v>7012911</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14367,10 +14367,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121217724</v>
+        <v>121217763</v>
       </c>
       <c r="B124" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14383,21 +14383,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14407,10 +14407,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574579</v>
+        <v>574617</v>
       </c>
       <c r="R124" t="n">
-        <v>7013036</v>
+        <v>7012907</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120758613</v>
+        <v>121217723</v>
       </c>
       <c r="B125" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14485,21 +14485,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>574587</v>
+        <v>574662</v>
       </c>
       <c r="R125" t="n">
-        <v>7013277</v>
+        <v>7012905</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -14571,7 +14571,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121217729</v>
+        <v>121217764</v>
       </c>
       <c r="B126" t="n">
         <v>79689</v>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>574659</v>
+        <v>574587</v>
       </c>
       <c r="R126" t="n">
-        <v>7012913</v>
+        <v>7013277</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217762</v>
+        <v>121217729</v>
       </c>
       <c r="B127" t="n">
-        <v>79688</v>
+        <v>79690</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
         <v>574659</v>
       </c>
       <c r="R127" t="n">
-        <v>7012911</v>
+        <v>7012913</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121217763</v>
+        <v>121217762</v>
       </c>
       <c r="B128" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>574617</v>
+        <v>574659</v>
       </c>
       <c r="R128" t="n">
-        <v>7012907</v>
+        <v>7012911</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14880,7 +14880,7 @@
         <v>121217742</v>
       </c>
       <c r="B129" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121217723</v>
+        <v>121217761</v>
       </c>
       <c r="B130" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14995,21 +14995,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>574662</v>
+        <v>574798</v>
       </c>
       <c r="R130" t="n">
-        <v>7012905</v>
+        <v>7012916</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121217761</v>
+        <v>121217724</v>
       </c>
       <c r="B131" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15097,21 +15097,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>574798</v>
+        <v>574579</v>
       </c>
       <c r="R131" t="n">
-        <v>7012916</v>
+        <v>7013036</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -15183,10 +15183,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121478173</v>
+        <v>121478174</v>
       </c>
       <c r="B132" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>575033</v>
+        <v>574694</v>
       </c>
       <c r="R132" t="n">
-        <v>7012975</v>
+        <v>7013073</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15295,10 +15295,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478169</v>
+        <v>121478181</v>
       </c>
       <c r="B133" t="n">
-        <v>90713</v>
+        <v>57355</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15311,34 +15311,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>574914</v>
+        <v>574923</v>
       </c>
       <c r="R133" t="n">
-        <v>7012937</v>
+        <v>7013012</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15365,12 +15370,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15400,7 +15410,7 @@
         <v>121478176</v>
       </c>
       <c r="B134" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15509,10 +15519,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478178</v>
+        <v>121478179</v>
       </c>
       <c r="B135" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15554,10 +15564,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>575154</v>
+        <v>575047</v>
       </c>
       <c r="R135" t="n">
-        <v>7012925</v>
+        <v>7012991</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15621,10 +15631,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478171</v>
+        <v>121478169</v>
       </c>
       <c r="B136" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15637,21 +15647,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15661,10 +15671,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>574767</v>
+        <v>574914</v>
       </c>
       <c r="R136" t="n">
-        <v>7012883</v>
+        <v>7012937</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15723,10 +15733,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478170</v>
+        <v>121478178</v>
       </c>
       <c r="B137" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15768,10 +15778,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>574837</v>
+        <v>575154</v>
       </c>
       <c r="R137" t="n">
-        <v>7013028</v>
+        <v>7012925</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15838,7 +15848,7 @@
         <v>121478177</v>
       </c>
       <c r="B138" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15947,10 +15957,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478180</v>
+        <v>121478173</v>
       </c>
       <c r="B139" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15992,10 +16002,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>574621</v>
+        <v>575033</v>
       </c>
       <c r="R139" t="n">
-        <v>7013135</v>
+        <v>7012975</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16022,12 +16032,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -16059,10 +16069,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478181</v>
+        <v>121478170</v>
       </c>
       <c r="B140" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16104,10 +16114,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>574923</v>
+        <v>574837</v>
       </c>
       <c r="R140" t="n">
-        <v>7013012</v>
+        <v>7013028</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16134,12 +16144,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -16171,10 +16181,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478174</v>
+        <v>121478180</v>
       </c>
       <c r="B141" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16207,7 +16217,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -16216,10 +16226,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>574694</v>
+        <v>574621</v>
       </c>
       <c r="R141" t="n">
-        <v>7013073</v>
+        <v>7013135</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16246,17 +16256,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16283,10 +16293,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478179</v>
+        <v>121478171</v>
       </c>
       <c r="B142" t="n">
-        <v>57354</v>
+        <v>79689</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16299,39 +16309,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>575047</v>
+        <v>574767</v>
       </c>
       <c r="R142" t="n">
-        <v>7012991</v>
+        <v>7012883</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16364,11 +16369,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -15519,10 +15519,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478179</v>
+        <v>121478169</v>
       </c>
       <c r="B135" t="n">
-        <v>57355</v>
+        <v>90719</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15535,39 +15535,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>575047</v>
+        <v>574914</v>
       </c>
       <c r="R135" t="n">
-        <v>7012991</v>
+        <v>7012937</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15600,11 +15595,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15631,10 +15621,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478169</v>
+        <v>121478179</v>
       </c>
       <c r="B136" t="n">
-        <v>90719</v>
+        <v>57355</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15647,34 +15637,39 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>574914</v>
+        <v>575047</v>
       </c>
       <c r="R136" t="n">
-        <v>7012937</v>
+        <v>7012991</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15707,6 +15702,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14370,7 +14370,7 @@
         <v>121217763</v>
       </c>
       <c r="B124" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121217723</v>
+        <v>121217764</v>
       </c>
       <c r="B125" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14485,21 +14485,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>574662</v>
+        <v>574587</v>
       </c>
       <c r="R125" t="n">
-        <v>7012905</v>
+        <v>7013277</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121217764</v>
+        <v>121217762</v>
       </c>
       <c r="B126" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>574587</v>
+        <v>574659</v>
       </c>
       <c r="R126" t="n">
-        <v>7013277</v>
+        <v>7012911</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217729</v>
+        <v>121217723</v>
       </c>
       <c r="B127" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>574659</v>
+        <v>574662</v>
       </c>
       <c r="R127" t="n">
-        <v>7012913</v>
+        <v>7012905</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121217762</v>
+        <v>120758610</v>
       </c>
       <c r="B128" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>574659</v>
+        <v>574798</v>
       </c>
       <c r="R128" t="n">
-        <v>7012911</v>
+        <v>7012916</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121217742</v>
+        <v>121217724</v>
       </c>
       <c r="B129" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>575004</v>
+        <v>574579</v>
       </c>
       <c r="R129" t="n">
-        <v>7013092</v>
+        <v>7013036</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121217761</v>
+        <v>121217742</v>
       </c>
       <c r="B130" t="n">
-        <v>79689</v>
+        <v>57356</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14995,21 +14995,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>574798</v>
+        <v>575004</v>
       </c>
       <c r="R130" t="n">
-        <v>7012916</v>
+        <v>7013092</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121217724</v>
+        <v>121217729</v>
       </c>
       <c r="B131" t="n">
-        <v>90719</v>
+        <v>79691</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15097,21 +15097,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>574579</v>
+        <v>574659</v>
       </c>
       <c r="R131" t="n">
-        <v>7013036</v>
+        <v>7012913</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -15183,10 +15183,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121478174</v>
+        <v>121478178</v>
       </c>
       <c r="B132" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>574694</v>
+        <v>575154</v>
       </c>
       <c r="R132" t="n">
-        <v>7013073</v>
+        <v>7012925</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15295,10 +15295,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478181</v>
+        <v>121478170</v>
       </c>
       <c r="B133" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>574923</v>
+        <v>574837</v>
       </c>
       <c r="R133" t="n">
-        <v>7013012</v>
+        <v>7013028</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15370,12 +15370,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -15407,10 +15407,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121478176</v>
+        <v>121478181</v>
       </c>
       <c r="B134" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15452,10 +15452,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>575007</v>
+        <v>574923</v>
       </c>
       <c r="R134" t="n">
-        <v>7012910</v>
+        <v>7013012</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15482,12 +15482,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -15519,10 +15519,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478169</v>
+        <v>121478174</v>
       </c>
       <c r="B135" t="n">
-        <v>90719</v>
+        <v>57356</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15535,34 +15535,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>574914</v>
+        <v>574694</v>
       </c>
       <c r="R135" t="n">
-        <v>7012937</v>
+        <v>7013073</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15595,6 +15600,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15621,10 +15631,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478179</v>
+        <v>121478176</v>
       </c>
       <c r="B136" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15666,10 +15676,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>575047</v>
+        <v>575007</v>
       </c>
       <c r="R136" t="n">
-        <v>7012991</v>
+        <v>7012910</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15733,10 +15743,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478178</v>
+        <v>121478173</v>
       </c>
       <c r="B137" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15778,10 +15788,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>575154</v>
+        <v>575033</v>
       </c>
       <c r="R137" t="n">
-        <v>7012925</v>
+        <v>7012975</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15848,7 +15858,7 @@
         <v>121478177</v>
       </c>
       <c r="B138" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15957,10 +15967,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478173</v>
+        <v>121478179</v>
       </c>
       <c r="B139" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16002,10 +16012,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>575033</v>
+        <v>575047</v>
       </c>
       <c r="R139" t="n">
-        <v>7012975</v>
+        <v>7012991</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16069,10 +16079,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478170</v>
+        <v>121478171</v>
       </c>
       <c r="B140" t="n">
-        <v>57355</v>
+        <v>79690</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16085,39 +16095,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>574837</v>
+        <v>574767</v>
       </c>
       <c r="R140" t="n">
-        <v>7013028</v>
+        <v>7012883</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16150,11 +16155,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16181,10 +16181,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478180</v>
+        <v>121478169</v>
       </c>
       <c r="B141" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16197,39 +16197,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>574621</v>
+        <v>574914</v>
       </c>
       <c r="R141" t="n">
-        <v>7013135</v>
+        <v>7012937</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16256,17 +16251,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16293,10 +16283,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478171</v>
+        <v>121478180</v>
       </c>
       <c r="B142" t="n">
-        <v>79689</v>
+        <v>57356</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16309,34 +16299,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>574767</v>
+        <v>574621</v>
       </c>
       <c r="R142" t="n">
-        <v>7012883</v>
+        <v>7013135</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16363,12 +16358,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14367,7 +14367,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121217763</v>
+        <v>120758612</v>
       </c>
       <c r="B124" t="n">
         <v>79690</v>
@@ -14469,10 +14469,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121217764</v>
+        <v>121217724</v>
       </c>
       <c r="B125" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14485,21 +14485,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>574587</v>
+        <v>574579</v>
       </c>
       <c r="R125" t="n">
-        <v>7013277</v>
+        <v>7013036</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121217762</v>
+        <v>121217729</v>
       </c>
       <c r="B126" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14614,7 +14614,7 @@
         <v>574659</v>
       </c>
       <c r="R126" t="n">
-        <v>7012911</v>
+        <v>7012913</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217723</v>
+        <v>121217742</v>
       </c>
       <c r="B127" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>574662</v>
+        <v>575004</v>
       </c>
       <c r="R127" t="n">
-        <v>7012905</v>
+        <v>7013092</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120758610</v>
+        <v>121217723</v>
       </c>
       <c r="B128" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14791,21 +14791,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>574798</v>
+        <v>574662</v>
       </c>
       <c r="R128" t="n">
-        <v>7012916</v>
+        <v>7012905</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121217724</v>
+        <v>120758611</v>
       </c>
       <c r="B129" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>574579</v>
+        <v>574659</v>
       </c>
       <c r="R129" t="n">
-        <v>7013036</v>
+        <v>7012911</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121217742</v>
+        <v>121217761</v>
       </c>
       <c r="B130" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14995,21 +14995,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>575004</v>
+        <v>574798</v>
       </c>
       <c r="R130" t="n">
-        <v>7013092</v>
+        <v>7012916</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121217729</v>
+        <v>121217764</v>
       </c>
       <c r="B131" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15097,21 +15097,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>574659</v>
+        <v>574587</v>
       </c>
       <c r="R131" t="n">
-        <v>7012913</v>
+        <v>7013277</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -15183,7 +15183,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121478178</v>
+        <v>121478176</v>
       </c>
       <c r="B132" t="n">
         <v>57356</v>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>575154</v>
+        <v>575007</v>
       </c>
       <c r="R132" t="n">
-        <v>7012925</v>
+        <v>7012910</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15295,7 +15295,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478170</v>
+        <v>121478180</v>
       </c>
       <c r="B133" t="n">
         <v>57356</v>
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>574837</v>
+        <v>574621</v>
       </c>
       <c r="R133" t="n">
-        <v>7013028</v>
+        <v>7013135</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15370,12 +15370,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -15407,10 +15407,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121478181</v>
+        <v>121478169</v>
       </c>
       <c r="B134" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15423,39 +15423,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>574923</v>
+        <v>574914</v>
       </c>
       <c r="R134" t="n">
-        <v>7013012</v>
+        <v>7012937</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15482,17 +15477,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15519,7 +15509,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478174</v>
+        <v>121478173</v>
       </c>
       <c r="B135" t="n">
         <v>57356</v>
@@ -15555,7 +15545,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15564,10 +15554,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>574694</v>
+        <v>575033</v>
       </c>
       <c r="R135" t="n">
-        <v>7013073</v>
+        <v>7012975</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15604,7 +15594,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15631,10 +15621,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478176</v>
+        <v>121478171</v>
       </c>
       <c r="B136" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15647,39 +15637,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>575007</v>
+        <v>574767</v>
       </c>
       <c r="R136" t="n">
-        <v>7012910</v>
+        <v>7012883</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15712,11 +15697,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15743,7 +15723,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478173</v>
+        <v>121478181</v>
       </c>
       <c r="B137" t="n">
         <v>57356</v>
@@ -15788,10 +15768,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>575033</v>
+        <v>574923</v>
       </c>
       <c r="R137" t="n">
-        <v>7012975</v>
+        <v>7013012</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15818,12 +15798,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -15855,7 +15835,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121478177</v>
+        <v>121478179</v>
       </c>
       <c r="B138" t="n">
         <v>57356</v>
@@ -15900,10 +15880,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>575062</v>
+        <v>575047</v>
       </c>
       <c r="R138" t="n">
-        <v>7012904</v>
+        <v>7012991</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15967,7 +15947,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478179</v>
+        <v>121478178</v>
       </c>
       <c r="B139" t="n">
         <v>57356</v>
@@ -16012,10 +15992,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>575047</v>
+        <v>575154</v>
       </c>
       <c r="R139" t="n">
-        <v>7012991</v>
+        <v>7012925</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16079,10 +16059,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478171</v>
+        <v>121478170</v>
       </c>
       <c r="B140" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16095,34 +16075,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>574767</v>
+        <v>574837</v>
       </c>
       <c r="R140" t="n">
-        <v>7012883</v>
+        <v>7013028</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16155,6 +16140,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16181,10 +16171,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478169</v>
+        <v>121478174</v>
       </c>
       <c r="B141" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16197,34 +16187,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>574914</v>
+        <v>574694</v>
       </c>
       <c r="R141" t="n">
-        <v>7012937</v>
+        <v>7013073</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16257,6 +16252,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16283,7 +16283,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478180</v>
+        <v>121478177</v>
       </c>
       <c r="B142" t="n">
         <v>57356</v>
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>574621</v>
+        <v>575062</v>
       </c>
       <c r="R142" t="n">
-        <v>7013135</v>
+        <v>7012904</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16358,12 +16358,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -14367,7 +14367,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120758612</v>
+        <v>121217761</v>
       </c>
       <c r="B124" t="n">
         <v>79690</v>
@@ -14407,10 +14407,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>574617</v>
+        <v>574798</v>
       </c>
       <c r="R124" t="n">
-        <v>7012907</v>
+        <v>7012916</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -14469,7 +14469,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121217724</v>
+        <v>121217723</v>
       </c>
       <c r="B125" t="n">
         <v>90720</v>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>574579</v>
+        <v>574662</v>
       </c>
       <c r="R125" t="n">
-        <v>7013036</v>
+        <v>7012905</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -14571,10 +14571,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121217729</v>
+        <v>121217763</v>
       </c>
       <c r="B126" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14587,21 +14587,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>574659</v>
+        <v>574617</v>
       </c>
       <c r="R126" t="n">
-        <v>7012913</v>
+        <v>7012907</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121217742</v>
+        <v>121217762</v>
       </c>
       <c r="B127" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>575004</v>
+        <v>574659</v>
       </c>
       <c r="R127" t="n">
-        <v>7013092</v>
+        <v>7012911</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121217723</v>
+        <v>121217764</v>
       </c>
       <c r="B128" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14791,21 +14791,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>574662</v>
+        <v>574587</v>
       </c>
       <c r="R128" t="n">
-        <v>7012905</v>
+        <v>7013277</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120758611</v>
+        <v>121217729</v>
       </c>
       <c r="B129" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14920,7 +14920,7 @@
         <v>574659</v>
       </c>
       <c r="R129" t="n">
-        <v>7012911</v>
+        <v>7012913</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14979,10 +14979,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121217761</v>
+        <v>121217742</v>
       </c>
       <c r="B130" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14995,21 +14995,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15019,10 +15019,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>574798</v>
+        <v>575004</v>
       </c>
       <c r="R130" t="n">
-        <v>7012916</v>
+        <v>7013092</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121217764</v>
+        <v>121217724</v>
       </c>
       <c r="B131" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15097,21 +15097,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>574587</v>
+        <v>574579</v>
       </c>
       <c r="R131" t="n">
-        <v>7013277</v>
+        <v>7013036</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -15183,7 +15183,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121478176</v>
+        <v>121478178</v>
       </c>
       <c r="B132" t="n">
         <v>57356</v>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>575007</v>
+        <v>575154</v>
       </c>
       <c r="R132" t="n">
-        <v>7012910</v>
+        <v>7012925</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15295,7 +15295,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478180</v>
+        <v>121478174</v>
       </c>
       <c r="B133" t="n">
         <v>57356</v>
@@ -15331,7 +15331,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>574621</v>
+        <v>574694</v>
       </c>
       <c r="R133" t="n">
-        <v>7013135</v>
+        <v>7013073</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15370,17 +15370,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15407,10 +15407,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121478169</v>
+        <v>121478181</v>
       </c>
       <c r="B134" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15423,34 +15423,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>574914</v>
+        <v>574923</v>
       </c>
       <c r="R134" t="n">
-        <v>7012937</v>
+        <v>7013012</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15477,12 +15482,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15509,7 +15519,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478173</v>
+        <v>121478180</v>
       </c>
       <c r="B135" t="n">
         <v>57356</v>
@@ -15554,10 +15564,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>575033</v>
+        <v>574621</v>
       </c>
       <c r="R135" t="n">
-        <v>7012975</v>
+        <v>7013135</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15584,12 +15594,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -15621,10 +15631,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478171</v>
+        <v>121478169</v>
       </c>
       <c r="B136" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15637,21 +15647,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15661,10 +15671,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>574767</v>
+        <v>574914</v>
       </c>
       <c r="R136" t="n">
-        <v>7012883</v>
+        <v>7012937</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15723,7 +15733,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478181</v>
+        <v>121478170</v>
       </c>
       <c r="B137" t="n">
         <v>57356</v>
@@ -15768,10 +15778,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>574923</v>
+        <v>574837</v>
       </c>
       <c r="R137" t="n">
-        <v>7013012</v>
+        <v>7013028</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15798,12 +15808,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -15947,7 +15957,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478178</v>
+        <v>121478173</v>
       </c>
       <c r="B139" t="n">
         <v>57356</v>
@@ -15992,10 +16002,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>575154</v>
+        <v>575033</v>
       </c>
       <c r="R139" t="n">
-        <v>7012925</v>
+        <v>7012975</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16059,10 +16069,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478170</v>
+        <v>121478171</v>
       </c>
       <c r="B140" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16075,39 +16085,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>574837</v>
+        <v>574767</v>
       </c>
       <c r="R140" t="n">
-        <v>7013028</v>
+        <v>7012883</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16140,11 +16145,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16171,7 +16171,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478174</v>
+        <v>121478177</v>
       </c>
       <c r="B141" t="n">
         <v>57356</v>
@@ -16207,7 +16207,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>574694</v>
+        <v>575062</v>
       </c>
       <c r="R141" t="n">
-        <v>7013073</v>
+        <v>7012904</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16283,7 +16283,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478177</v>
+        <v>121478176</v>
       </c>
       <c r="B142" t="n">
         <v>57356</v>
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>575062</v>
+        <v>575007</v>
       </c>
       <c r="R142" t="n">
-        <v>7012904</v>
+        <v>7012910</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -15183,7 +15183,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121478178</v>
+        <v>121478179</v>
       </c>
       <c r="B132" t="n">
         <v>57356</v>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>575154</v>
+        <v>575047</v>
       </c>
       <c r="R132" t="n">
-        <v>7012925</v>
+        <v>7012991</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15295,7 +15295,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478174</v>
+        <v>121478178</v>
       </c>
       <c r="B133" t="n">
         <v>57356</v>
@@ -15331,7 +15331,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>574694</v>
+        <v>575154</v>
       </c>
       <c r="R133" t="n">
-        <v>7013073</v>
+        <v>7012925</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15407,7 +15407,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121478181</v>
+        <v>121478177</v>
       </c>
       <c r="B134" t="n">
         <v>57356</v>
@@ -15452,10 +15452,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>574923</v>
+        <v>575062</v>
       </c>
       <c r="R134" t="n">
-        <v>7013012</v>
+        <v>7012904</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15482,12 +15482,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -15519,7 +15519,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478180</v>
+        <v>121478176</v>
       </c>
       <c r="B135" t="n">
         <v>57356</v>
@@ -15564,10 +15564,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>574621</v>
+        <v>575007</v>
       </c>
       <c r="R135" t="n">
-        <v>7013135</v>
+        <v>7012910</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15594,12 +15594,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -15631,10 +15631,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478169</v>
+        <v>121478180</v>
       </c>
       <c r="B136" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15647,34 +15647,39 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>574914</v>
+        <v>574621</v>
       </c>
       <c r="R136" t="n">
-        <v>7012937</v>
+        <v>7013135</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15701,12 +15706,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15733,10 +15743,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478170</v>
+        <v>121478169</v>
       </c>
       <c r="B137" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15749,39 +15759,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>574837</v>
+        <v>574914</v>
       </c>
       <c r="R137" t="n">
-        <v>7013028</v>
+        <v>7012937</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15814,11 +15819,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15845,7 +15845,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121478179</v>
+        <v>121478170</v>
       </c>
       <c r="B138" t="n">
         <v>57356</v>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>575047</v>
+        <v>574837</v>
       </c>
       <c r="R138" t="n">
-        <v>7012991</v>
+        <v>7013028</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15957,7 +15957,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478173</v>
+        <v>121478181</v>
       </c>
       <c r="B139" t="n">
         <v>57356</v>
@@ -16002,10 +16002,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>575033</v>
+        <v>574923</v>
       </c>
       <c r="R139" t="n">
-        <v>7012975</v>
+        <v>7013012</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16032,12 +16032,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -16069,10 +16069,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478171</v>
+        <v>121478173</v>
       </c>
       <c r="B140" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16085,34 +16085,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>574767</v>
+        <v>575033</v>
       </c>
       <c r="R140" t="n">
-        <v>7012883</v>
+        <v>7012975</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16145,6 +16150,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16171,10 +16181,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478177</v>
+        <v>121478171</v>
       </c>
       <c r="B141" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16187,39 +16197,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>575062</v>
+        <v>574767</v>
       </c>
       <c r="R141" t="n">
-        <v>7012904</v>
+        <v>7012883</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16252,11 +16257,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16283,7 +16283,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478176</v>
+        <v>121478174</v>
       </c>
       <c r="B142" t="n">
         <v>57356</v>
@@ -16319,7 +16319,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>575007</v>
+        <v>574694</v>
       </c>
       <c r="R142" t="n">
-        <v>7012910</v>
+        <v>7013073</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -15186,7 +15186,7 @@
         <v>121478179</v>
       </c>
       <c r="B132" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15295,10 +15295,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478178</v>
+        <v>121478180</v>
       </c>
       <c r="B133" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>575154</v>
+        <v>574621</v>
       </c>
       <c r="R133" t="n">
-        <v>7012925</v>
+        <v>7013135</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15370,12 +15370,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -15410,7 +15410,7 @@
         <v>121478177</v>
       </c>
       <c r="B134" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>121478176</v>
       </c>
       <c r="B135" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15631,10 +15631,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478180</v>
+        <v>121478170</v>
       </c>
       <c r="B136" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15676,10 +15676,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>574621</v>
+        <v>574837</v>
       </c>
       <c r="R136" t="n">
-        <v>7013135</v>
+        <v>7013028</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15706,12 +15706,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478169</v>
+        <v>121478173</v>
       </c>
       <c r="B137" t="n">
-        <v>90720</v>
+        <v>57357</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15759,34 +15759,39 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>574914</v>
+        <v>575033</v>
       </c>
       <c r="R137" t="n">
-        <v>7012937</v>
+        <v>7012975</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15819,6 +15824,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15845,10 +15855,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121478170</v>
+        <v>121478169</v>
       </c>
       <c r="B138" t="n">
-        <v>57356</v>
+        <v>90728</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15861,39 +15871,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>574837</v>
+        <v>574914</v>
       </c>
       <c r="R138" t="n">
-        <v>7013028</v>
+        <v>7012937</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15926,11 +15931,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15957,10 +15957,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478181</v>
+        <v>121478174</v>
       </c>
       <c r="B139" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -16002,10 +16002,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>574923</v>
+        <v>574694</v>
       </c>
       <c r="R139" t="n">
-        <v>7013012</v>
+        <v>7013073</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16032,17 +16032,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16069,10 +16069,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478173</v>
+        <v>121478171</v>
       </c>
       <c r="B140" t="n">
-        <v>57356</v>
+        <v>79697</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16085,39 +16085,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>575033</v>
+        <v>574767</v>
       </c>
       <c r="R140" t="n">
-        <v>7012975</v>
+        <v>7012883</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16150,11 +16145,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16181,10 +16171,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478171</v>
+        <v>121478181</v>
       </c>
       <c r="B141" t="n">
-        <v>79690</v>
+        <v>57357</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16197,34 +16187,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>574767</v>
+        <v>574923</v>
       </c>
       <c r="R141" t="n">
-        <v>7012883</v>
+        <v>7013012</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16251,12 +16246,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16283,10 +16283,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478174</v>
+        <v>121478178</v>
       </c>
       <c r="B142" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>574694</v>
+        <v>575154</v>
       </c>
       <c r="R142" t="n">
-        <v>7013073</v>
+        <v>7012925</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -15183,7 +15183,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121478180</v>
+        <v>121478177</v>
       </c>
       <c r="B132" t="n">
         <v>57357</v>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>574621</v>
+        <v>575062</v>
       </c>
       <c r="R132" t="n">
-        <v>7013135</v>
+        <v>7012904</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -15295,7 +15295,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478178</v>
+        <v>121478173</v>
       </c>
       <c r="B133" t="n">
         <v>57357</v>
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>575154</v>
+        <v>575033</v>
       </c>
       <c r="R133" t="n">
-        <v>7012925</v>
+        <v>7012975</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15407,7 +15407,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121478176</v>
+        <v>121478170</v>
       </c>
       <c r="B134" t="n">
         <v>57357</v>
@@ -15452,10 +15452,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>575007</v>
+        <v>574837</v>
       </c>
       <c r="R134" t="n">
-        <v>7012910</v>
+        <v>7013028</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15631,10 +15631,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121478181</v>
+        <v>121478171</v>
       </c>
       <c r="B136" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15647,39 +15647,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>574923</v>
+        <v>574767</v>
       </c>
       <c r="R136" t="n">
-        <v>7013012</v>
+        <v>7012883</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15706,17 +15701,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15743,7 +15733,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478179</v>
+        <v>121478178</v>
       </c>
       <c r="B137" t="n">
         <v>57357</v>
@@ -15788,10 +15778,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>575047</v>
+        <v>575154</v>
       </c>
       <c r="R137" t="n">
-        <v>7012991</v>
+        <v>7012925</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15855,10 +15845,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121478177</v>
+        <v>121478169</v>
       </c>
       <c r="B138" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15871,39 +15861,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>575062</v>
+        <v>574914</v>
       </c>
       <c r="R138" t="n">
-        <v>7012904</v>
+        <v>7012937</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15936,11 +15921,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15967,7 +15947,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478170</v>
+        <v>121478179</v>
       </c>
       <c r="B139" t="n">
         <v>57357</v>
@@ -16012,10 +15992,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>574837</v>
+        <v>575047</v>
       </c>
       <c r="R139" t="n">
-        <v>7013028</v>
+        <v>7012991</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16079,10 +16059,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478171</v>
+        <v>121478180</v>
       </c>
       <c r="B140" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16095,34 +16075,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>574767</v>
+        <v>574621</v>
       </c>
       <c r="R140" t="n">
-        <v>7012883</v>
+        <v>7013135</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16149,12 +16134,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16181,7 +16171,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478173</v>
+        <v>121478176</v>
       </c>
       <c r="B141" t="n">
         <v>57357</v>
@@ -16226,10 +16216,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>575033</v>
+        <v>575007</v>
       </c>
       <c r="R141" t="n">
-        <v>7012975</v>
+        <v>7012910</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16293,10 +16283,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478169</v>
+        <v>121478181</v>
       </c>
       <c r="B142" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16309,34 +16299,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>574914</v>
+        <v>574923</v>
       </c>
       <c r="R142" t="n">
-        <v>7012937</v>
+        <v>7013012</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16363,12 +16358,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -15183,7 +15183,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121478177</v>
+        <v>121478179</v>
       </c>
       <c r="B132" t="n">
         <v>57357</v>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>575062</v>
+        <v>575047</v>
       </c>
       <c r="R132" t="n">
-        <v>7012904</v>
+        <v>7012991</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15295,7 +15295,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121478173</v>
+        <v>121478174</v>
       </c>
       <c r="B133" t="n">
         <v>57357</v>
@@ -15331,7 +15331,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>575033</v>
+        <v>574694</v>
       </c>
       <c r="R133" t="n">
-        <v>7012975</v>
+        <v>7013073</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15407,10 +15407,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121478170</v>
+        <v>121478169</v>
       </c>
       <c r="B134" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15423,39 +15423,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>574837</v>
+        <v>574914</v>
       </c>
       <c r="R134" t="n">
-        <v>7013028</v>
+        <v>7012937</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15488,11 +15483,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15519,7 +15509,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121478174</v>
+        <v>121478180</v>
       </c>
       <c r="B135" t="n">
         <v>57357</v>
@@ -15555,7 +15545,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15564,10 +15554,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>574694</v>
+        <v>574621</v>
       </c>
       <c r="R135" t="n">
-        <v>7013073</v>
+        <v>7013135</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15594,17 +15584,17 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15733,7 +15723,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121478178</v>
+        <v>121478170</v>
       </c>
       <c r="B137" t="n">
         <v>57357</v>
@@ -15778,10 +15768,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>575154</v>
+        <v>574837</v>
       </c>
       <c r="R137" t="n">
-        <v>7012925</v>
+        <v>7013028</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15845,10 +15835,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121478169</v>
+        <v>121478177</v>
       </c>
       <c r="B138" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15861,34 +15851,39 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>574914</v>
+        <v>575062</v>
       </c>
       <c r="R138" t="n">
-        <v>7012937</v>
+        <v>7012904</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15921,6 +15916,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15947,7 +15947,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121478179</v>
+        <v>121478178</v>
       </c>
       <c r="B139" t="n">
         <v>57357</v>
@@ -15992,10 +15992,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>575047</v>
+        <v>575154</v>
       </c>
       <c r="R139" t="n">
-        <v>7012991</v>
+        <v>7012925</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16059,7 +16059,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121478180</v>
+        <v>121478176</v>
       </c>
       <c r="B140" t="n">
         <v>57357</v>
@@ -16104,10 +16104,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>574621</v>
+        <v>575007</v>
       </c>
       <c r="R140" t="n">
-        <v>7013135</v>
+        <v>7012910</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16134,12 +16134,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -16171,7 +16171,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121478176</v>
+        <v>121478181</v>
       </c>
       <c r="B141" t="n">
         <v>57357</v>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>575007</v>
+        <v>574923</v>
       </c>
       <c r="R141" t="n">
-        <v>7012910</v>
+        <v>7013012</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16246,12 +16246,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -16283,7 +16283,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121478181</v>
+        <v>121478173</v>
       </c>
       <c r="B142" t="n">
         <v>57357</v>
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>574923</v>
+        <v>575033</v>
       </c>
       <c r="R142" t="n">
-        <v>7013012</v>
+        <v>7012975</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16358,12 +16358,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AY165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16393,6 +16393,2403 @@
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>125195553</v>
+      </c>
+      <c r="B143" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>574733</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7013248</v>
+      </c>
+      <c r="S143" t="n">
+        <v>15</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>125195547</v>
+      </c>
+      <c r="B144" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>574611</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7012911</v>
+      </c>
+      <c r="S144" t="n">
+        <v>15</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>125195567</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>574449</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7013223</v>
+      </c>
+      <c r="S145" t="n">
+        <v>15</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>125195548</v>
+      </c>
+      <c r="B146" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>574564</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7013042</v>
+      </c>
+      <c r="S146" t="n">
+        <v>15</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>125195556</v>
+      </c>
+      <c r="B147" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>574582</v>
+      </c>
+      <c r="R147" t="n">
+        <v>7013303</v>
+      </c>
+      <c r="S147" t="n">
+        <v>15</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>125195551</v>
+      </c>
+      <c r="B148" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>574481</v>
+      </c>
+      <c r="R148" t="n">
+        <v>7013117</v>
+      </c>
+      <c r="S148" t="n">
+        <v>15</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>125195562</v>
+      </c>
+      <c r="B149" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>574563</v>
+      </c>
+      <c r="R149" t="n">
+        <v>7013060</v>
+      </c>
+      <c r="S149" t="n">
+        <v>15</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>125195558</v>
+      </c>
+      <c r="B150" t="n">
+        <v>79795</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>574836</v>
+      </c>
+      <c r="R150" t="n">
+        <v>7013196</v>
+      </c>
+      <c r="S150" t="n">
+        <v>15</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>125195569</v>
+      </c>
+      <c r="B151" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>574883</v>
+      </c>
+      <c r="R151" t="n">
+        <v>7013157</v>
+      </c>
+      <c r="S151" t="n">
+        <v>15</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>125195552</v>
+      </c>
+      <c r="B152" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>574471</v>
+      </c>
+      <c r="R152" t="n">
+        <v>7013223</v>
+      </c>
+      <c r="S152" t="n">
+        <v>15</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>125195571</v>
+      </c>
+      <c r="B153" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>574586</v>
+      </c>
+      <c r="R153" t="n">
+        <v>7013007</v>
+      </c>
+      <c r="S153" t="n">
+        <v>15</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>125195559</v>
+      </c>
+      <c r="B154" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>658</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>574737</v>
+      </c>
+      <c r="R154" t="n">
+        <v>7013245</v>
+      </c>
+      <c r="S154" t="n">
+        <v>15</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>125195563</v>
+      </c>
+      <c r="B155" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>574545</v>
+      </c>
+      <c r="R155" t="n">
+        <v>7013083</v>
+      </c>
+      <c r="S155" t="n">
+        <v>15</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>125195550</v>
+      </c>
+      <c r="B156" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>574497</v>
+      </c>
+      <c r="R156" t="n">
+        <v>7013083</v>
+      </c>
+      <c r="S156" t="n">
+        <v>15</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>125195570</v>
+      </c>
+      <c r="B157" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>574471</v>
+      </c>
+      <c r="R157" t="n">
+        <v>7013223</v>
+      </c>
+      <c r="S157" t="n">
+        <v>15</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>125195565</v>
+      </c>
+      <c r="B158" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>574609</v>
+      </c>
+      <c r="R158" t="n">
+        <v>7012910</v>
+      </c>
+      <c r="S158" t="n">
+        <v>15</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>125195554</v>
+      </c>
+      <c r="B159" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>574464</v>
+      </c>
+      <c r="R159" t="n">
+        <v>7013233</v>
+      </c>
+      <c r="S159" t="n">
+        <v>15</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>125195566</v>
+      </c>
+      <c r="B160" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>574491</v>
+      </c>
+      <c r="R160" t="n">
+        <v>7013173</v>
+      </c>
+      <c r="S160" t="n">
+        <v>15</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>125195564</v>
+      </c>
+      <c r="B161" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>574811</v>
+      </c>
+      <c r="R161" t="n">
+        <v>7013197</v>
+      </c>
+      <c r="S161" t="n">
+        <v>15</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>125195557</v>
+      </c>
+      <c r="B162" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>574536</v>
+      </c>
+      <c r="R162" t="n">
+        <v>7013070</v>
+      </c>
+      <c r="S162" t="n">
+        <v>15</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>125195555</v>
+      </c>
+      <c r="B163" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>574564</v>
+      </c>
+      <c r="R163" t="n">
+        <v>7013042</v>
+      </c>
+      <c r="S163" t="n">
+        <v>15</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>125195568</v>
+      </c>
+      <c r="B164" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>574506</v>
+      </c>
+      <c r="R164" t="n">
+        <v>7013225</v>
+      </c>
+      <c r="S164" t="n">
+        <v>15</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>125195561</v>
+      </c>
+      <c r="B165" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>574574</v>
+      </c>
+      <c r="R165" t="n">
+        <v>7013257</v>
+      </c>
+      <c r="S165" t="n">
+        <v>15</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Ringhack, både färska och äldre spår</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16395,10 +16395,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125195553</v>
+        <v>125195568</v>
       </c>
       <c r="B143" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16411,21 +16411,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16435,10 +16435,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>574733</v>
+        <v>574506</v>
       </c>
       <c r="R143" t="n">
-        <v>7013248</v>
+        <v>7013225</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16497,10 +16497,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125195547</v>
+        <v>125195566</v>
       </c>
       <c r="B144" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16513,21 +16513,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16537,10 +16537,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>574611</v>
+        <v>574491</v>
       </c>
       <c r="R144" t="n">
-        <v>7012911</v>
+        <v>7013173</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16599,10 +16599,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125195567</v>
+        <v>125195554</v>
       </c>
       <c r="B145" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16615,34 +16615,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>574449</v>
+        <v>574464</v>
       </c>
       <c r="R145" t="n">
-        <v>7013223</v>
+        <v>7013233</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16701,10 +16706,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125195548</v>
+        <v>125195570</v>
       </c>
       <c r="B146" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16713,38 +16718,46 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>574564</v>
+        <v>574471</v>
       </c>
       <c r="R146" t="n">
-        <v>7013042</v>
+        <v>7013223</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16803,10 +16816,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125195556</v>
+        <v>125195558</v>
       </c>
       <c r="B147" t="n">
-        <v>57529</v>
+        <v>79795</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16815,43 +16828,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>574582</v>
+        <v>574836</v>
       </c>
       <c r="R147" t="n">
-        <v>7013303</v>
+        <v>7013196</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -17012,10 +17020,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125195562</v>
+        <v>125195559</v>
       </c>
       <c r="B149" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17028,21 +17036,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17052,10 +17060,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>574563</v>
+        <v>574737</v>
       </c>
       <c r="R149" t="n">
-        <v>7013060</v>
+        <v>7013245</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -17114,10 +17122,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195558</v>
+        <v>125195561</v>
       </c>
       <c r="B150" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17126,38 +17134,46 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574836</v>
+        <v>574574</v>
       </c>
       <c r="R150" t="n">
-        <v>7013196</v>
+        <v>7013257</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17190,6 +17206,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17216,10 +17237,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125195569</v>
+        <v>125195550</v>
       </c>
       <c r="B151" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17232,21 +17253,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17256,10 +17277,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>574883</v>
+        <v>574497</v>
       </c>
       <c r="R151" t="n">
-        <v>7013157</v>
+        <v>7013083</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17318,10 +17339,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125195552</v>
+        <v>125195565</v>
       </c>
       <c r="B152" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17334,21 +17355,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17358,10 +17379,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>574471</v>
+        <v>574609</v>
       </c>
       <c r="R152" t="n">
-        <v>7013223</v>
+        <v>7012910</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17420,10 +17441,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125195571</v>
+        <v>125195564</v>
       </c>
       <c r="B153" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17436,39 +17457,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>574586</v>
+        <v>574811</v>
       </c>
       <c r="R153" t="n">
-        <v>7013007</v>
+        <v>7013197</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17527,10 +17543,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125195559</v>
+        <v>125195567</v>
       </c>
       <c r="B154" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17543,21 +17559,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17567,10 +17583,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>574737</v>
+        <v>574449</v>
       </c>
       <c r="R154" t="n">
-        <v>7013245</v>
+        <v>7013223</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17629,10 +17645,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125195563</v>
+        <v>125195571</v>
       </c>
       <c r="B155" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17645,34 +17661,39 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>574545</v>
+        <v>574586</v>
       </c>
       <c r="R155" t="n">
-        <v>7013083</v>
+        <v>7013007</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -17731,7 +17752,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125195550</v>
+        <v>125195547</v>
       </c>
       <c r="B156" t="n">
         <v>91012</v>
@@ -17771,10 +17792,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>574497</v>
+        <v>574611</v>
       </c>
       <c r="R156" t="n">
-        <v>7013083</v>
+        <v>7012911</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17833,10 +17854,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125195570</v>
+        <v>125195557</v>
       </c>
       <c r="B157" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17845,20 +17866,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -17867,24 +17888,21 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>574471</v>
+        <v>574536</v>
       </c>
       <c r="R157" t="n">
-        <v>7013223</v>
+        <v>7013070</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17943,10 +17961,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125195565</v>
+        <v>125195548</v>
       </c>
       <c r="B158" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17959,21 +17977,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17983,10 +18001,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>574609</v>
+        <v>574564</v>
       </c>
       <c r="R158" t="n">
-        <v>7012910</v>
+        <v>7013042</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -18045,10 +18063,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125195554</v>
+        <v>125195553</v>
       </c>
       <c r="B159" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18061,39 +18079,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574464</v>
+        <v>574733</v>
       </c>
       <c r="R159" t="n">
-        <v>7013233</v>
+        <v>7013248</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18152,7 +18165,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125195566</v>
+        <v>125195562</v>
       </c>
       <c r="B160" t="n">
         <v>79891</v>
@@ -18192,10 +18205,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>574491</v>
+        <v>574563</v>
       </c>
       <c r="R160" t="n">
-        <v>7013173</v>
+        <v>7013060</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18254,10 +18267,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125195564</v>
+        <v>125195552</v>
       </c>
       <c r="B161" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18270,21 +18283,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18294,10 +18307,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>574811</v>
+        <v>574471</v>
       </c>
       <c r="R161" t="n">
-        <v>7013197</v>
+        <v>7013223</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -18356,10 +18369,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125195557</v>
+        <v>125195555</v>
       </c>
       <c r="B162" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18372,16 +18385,16 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -18392,7 +18405,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18401,10 +18414,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>574536</v>
+        <v>574564</v>
       </c>
       <c r="R162" t="n">
-        <v>7013070</v>
+        <v>7013042</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18437,6 +18450,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18463,10 +18481,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125195555</v>
+        <v>125195556</v>
       </c>
       <c r="B163" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18479,16 +18497,16 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -18499,7 +18517,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -18508,10 +18526,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>574564</v>
+        <v>574582</v>
       </c>
       <c r="R163" t="n">
-        <v>7013042</v>
+        <v>7013303</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18544,11 +18562,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18575,7 +18588,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125195568</v>
+        <v>125195569</v>
       </c>
       <c r="B164" t="n">
         <v>79891</v>
@@ -18615,10 +18628,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574506</v>
+        <v>574883</v>
       </c>
       <c r="R164" t="n">
-        <v>7013225</v>
+        <v>7013157</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18677,10 +18690,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125195561</v>
+        <v>125195563</v>
       </c>
       <c r="B165" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18693,42 +18706,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574574</v>
+        <v>574545</v>
       </c>
       <c r="R165" t="n">
-        <v>7013257</v>
+        <v>7013083</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -18761,11 +18766,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD165" t="b">

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16395,10 +16395,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125195568</v>
+        <v>125195553</v>
       </c>
       <c r="B143" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16411,21 +16411,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16435,10 +16435,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>574506</v>
+        <v>574733</v>
       </c>
       <c r="R143" t="n">
-        <v>7013225</v>
+        <v>7013248</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16497,10 +16497,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125195566</v>
+        <v>125195547</v>
       </c>
       <c r="B144" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16513,21 +16513,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16537,10 +16537,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>574491</v>
+        <v>574611</v>
       </c>
       <c r="R144" t="n">
-        <v>7013173</v>
+        <v>7012911</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16599,10 +16599,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125195554</v>
+        <v>125195551</v>
       </c>
       <c r="B145" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16615,39 +16615,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>574464</v>
+        <v>574481</v>
       </c>
       <c r="R145" t="n">
-        <v>7013233</v>
+        <v>7013117</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16706,10 +16701,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125195570</v>
+        <v>125195567</v>
       </c>
       <c r="B146" t="n">
-        <v>57883</v>
+        <v>79891</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16718,43 +16713,35 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>574471</v>
+        <v>574449</v>
       </c>
       <c r="R146" t="n">
         <v>7013223</v>
@@ -16816,10 +16803,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125195558</v>
+        <v>125195569</v>
       </c>
       <c r="B147" t="n">
-        <v>79795</v>
+        <v>79891</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16828,25 +16815,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16856,10 +16843,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>574836</v>
+        <v>574883</v>
       </c>
       <c r="R147" t="n">
-        <v>7013196</v>
+        <v>7013157</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -16918,10 +16905,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125195551</v>
+        <v>125195561</v>
       </c>
       <c r="B148" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16934,34 +16921,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>574481</v>
+        <v>574574</v>
       </c>
       <c r="R148" t="n">
-        <v>7013117</v>
+        <v>7013257</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16994,6 +16989,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17020,10 +17020,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125195559</v>
+        <v>125195552</v>
       </c>
       <c r="B149" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17036,21 +17036,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17060,10 +17060,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>574737</v>
+        <v>574471</v>
       </c>
       <c r="R149" t="n">
-        <v>7013245</v>
+        <v>7013223</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -17122,10 +17122,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195561</v>
+        <v>125195550</v>
       </c>
       <c r="B150" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17138,42 +17138,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574574</v>
+        <v>574497</v>
       </c>
       <c r="R150" t="n">
-        <v>7013257</v>
+        <v>7013083</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17206,11 +17198,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17237,10 +17224,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125195550</v>
+        <v>125195566</v>
       </c>
       <c r="B151" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17253,21 +17240,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17277,10 +17264,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>574497</v>
+        <v>574491</v>
       </c>
       <c r="R151" t="n">
-        <v>7013083</v>
+        <v>7013173</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17339,10 +17326,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125195565</v>
+        <v>125195555</v>
       </c>
       <c r="B152" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17355,34 +17342,39 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>574609</v>
+        <v>574564</v>
       </c>
       <c r="R152" t="n">
-        <v>7012910</v>
+        <v>7013042</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17415,6 +17407,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17441,10 +17438,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125195564</v>
+        <v>125195572</v>
       </c>
       <c r="B153" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17457,34 +17454,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>574811</v>
+        <v>574586</v>
       </c>
       <c r="R153" t="n">
-        <v>7013197</v>
+        <v>7013007</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17517,6 +17522,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Nygjort bohål, 2m upp i gammal gran. Obs av hona utanför.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17543,10 +17553,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125195567</v>
+        <v>125195548</v>
       </c>
       <c r="B154" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17559,21 +17569,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17583,10 +17593,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>574449</v>
+        <v>574564</v>
       </c>
       <c r="R154" t="n">
-        <v>7013223</v>
+        <v>7013042</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17645,10 +17655,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125195571</v>
+        <v>125195563</v>
       </c>
       <c r="B155" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17661,39 +17671,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>574586</v>
+        <v>574545</v>
       </c>
       <c r="R155" t="n">
-        <v>7013007</v>
+        <v>7013083</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -17752,10 +17757,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125195547</v>
+        <v>125195557</v>
       </c>
       <c r="B156" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17768,34 +17773,39 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>574611</v>
+        <v>574536</v>
       </c>
       <c r="R156" t="n">
-        <v>7012911</v>
+        <v>7013070</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17854,7 +17864,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125195557</v>
+        <v>125195556</v>
       </c>
       <c r="B157" t="n">
         <v>57529</v>
@@ -17899,10 +17909,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>574536</v>
+        <v>574582</v>
       </c>
       <c r="R157" t="n">
-        <v>7013070</v>
+        <v>7013303</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17961,10 +17971,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125195548</v>
+        <v>125195565</v>
       </c>
       <c r="B158" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17977,21 +17987,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18001,10 +18011,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>574564</v>
+        <v>574609</v>
       </c>
       <c r="R158" t="n">
-        <v>7013042</v>
+        <v>7012910</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -18063,10 +18073,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125195553</v>
+        <v>125195559</v>
       </c>
       <c r="B159" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18079,21 +18089,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18103,10 +18113,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574733</v>
+        <v>574737</v>
       </c>
       <c r="R159" t="n">
-        <v>7013248</v>
+        <v>7013245</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18165,7 +18175,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125195562</v>
+        <v>125195564</v>
       </c>
       <c r="B160" t="n">
         <v>79891</v>
@@ -18205,10 +18215,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>574563</v>
+        <v>574811</v>
       </c>
       <c r="R160" t="n">
-        <v>7013060</v>
+        <v>7013197</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18267,10 +18277,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125195552</v>
+        <v>125195570</v>
       </c>
       <c r="B161" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18279,28 +18289,36 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
@@ -18369,7 +18387,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125195555</v>
+        <v>125195554</v>
       </c>
       <c r="B162" t="n">
         <v>57513</v>
@@ -18405,7 +18423,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18414,10 +18432,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>574564</v>
+        <v>574464</v>
       </c>
       <c r="R162" t="n">
-        <v>7013042</v>
+        <v>7013233</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18450,11 +18468,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18481,10 +18494,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125195556</v>
+        <v>125195558</v>
       </c>
       <c r="B163" t="n">
-        <v>57529</v>
+        <v>79795</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18493,43 +18506,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>574582</v>
+        <v>574836</v>
       </c>
       <c r="R163" t="n">
-        <v>7013303</v>
+        <v>7013196</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18588,7 +18596,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125195569</v>
+        <v>125195562</v>
       </c>
       <c r="B164" t="n">
         <v>79891</v>
@@ -18628,10 +18636,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574883</v>
+        <v>574563</v>
       </c>
       <c r="R164" t="n">
-        <v>7013157</v>
+        <v>7013060</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18690,7 +18698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125195563</v>
+        <v>125195568</v>
       </c>
       <c r="B165" t="n">
         <v>79891</v>
@@ -18730,10 +18738,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574545</v>
+        <v>574506</v>
       </c>
       <c r="R165" t="n">
-        <v>7013083</v>
+        <v>7013225</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16395,10 +16395,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125195553</v>
+        <v>125195558</v>
       </c>
       <c r="B143" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16407,25 +16407,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16435,10 +16435,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>574733</v>
+        <v>574836</v>
       </c>
       <c r="R143" t="n">
-        <v>7013248</v>
+        <v>7013196</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16497,10 +16497,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125195547</v>
+        <v>125195561</v>
       </c>
       <c r="B144" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16513,34 +16513,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>574611</v>
+        <v>574574</v>
       </c>
       <c r="R144" t="n">
-        <v>7012911</v>
+        <v>7013257</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16573,6 +16581,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16599,10 +16612,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125195551</v>
+        <v>125195555</v>
       </c>
       <c r="B145" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16615,34 +16628,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>574481</v>
+        <v>574564</v>
       </c>
       <c r="R145" t="n">
-        <v>7013117</v>
+        <v>7013042</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16675,6 +16693,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16701,7 +16724,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125195567</v>
+        <v>125195562</v>
       </c>
       <c r="B146" t="n">
         <v>79891</v>
@@ -16741,10 +16764,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>574449</v>
+        <v>574563</v>
       </c>
       <c r="R146" t="n">
-        <v>7013223</v>
+        <v>7013060</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16803,7 +16826,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125195569</v>
+        <v>125195567</v>
       </c>
       <c r="B147" t="n">
         <v>79891</v>
@@ -16843,10 +16866,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>574883</v>
+        <v>574449</v>
       </c>
       <c r="R147" t="n">
-        <v>7013157</v>
+        <v>7013223</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -16905,10 +16928,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125195561</v>
+        <v>125195552</v>
       </c>
       <c r="B148" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16921,42 +16944,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>574574</v>
+        <v>574471</v>
       </c>
       <c r="R148" t="n">
-        <v>7013257</v>
+        <v>7013223</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16989,11 +17004,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17020,10 +17030,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125195552</v>
+        <v>125195570</v>
       </c>
       <c r="B149" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17032,28 +17042,36 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
@@ -17122,10 +17140,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195550</v>
+        <v>125195568</v>
       </c>
       <c r="B150" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17138,21 +17156,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17162,10 +17180,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574497</v>
+        <v>574506</v>
       </c>
       <c r="R150" t="n">
-        <v>7013083</v>
+        <v>7013225</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17326,10 +17344,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125195555</v>
+        <v>125195564</v>
       </c>
       <c r="B152" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17342,39 +17360,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>574564</v>
+        <v>574811</v>
       </c>
       <c r="R152" t="n">
-        <v>7013042</v>
+        <v>7013197</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17407,11 +17420,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17438,10 +17446,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125195572</v>
+        <v>125195548</v>
       </c>
       <c r="B153" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17454,42 +17462,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>574586</v>
+        <v>574564</v>
       </c>
       <c r="R153" t="n">
-        <v>7013007</v>
+        <v>7013042</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17522,11 +17522,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Nygjort bohål, 2m upp i gammal gran. Obs av hona utanför.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17553,10 +17548,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125195548</v>
+        <v>125195557</v>
       </c>
       <c r="B154" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17569,34 +17564,39 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>574564</v>
+        <v>574536</v>
       </c>
       <c r="R154" t="n">
-        <v>7013042</v>
+        <v>7013070</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17655,10 +17655,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125195563</v>
+        <v>125195551</v>
       </c>
       <c r="B155" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17671,21 +17671,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17695,10 +17695,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>574545</v>
+        <v>574481</v>
       </c>
       <c r="R155" t="n">
-        <v>7013083</v>
+        <v>7013117</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -17757,10 +17757,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125195557</v>
+        <v>125195547</v>
       </c>
       <c r="B156" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17773,39 +17773,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>574536</v>
+        <v>574611</v>
       </c>
       <c r="R156" t="n">
-        <v>7013070</v>
+        <v>7012911</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17864,10 +17859,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125195556</v>
+        <v>125195565</v>
       </c>
       <c r="B157" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17880,39 +17875,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>574582</v>
+        <v>574609</v>
       </c>
       <c r="R157" t="n">
-        <v>7013303</v>
+        <v>7012910</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17971,7 +17961,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125195565</v>
+        <v>125195563</v>
       </c>
       <c r="B158" t="n">
         <v>79891</v>
@@ -18011,10 +18001,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>574609</v>
+        <v>574545</v>
       </c>
       <c r="R158" t="n">
-        <v>7012910</v>
+        <v>7013083</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -18073,10 +18063,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125195559</v>
+        <v>125195553</v>
       </c>
       <c r="B159" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18089,21 +18079,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18113,10 +18103,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574737</v>
+        <v>574733</v>
       </c>
       <c r="R159" t="n">
-        <v>7013245</v>
+        <v>7013248</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18175,10 +18165,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125195564</v>
+        <v>125195572</v>
       </c>
       <c r="B160" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18191,34 +18181,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>574811</v>
+        <v>574586</v>
       </c>
       <c r="R160" t="n">
-        <v>7013197</v>
+        <v>7013007</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18251,6 +18249,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Nygjort bohål, 2m upp i gammal gran. Obs av hona utanför.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18277,10 +18280,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125195570</v>
+        <v>125195554</v>
       </c>
       <c r="B161" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18289,20 +18292,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -18311,24 +18314,21 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>574471</v>
+        <v>574464</v>
       </c>
       <c r="R161" t="n">
-        <v>7013223</v>
+        <v>7013233</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -18387,10 +18387,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125195554</v>
+        <v>125195559</v>
       </c>
       <c r="B162" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18403,39 +18403,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>574464</v>
+        <v>574737</v>
       </c>
       <c r="R162" t="n">
-        <v>7013233</v>
+        <v>7013245</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18494,10 +18489,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125195558</v>
+        <v>125195556</v>
       </c>
       <c r="B163" t="n">
-        <v>79795</v>
+        <v>57529</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18506,38 +18501,43 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>574836</v>
+        <v>574582</v>
       </c>
       <c r="R163" t="n">
-        <v>7013196</v>
+        <v>7013303</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18596,10 +18596,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125195562</v>
+        <v>125195550</v>
       </c>
       <c r="B164" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18612,21 +18612,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18636,10 +18636,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574563</v>
+        <v>574497</v>
       </c>
       <c r="R164" t="n">
-        <v>7013060</v>
+        <v>7013083</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18698,7 +18698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125195568</v>
+        <v>125195569</v>
       </c>
       <c r="B165" t="n">
         <v>79891</v>
@@ -18738,10 +18738,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574506</v>
+        <v>574883</v>
       </c>
       <c r="R165" t="n">
-        <v>7013225</v>
+        <v>7013157</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16395,10 +16395,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125195558</v>
+        <v>125195570</v>
       </c>
       <c r="B143" t="n">
-        <v>79795</v>
+        <v>57883</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16411,34 +16411,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>574836</v>
+        <v>574471</v>
       </c>
       <c r="R143" t="n">
-        <v>7013196</v>
+        <v>7013223</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16497,10 +16505,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125195561</v>
+        <v>125195547</v>
       </c>
       <c r="B144" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16513,42 +16521,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>574574</v>
+        <v>574611</v>
       </c>
       <c r="R144" t="n">
-        <v>7013257</v>
+        <v>7012911</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16581,11 +16581,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16612,10 +16607,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125195555</v>
+        <v>125195566</v>
       </c>
       <c r="B145" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16628,39 +16623,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>574564</v>
+        <v>574491</v>
       </c>
       <c r="R145" t="n">
-        <v>7013042</v>
+        <v>7013173</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16693,11 +16683,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16724,7 +16709,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125195562</v>
+        <v>125195565</v>
       </c>
       <c r="B146" t="n">
         <v>79891</v>
@@ -16764,10 +16749,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>574563</v>
+        <v>574609</v>
       </c>
       <c r="R146" t="n">
-        <v>7013060</v>
+        <v>7012910</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16826,10 +16811,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125195567</v>
+        <v>125195558</v>
       </c>
       <c r="B147" t="n">
-        <v>79891</v>
+        <v>79795</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16838,25 +16823,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16866,10 +16851,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>574449</v>
+        <v>574836</v>
       </c>
       <c r="R147" t="n">
-        <v>7013223</v>
+        <v>7013196</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -16928,10 +16913,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125195552</v>
+        <v>125195569</v>
       </c>
       <c r="B148" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16944,21 +16929,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16968,10 +16953,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>574471</v>
+        <v>574883</v>
       </c>
       <c r="R148" t="n">
-        <v>7013223</v>
+        <v>7013157</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -17030,10 +17015,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125195570</v>
+        <v>125195553</v>
       </c>
       <c r="B149" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17042,46 +17027,38 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>574471</v>
+        <v>574733</v>
       </c>
       <c r="R149" t="n">
-        <v>7013223</v>
+        <v>7013248</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -17140,10 +17117,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195568</v>
+        <v>125195550</v>
       </c>
       <c r="B150" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17156,21 +17133,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17180,10 +17157,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574506</v>
+        <v>574497</v>
       </c>
       <c r="R150" t="n">
-        <v>7013225</v>
+        <v>7013083</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17242,10 +17219,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125195566</v>
+        <v>125195552</v>
       </c>
       <c r="B151" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17258,21 +17235,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17282,10 +17259,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>574491</v>
+        <v>574471</v>
       </c>
       <c r="R151" t="n">
-        <v>7013173</v>
+        <v>7013223</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17344,10 +17321,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125195564</v>
+        <v>125195559</v>
       </c>
       <c r="B152" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17360,21 +17337,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17384,10 +17361,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>574811</v>
+        <v>574737</v>
       </c>
       <c r="R152" t="n">
-        <v>7013197</v>
+        <v>7013245</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17446,10 +17423,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125195548</v>
+        <v>125195563</v>
       </c>
       <c r="B153" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17462,21 +17439,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17486,10 +17463,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>574564</v>
+        <v>574545</v>
       </c>
       <c r="R153" t="n">
-        <v>7013042</v>
+        <v>7013083</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17548,7 +17525,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125195557</v>
+        <v>125195556</v>
       </c>
       <c r="B154" t="n">
         <v>57529</v>
@@ -17593,10 +17570,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>574536</v>
+        <v>574582</v>
       </c>
       <c r="R154" t="n">
-        <v>7013070</v>
+        <v>7013303</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17757,10 +17734,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125195547</v>
+        <v>125195568</v>
       </c>
       <c r="B156" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17773,21 +17750,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17797,10 +17774,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>574611</v>
+        <v>574506</v>
       </c>
       <c r="R156" t="n">
-        <v>7012911</v>
+        <v>7013225</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17859,7 +17836,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125195565</v>
+        <v>125195567</v>
       </c>
       <c r="B157" t="n">
         <v>79891</v>
@@ -17899,10 +17876,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>574609</v>
+        <v>574449</v>
       </c>
       <c r="R157" t="n">
-        <v>7012910</v>
+        <v>7013223</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17961,10 +17938,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125195563</v>
+        <v>125195555</v>
       </c>
       <c r="B158" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17977,34 +17954,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>574545</v>
+        <v>574564</v>
       </c>
       <c r="R158" t="n">
-        <v>7013083</v>
+        <v>7013042</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -18037,6 +18019,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18063,10 +18050,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125195553</v>
+        <v>125195571</v>
       </c>
       <c r="B159" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18079,34 +18066,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574733</v>
+        <v>574586</v>
       </c>
       <c r="R159" t="n">
-        <v>7013248</v>
+        <v>7013007</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18165,10 +18157,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125195572</v>
+        <v>125195557</v>
       </c>
       <c r="B160" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18181,16 +18173,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -18199,24 +18191,21 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>574586</v>
+        <v>574536</v>
       </c>
       <c r="R160" t="n">
-        <v>7013007</v>
+        <v>7013070</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18249,11 +18238,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Nygjort bohål, 2m upp i gammal gran. Obs av hona utanför.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18280,10 +18264,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125195554</v>
+        <v>125195564</v>
       </c>
       <c r="B161" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18296,39 +18280,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>574464</v>
+        <v>574811</v>
       </c>
       <c r="R161" t="n">
-        <v>7013233</v>
+        <v>7013197</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -18387,10 +18366,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125195559</v>
+        <v>125195561</v>
       </c>
       <c r="B162" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18403,34 +18382,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>574737</v>
+        <v>574574</v>
       </c>
       <c r="R162" t="n">
-        <v>7013245</v>
+        <v>7013257</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18463,6 +18450,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18489,10 +18481,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125195556</v>
+        <v>125195548</v>
       </c>
       <c r="B163" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18505,39 +18497,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>574582</v>
+        <v>574564</v>
       </c>
       <c r="R163" t="n">
-        <v>7013303</v>
+        <v>7013042</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18596,10 +18583,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125195550</v>
+        <v>125195562</v>
       </c>
       <c r="B164" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18612,21 +18599,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18636,10 +18623,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574497</v>
+        <v>574563</v>
       </c>
       <c r="R164" t="n">
-        <v>7013083</v>
+        <v>7013060</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18698,10 +18685,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125195569</v>
+        <v>125195554</v>
       </c>
       <c r="B165" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18714,34 +18701,39 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574883</v>
+        <v>574464</v>
       </c>
       <c r="R165" t="n">
-        <v>7013157</v>
+        <v>7013233</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -17117,7 +17117,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195550</v>
+        <v>125195552</v>
       </c>
       <c r="B150" t="n">
         <v>91012</v>
@@ -17157,10 +17157,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574497</v>
+        <v>574471</v>
       </c>
       <c r="R150" t="n">
-        <v>7013083</v>
+        <v>7013223</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17219,7 +17219,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125195552</v>
+        <v>125195550</v>
       </c>
       <c r="B151" t="n">
         <v>91012</v>
@@ -17259,10 +17259,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>574471</v>
+        <v>574497</v>
       </c>
       <c r="R151" t="n">
-        <v>7013223</v>
+        <v>7013083</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16395,10 +16395,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125195570</v>
+        <v>125195561</v>
       </c>
       <c r="B143" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16407,20 +16407,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -16433,7 +16433,7 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -16443,10 +16443,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>574471</v>
+        <v>574574</v>
       </c>
       <c r="R143" t="n">
-        <v>7013223</v>
+        <v>7013257</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16479,6 +16479,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16505,10 +16510,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125195547</v>
+        <v>125195570</v>
       </c>
       <c r="B144" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16517,38 +16522,46 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>574611</v>
+        <v>574471</v>
       </c>
       <c r="R144" t="n">
-        <v>7012911</v>
+        <v>7013223</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16607,10 +16620,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125195566</v>
+        <v>125195553</v>
       </c>
       <c r="B145" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16623,21 +16636,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16647,10 +16660,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>574491</v>
+        <v>574733</v>
       </c>
       <c r="R145" t="n">
-        <v>7013173</v>
+        <v>7013248</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16709,10 +16722,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125195565</v>
+        <v>125195552</v>
       </c>
       <c r="B146" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16725,21 +16738,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16749,10 +16762,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>574609</v>
+        <v>574471</v>
       </c>
       <c r="R146" t="n">
-        <v>7012910</v>
+        <v>7013223</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16811,10 +16824,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125195558</v>
+        <v>125195563</v>
       </c>
       <c r="B147" t="n">
-        <v>79795</v>
+        <v>79891</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16823,25 +16836,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16851,10 +16864,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>574836</v>
+        <v>574545</v>
       </c>
       <c r="R147" t="n">
-        <v>7013196</v>
+        <v>7013083</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -16913,10 +16926,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125195569</v>
+        <v>125195557</v>
       </c>
       <c r="B148" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16929,34 +16942,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>574883</v>
+        <v>574536</v>
       </c>
       <c r="R148" t="n">
-        <v>7013157</v>
+        <v>7013070</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -17015,10 +17033,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125195553</v>
+        <v>125195566</v>
       </c>
       <c r="B149" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17031,21 +17049,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17055,10 +17073,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>574733</v>
+        <v>574491</v>
       </c>
       <c r="R149" t="n">
-        <v>7013248</v>
+        <v>7013173</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -17117,7 +17135,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195552</v>
+        <v>125195550</v>
       </c>
       <c r="B150" t="n">
         <v>91012</v>
@@ -17157,10 +17175,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574471</v>
+        <v>574497</v>
       </c>
       <c r="R150" t="n">
-        <v>7013223</v>
+        <v>7013083</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17219,10 +17237,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125195550</v>
+        <v>125195571</v>
       </c>
       <c r="B151" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17235,34 +17253,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>574497</v>
+        <v>574586</v>
       </c>
       <c r="R151" t="n">
-        <v>7013083</v>
+        <v>7013007</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17321,10 +17344,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125195559</v>
+        <v>125195562</v>
       </c>
       <c r="B152" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17337,21 +17360,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17361,10 +17384,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>574737</v>
+        <v>574563</v>
       </c>
       <c r="R152" t="n">
-        <v>7013245</v>
+        <v>7013060</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17423,7 +17446,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125195563</v>
+        <v>125195564</v>
       </c>
       <c r="B153" t="n">
         <v>79891</v>
@@ -17463,10 +17486,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>574545</v>
+        <v>574811</v>
       </c>
       <c r="R153" t="n">
-        <v>7013083</v>
+        <v>7013197</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17734,10 +17757,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125195568</v>
+        <v>125195558</v>
       </c>
       <c r="B156" t="n">
-        <v>79891</v>
+        <v>79795</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17746,25 +17769,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17774,10 +17797,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>574506</v>
+        <v>574836</v>
       </c>
       <c r="R156" t="n">
-        <v>7013225</v>
+        <v>7013196</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17836,10 +17859,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125195567</v>
+        <v>125195548</v>
       </c>
       <c r="B157" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17852,21 +17875,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17876,10 +17899,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>574449</v>
+        <v>574564</v>
       </c>
       <c r="R157" t="n">
-        <v>7013223</v>
+        <v>7013042</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -18050,10 +18073,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125195571</v>
+        <v>125195565</v>
       </c>
       <c r="B159" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18066,39 +18089,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574586</v>
+        <v>574609</v>
       </c>
       <c r="R159" t="n">
-        <v>7013007</v>
+        <v>7012910</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18157,10 +18175,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125195557</v>
+        <v>125195547</v>
       </c>
       <c r="B160" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18173,39 +18191,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>574536</v>
+        <v>574611</v>
       </c>
       <c r="R160" t="n">
-        <v>7013070</v>
+        <v>7012911</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18264,7 +18277,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125195564</v>
+        <v>125195569</v>
       </c>
       <c r="B161" t="n">
         <v>79891</v>
@@ -18304,10 +18317,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>574811</v>
+        <v>574883</v>
       </c>
       <c r="R161" t="n">
-        <v>7013197</v>
+        <v>7013157</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -18366,10 +18379,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125195561</v>
+        <v>125195567</v>
       </c>
       <c r="B162" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18382,42 +18395,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>574574</v>
+        <v>574449</v>
       </c>
       <c r="R162" t="n">
-        <v>7013257</v>
+        <v>7013223</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18450,11 +18455,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18481,10 +18481,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125195548</v>
+        <v>125195559</v>
       </c>
       <c r="B163" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18497,21 +18497,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18521,10 +18521,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>574564</v>
+        <v>574737</v>
       </c>
       <c r="R163" t="n">
-        <v>7013042</v>
+        <v>7013245</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18583,10 +18583,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125195562</v>
+        <v>125195554</v>
       </c>
       <c r="B164" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18599,34 +18599,39 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574563</v>
+        <v>574464</v>
       </c>
       <c r="R164" t="n">
-        <v>7013060</v>
+        <v>7013233</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18685,10 +18690,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125195554</v>
+        <v>125195568</v>
       </c>
       <c r="B165" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18701,39 +18706,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574464</v>
+        <v>574506</v>
       </c>
       <c r="R165" t="n">
-        <v>7013233</v>
+        <v>7013225</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16395,10 +16395,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125195561</v>
+        <v>125195565</v>
       </c>
       <c r="B143" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16411,42 +16411,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>574574</v>
+        <v>574609</v>
       </c>
       <c r="R143" t="n">
-        <v>7013257</v>
+        <v>7012910</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16479,11 +16471,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16510,10 +16497,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125195570</v>
+        <v>125195563</v>
       </c>
       <c r="B144" t="n">
-        <v>57883</v>
+        <v>80028</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16522,46 +16509,38 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>574471</v>
+        <v>574545</v>
       </c>
       <c r="R144" t="n">
-        <v>7013223</v>
+        <v>7013083</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16620,10 +16599,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125195553</v>
+        <v>125195567</v>
       </c>
       <c r="B145" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16636,21 +16615,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16660,10 +16639,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>574733</v>
+        <v>574449</v>
       </c>
       <c r="R145" t="n">
-        <v>7013248</v>
+        <v>7013223</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16722,10 +16701,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125195552</v>
+        <v>125195568</v>
       </c>
       <c r="B146" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16738,21 +16717,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16762,10 +16741,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>574471</v>
+        <v>574506</v>
       </c>
       <c r="R146" t="n">
-        <v>7013223</v>
+        <v>7013225</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16824,10 +16803,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125195563</v>
+        <v>125195551</v>
       </c>
       <c r="B147" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16840,21 +16819,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16864,10 +16843,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>574545</v>
+        <v>574481</v>
       </c>
       <c r="R147" t="n">
-        <v>7013083</v>
+        <v>7013117</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -16926,10 +16905,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125195557</v>
+        <v>125195566</v>
       </c>
       <c r="B148" t="n">
-        <v>57529</v>
+        <v>80028</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16942,39 +16921,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>574536</v>
+        <v>574491</v>
       </c>
       <c r="R148" t="n">
-        <v>7013070</v>
+        <v>7013173</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -17033,10 +17007,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125195566</v>
+        <v>125195557</v>
       </c>
       <c r="B149" t="n">
-        <v>79891</v>
+        <v>57632</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17049,34 +17023,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>574491</v>
+        <v>574536</v>
       </c>
       <c r="R149" t="n">
-        <v>7013173</v>
+        <v>7013070</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -17135,10 +17114,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195550</v>
+        <v>125195559</v>
       </c>
       <c r="B150" t="n">
-        <v>91012</v>
+        <v>91459</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17151,21 +17130,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17175,10 +17154,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574497</v>
+        <v>574737</v>
       </c>
       <c r="R150" t="n">
-        <v>7013083</v>
+        <v>7013245</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17237,10 +17216,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125195571</v>
+        <v>125195558</v>
       </c>
       <c r="B151" t="n">
-        <v>57513</v>
+        <v>79932</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17249,43 +17228,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>574586</v>
+        <v>574836</v>
       </c>
       <c r="R151" t="n">
-        <v>7013007</v>
+        <v>7013196</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17344,10 +17318,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125195562</v>
+        <v>125195564</v>
       </c>
       <c r="B152" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17384,10 +17358,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>574563</v>
+        <v>574811</v>
       </c>
       <c r="R152" t="n">
-        <v>7013060</v>
+        <v>7013197</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17446,10 +17420,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125195564</v>
+        <v>125195561</v>
       </c>
       <c r="B153" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17462,34 +17436,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>574811</v>
+        <v>574574</v>
       </c>
       <c r="R153" t="n">
-        <v>7013197</v>
+        <v>7013257</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17522,6 +17504,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17548,10 +17535,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125195556</v>
+        <v>125195570</v>
       </c>
       <c r="B154" t="n">
-        <v>57529</v>
+        <v>58001</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17560,20 +17547,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -17582,21 +17569,24 @@
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>574582</v>
+        <v>574471</v>
       </c>
       <c r="R154" t="n">
-        <v>7013303</v>
+        <v>7013223</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17655,10 +17645,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125195551</v>
+        <v>125195555</v>
       </c>
       <c r="B155" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17671,34 +17661,39 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>574481</v>
+        <v>574564</v>
       </c>
       <c r="R155" t="n">
-        <v>7013117</v>
+        <v>7013042</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -17731,6 +17726,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17757,10 +17757,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125195558</v>
+        <v>125195569</v>
       </c>
       <c r="B156" t="n">
-        <v>79795</v>
+        <v>80028</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17769,25 +17769,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17797,10 +17797,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>574836</v>
+        <v>574883</v>
       </c>
       <c r="R156" t="n">
-        <v>7013196</v>
+        <v>7013157</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17859,10 +17859,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125195548</v>
+        <v>125195553</v>
       </c>
       <c r="B157" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>574564</v>
+        <v>574733</v>
       </c>
       <c r="R157" t="n">
-        <v>7013042</v>
+        <v>7013248</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125195555</v>
+        <v>125195556</v>
       </c>
       <c r="B158" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17977,16 +17977,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -17997,7 +17997,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18006,10 +18006,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>574564</v>
+        <v>574582</v>
       </c>
       <c r="R158" t="n">
-        <v>7013042</v>
+        <v>7013303</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -18042,11 +18042,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18073,10 +18068,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125195565</v>
+        <v>125195548</v>
       </c>
       <c r="B159" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18089,21 +18084,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18113,10 +18108,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574609</v>
+        <v>574564</v>
       </c>
       <c r="R159" t="n">
-        <v>7012910</v>
+        <v>7013042</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18175,10 +18170,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125195547</v>
+        <v>125195554</v>
       </c>
       <c r="B160" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18191,34 +18186,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>574611</v>
+        <v>574464</v>
       </c>
       <c r="R160" t="n">
-        <v>7012911</v>
+        <v>7013233</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18277,10 +18277,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125195569</v>
+        <v>125195547</v>
       </c>
       <c r="B161" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18293,21 +18293,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18317,10 +18317,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>574883</v>
+        <v>574611</v>
       </c>
       <c r="R161" t="n">
-        <v>7013157</v>
+        <v>7012911</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -18379,10 +18379,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125195567</v>
+        <v>125195571</v>
       </c>
       <c r="B162" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18395,34 +18395,39 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>574449</v>
+        <v>574586</v>
       </c>
       <c r="R162" t="n">
-        <v>7013223</v>
+        <v>7013007</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18481,10 +18486,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125195559</v>
+        <v>125195562</v>
       </c>
       <c r="B163" t="n">
-        <v>91299</v>
+        <v>80028</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18497,21 +18502,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18521,10 +18526,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>574737</v>
+        <v>574563</v>
       </c>
       <c r="R163" t="n">
-        <v>7013245</v>
+        <v>7013060</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18583,10 +18588,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125195554</v>
+        <v>125195550</v>
       </c>
       <c r="B164" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18599,39 +18604,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574464</v>
+        <v>574497</v>
       </c>
       <c r="R164" t="n">
-        <v>7013233</v>
+        <v>7013083</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18690,10 +18690,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125195568</v>
+        <v>125195552</v>
       </c>
       <c r="B165" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18706,21 +18706,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18730,10 +18730,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574506</v>
+        <v>574471</v>
       </c>
       <c r="R165" t="n">
-        <v>7013225</v>
+        <v>7013223</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16395,10 +16395,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125195565</v>
+        <v>125195548</v>
       </c>
       <c r="B143" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16411,21 +16411,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16435,10 +16435,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>574609</v>
+        <v>574564</v>
       </c>
       <c r="R143" t="n">
-        <v>7012910</v>
+        <v>7013042</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16497,10 +16497,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125195563</v>
+        <v>125195571</v>
       </c>
       <c r="B144" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16513,34 +16513,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>574545</v>
+        <v>574586</v>
       </c>
       <c r="R144" t="n">
-        <v>7013083</v>
+        <v>7013007</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16599,7 +16604,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125195567</v>
+        <v>125195562</v>
       </c>
       <c r="B145" t="n">
         <v>80028</v>
@@ -16639,10 +16644,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>574449</v>
+        <v>574563</v>
       </c>
       <c r="R145" t="n">
-        <v>7013223</v>
+        <v>7013060</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16701,10 +16706,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125195568</v>
+        <v>125195561</v>
       </c>
       <c r="B146" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16717,34 +16722,42 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>574506</v>
+        <v>574574</v>
       </c>
       <c r="R146" t="n">
-        <v>7013225</v>
+        <v>7013257</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16777,6 +16790,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16803,10 +16821,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125195551</v>
+        <v>125195565</v>
       </c>
       <c r="B147" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16819,21 +16837,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16843,10 +16861,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>574481</v>
+        <v>574609</v>
       </c>
       <c r="R147" t="n">
-        <v>7013117</v>
+        <v>7012910</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -16905,10 +16923,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125195566</v>
+        <v>125195552</v>
       </c>
       <c r="B148" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16921,21 +16939,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16945,10 +16963,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>574491</v>
+        <v>574471</v>
       </c>
       <c r="R148" t="n">
-        <v>7013173</v>
+        <v>7013223</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -17007,10 +17025,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125195557</v>
+        <v>125195568</v>
       </c>
       <c r="B149" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17023,39 +17041,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>574536</v>
+        <v>574506</v>
       </c>
       <c r="R149" t="n">
-        <v>7013070</v>
+        <v>7013225</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -17114,10 +17127,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195559</v>
+        <v>125195553</v>
       </c>
       <c r="B150" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17130,21 +17143,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17154,10 +17167,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574737</v>
+        <v>574733</v>
       </c>
       <c r="R150" t="n">
-        <v>7013245</v>
+        <v>7013248</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17216,10 +17229,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125195558</v>
+        <v>125195551</v>
       </c>
       <c r="B151" t="n">
-        <v>79932</v>
+        <v>91166</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17228,25 +17241,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17256,10 +17269,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>574836</v>
+        <v>574481</v>
       </c>
       <c r="R151" t="n">
-        <v>7013196</v>
+        <v>7013117</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17318,7 +17331,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125195564</v>
+        <v>125195563</v>
       </c>
       <c r="B152" t="n">
         <v>80028</v>
@@ -17358,10 +17371,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>574811</v>
+        <v>574545</v>
       </c>
       <c r="R152" t="n">
-        <v>7013197</v>
+        <v>7013083</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17420,10 +17433,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125195561</v>
+        <v>125195564</v>
       </c>
       <c r="B153" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17436,42 +17449,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>574574</v>
+        <v>574811</v>
       </c>
       <c r="R153" t="n">
-        <v>7013257</v>
+        <v>7013197</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17504,11 +17509,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17535,10 +17535,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125195570</v>
+        <v>125195547</v>
       </c>
       <c r="B154" t="n">
-        <v>58001</v>
+        <v>91166</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17547,46 +17547,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>574471</v>
+        <v>574611</v>
       </c>
       <c r="R154" t="n">
-        <v>7013223</v>
+        <v>7012911</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17645,10 +17637,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125195555</v>
+        <v>125195556</v>
       </c>
       <c r="B155" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17661,16 +17653,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -17681,7 +17673,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17690,10 +17682,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>574564</v>
+        <v>574582</v>
       </c>
       <c r="R155" t="n">
-        <v>7013042</v>
+        <v>7013303</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -17726,11 +17718,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17757,7 +17744,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125195569</v>
+        <v>125195567</v>
       </c>
       <c r="B156" t="n">
         <v>80028</v>
@@ -17797,10 +17784,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>574883</v>
+        <v>574449</v>
       </c>
       <c r="R156" t="n">
-        <v>7013157</v>
+        <v>7013223</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17859,10 +17846,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125195553</v>
+        <v>125195566</v>
       </c>
       <c r="B157" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17875,21 +17862,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17899,10 +17886,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>574733</v>
+        <v>574491</v>
       </c>
       <c r="R157" t="n">
-        <v>7013248</v>
+        <v>7013173</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17961,10 +17948,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125195556</v>
+        <v>125195555</v>
       </c>
       <c r="B158" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17977,16 +17964,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -17997,7 +17984,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18006,10 +17993,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>574582</v>
+        <v>574564</v>
       </c>
       <c r="R158" t="n">
-        <v>7013303</v>
+        <v>7013042</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -18042,6 +18029,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18068,10 +18060,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125195548</v>
+        <v>125195558</v>
       </c>
       <c r="B159" t="n">
-        <v>91166</v>
+        <v>79932</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18080,25 +18072,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18108,10 +18100,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574564</v>
+        <v>574836</v>
       </c>
       <c r="R159" t="n">
-        <v>7013042</v>
+        <v>7013196</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18170,10 +18162,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125195554</v>
+        <v>125195570</v>
       </c>
       <c r="B160" t="n">
-        <v>57635</v>
+        <v>58001</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18182,20 +18174,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -18204,21 +18196,24 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>574464</v>
+        <v>574471</v>
       </c>
       <c r="R160" t="n">
-        <v>7013233</v>
+        <v>7013223</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18277,10 +18272,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125195547</v>
+        <v>125195557</v>
       </c>
       <c r="B161" t="n">
-        <v>91166</v>
+        <v>57632</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18293,34 +18288,39 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>574611</v>
+        <v>574536</v>
       </c>
       <c r="R161" t="n">
-        <v>7012911</v>
+        <v>7013070</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -18379,10 +18379,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125195571</v>
+        <v>125195550</v>
       </c>
       <c r="B162" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18395,39 +18395,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>574586</v>
+        <v>574497</v>
       </c>
       <c r="R162" t="n">
-        <v>7013007</v>
+        <v>7013083</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18486,7 +18481,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125195562</v>
+        <v>125195569</v>
       </c>
       <c r="B163" t="n">
         <v>80028</v>
@@ -18526,10 +18521,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>574563</v>
+        <v>574883</v>
       </c>
       <c r="R163" t="n">
-        <v>7013060</v>
+        <v>7013157</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18588,10 +18583,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125195550</v>
+        <v>125195554</v>
       </c>
       <c r="B164" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18604,34 +18599,39 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574497</v>
+        <v>574464</v>
       </c>
       <c r="R164" t="n">
-        <v>7013083</v>
+        <v>7013233</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18690,10 +18690,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125195552</v>
+        <v>125195559</v>
       </c>
       <c r="B165" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18706,21 +18706,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18730,10 +18730,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574471</v>
+        <v>574737</v>
       </c>
       <c r="R165" t="n">
-        <v>7013223</v>
+        <v>7013245</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16821,10 +16821,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125195565</v>
+        <v>125195552</v>
       </c>
       <c r="B147" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16837,21 +16837,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16861,10 +16861,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>574609</v>
+        <v>574471</v>
       </c>
       <c r="R147" t="n">
-        <v>7012910</v>
+        <v>7013223</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -16923,10 +16923,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125195552</v>
+        <v>125195565</v>
       </c>
       <c r="B148" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16939,21 +16939,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16963,10 +16963,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>574471</v>
+        <v>574609</v>
       </c>
       <c r="R148" t="n">
-        <v>7013223</v>
+        <v>7012910</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16395,15 +16395,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125195548</v>
+        <v>125195565</v>
       </c>
       <c r="B143" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16411,21 +16406,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16435,10 +16430,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>574564</v>
+        <v>574609</v>
       </c>
       <c r="R143" t="n">
-        <v>7013042</v>
+        <v>7012910</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16497,15 +16492,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125195571</v>
+        <v>125195557</v>
       </c>
       <c r="B144" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16513,16 +16503,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -16533,7 +16523,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16542,10 +16532,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>574586</v>
+        <v>574536</v>
       </c>
       <c r="R144" t="n">
-        <v>7013007</v>
+        <v>7013070</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16604,15 +16594,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125195562</v>
+        <v>125195547</v>
       </c>
       <c r="B145" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16620,21 +16605,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16644,10 +16629,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>574563</v>
+        <v>574611</v>
       </c>
       <c r="R145" t="n">
-        <v>7013060</v>
+        <v>7012911</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16709,12 +16694,7 @@
         <v>125195561</v>
       </c>
       <c r="B146" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16821,37 +16801,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125195552</v>
+        <v>125195558</v>
       </c>
       <c r="B147" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16861,10 +16836,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>574471</v>
+        <v>574836</v>
       </c>
       <c r="R147" t="n">
-        <v>7013223</v>
+        <v>7013196</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -16923,15 +16898,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125195565</v>
+        <v>125195553</v>
       </c>
       <c r="B148" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16939,21 +16909,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16963,10 +16933,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>574609</v>
+        <v>574733</v>
       </c>
       <c r="R148" t="n">
-        <v>7012910</v>
+        <v>7013248</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -17025,15 +16995,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125195568</v>
+        <v>125195555</v>
       </c>
       <c r="B149" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17041,34 +17006,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>574506</v>
+        <v>574564</v>
       </c>
       <c r="R149" t="n">
-        <v>7013225</v>
+        <v>7013042</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -17101,6 +17071,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17127,15 +17102,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195553</v>
+        <v>125195548</v>
       </c>
       <c r="B150" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17167,10 +17137,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574733</v>
+        <v>574564</v>
       </c>
       <c r="R150" t="n">
-        <v>7013248</v>
+        <v>7013042</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17229,15 +17199,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125195551</v>
+        <v>125195566</v>
       </c>
       <c r="B151" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17245,21 +17210,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17269,10 +17234,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>574481</v>
+        <v>574491</v>
       </c>
       <c r="R151" t="n">
-        <v>7013117</v>
+        <v>7013173</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17331,15 +17296,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125195563</v>
+        <v>125195554</v>
       </c>
       <c r="B152" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17347,34 +17307,39 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>574545</v>
+        <v>574464</v>
       </c>
       <c r="R152" t="n">
-        <v>7013083</v>
+        <v>7013233</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17433,15 +17398,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125195564</v>
+        <v>125195563</v>
       </c>
       <c r="B153" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17473,10 +17433,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>574811</v>
+        <v>574545</v>
       </c>
       <c r="R153" t="n">
-        <v>7013197</v>
+        <v>7013083</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17535,15 +17495,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125195547</v>
+        <v>125195551</v>
       </c>
       <c r="B154" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17575,10 +17530,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>574611</v>
+        <v>574481</v>
       </c>
       <c r="R154" t="n">
-        <v>7012911</v>
+        <v>7013117</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17637,15 +17592,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125195556</v>
+        <v>125195559</v>
       </c>
       <c r="B155" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17653,39 +17603,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>574582</v>
+        <v>574737</v>
       </c>
       <c r="R155" t="n">
-        <v>7013303</v>
+        <v>7013245</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -17747,12 +17692,7 @@
         <v>125195567</v>
       </c>
       <c r="B156" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17846,15 +17786,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125195566</v>
+        <v>125195569</v>
       </c>
       <c r="B157" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17886,10 +17821,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>574491</v>
+        <v>574883</v>
       </c>
       <c r="R157" t="n">
-        <v>7013173</v>
+        <v>7013157</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17948,15 +17883,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125195555</v>
+        <v>125195571</v>
       </c>
       <c r="B158" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17984,7 +17914,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -17993,10 +17923,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>574564</v>
+        <v>574586</v>
       </c>
       <c r="R158" t="n">
-        <v>7013042</v>
+        <v>7013007</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -18029,11 +17959,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18060,15 +17985,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125195558</v>
+        <v>125195570</v>
       </c>
       <c r="B159" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18076,34 +17996,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574836</v>
+        <v>574471</v>
       </c>
       <c r="R159" t="n">
-        <v>7013196</v>
+        <v>7013223</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18162,58 +18090,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125195570</v>
+        <v>125195550</v>
       </c>
       <c r="B160" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>574471</v>
+        <v>574497</v>
       </c>
       <c r="R160" t="n">
-        <v>7013223</v>
+        <v>7013083</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18272,15 +18187,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125195557</v>
+        <v>125195568</v>
       </c>
       <c r="B161" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18288,39 +18198,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>574536</v>
+        <v>574506</v>
       </c>
       <c r="R161" t="n">
-        <v>7013070</v>
+        <v>7013225</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -18379,15 +18284,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125195550</v>
+        <v>125195556</v>
       </c>
       <c r="B162" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18395,34 +18295,39 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>574497</v>
+        <v>574582</v>
       </c>
       <c r="R162" t="n">
-        <v>7013083</v>
+        <v>7013303</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18481,15 +18386,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125195569</v>
+        <v>125195564</v>
       </c>
       <c r="B163" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18521,10 +18421,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>574883</v>
+        <v>574811</v>
       </c>
       <c r="R163" t="n">
-        <v>7013157</v>
+        <v>7013197</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18583,15 +18483,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125195554</v>
+        <v>125195552</v>
       </c>
       <c r="B164" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18599,39 +18494,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574464</v>
+        <v>574471</v>
       </c>
       <c r="R164" t="n">
-        <v>7013233</v>
+        <v>7013223</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18690,15 +18580,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125195559</v>
+        <v>125195562</v>
       </c>
       <c r="B165" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18706,21 +18591,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18730,10 +18615,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574737</v>
+        <v>574563</v>
       </c>
       <c r="R165" t="n">
-        <v>7013245</v>
+        <v>7013060</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16395,10 +16395,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125195565</v>
+        <v>125195557</v>
       </c>
       <c r="B143" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16406,34 +16406,39 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>574609</v>
+        <v>574536</v>
       </c>
       <c r="R143" t="n">
-        <v>7012910</v>
+        <v>7013070</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16492,10 +16497,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125195557</v>
+        <v>125195565</v>
       </c>
       <c r="B144" t="n">
-        <v>57648</v>
+        <v>80070</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16503,39 +16508,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>574536</v>
+        <v>574609</v>
       </c>
       <c r="R144" t="n">
-        <v>7013070</v>
+        <v>7012910</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16594,10 +16594,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125195547</v>
+        <v>125195561</v>
       </c>
       <c r="B145" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16605,34 +16605,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>574611</v>
+        <v>574574</v>
       </c>
       <c r="R145" t="n">
-        <v>7012911</v>
+        <v>7013257</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16665,6 +16673,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16691,10 +16704,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125195561</v>
+        <v>125195547</v>
       </c>
       <c r="B146" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,42 +16715,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>574574</v>
+        <v>574611</v>
       </c>
       <c r="R146" t="n">
-        <v>7013257</v>
+        <v>7012911</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16770,11 +16775,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16901,7 +16901,7 @@
         <v>125195553</v>
       </c>
       <c r="B148" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17102,10 +17102,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125195548</v>
+        <v>125195566</v>
       </c>
       <c r="B150" t="n">
-        <v>91220</v>
+        <v>80070</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17113,21 +17113,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17137,10 +17137,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>574564</v>
+        <v>574491</v>
       </c>
       <c r="R150" t="n">
-        <v>7013042</v>
+        <v>7013173</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17199,10 +17199,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125195566</v>
+        <v>125195548</v>
       </c>
       <c r="B151" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17210,21 +17210,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17234,10 +17234,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>574491</v>
+        <v>574564</v>
       </c>
       <c r="R151" t="n">
-        <v>7013173</v>
+        <v>7013042</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17398,10 +17398,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125195563</v>
+        <v>125195551</v>
       </c>
       <c r="B153" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17409,21 +17409,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17433,10 +17433,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>574545</v>
+        <v>574481</v>
       </c>
       <c r="R153" t="n">
-        <v>7013083</v>
+        <v>7013117</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17495,10 +17495,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125195551</v>
+        <v>125195563</v>
       </c>
       <c r="B154" t="n">
-        <v>91220</v>
+        <v>80070</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17506,21 +17506,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17530,10 +17530,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>574481</v>
+        <v>574545</v>
       </c>
       <c r="R154" t="n">
-        <v>7013117</v>
+        <v>7013083</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17592,10 +17592,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125195559</v>
+        <v>125195567</v>
       </c>
       <c r="B155" t="n">
-        <v>91513</v>
+        <v>80070</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17603,21 +17603,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>574737</v>
+        <v>574449</v>
       </c>
       <c r="R155" t="n">
-        <v>7013245</v>
+        <v>7013223</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -17689,10 +17689,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125195567</v>
+        <v>125195559</v>
       </c>
       <c r="B156" t="n">
-        <v>80070</v>
+        <v>91520</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17700,21 +17700,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17724,10 +17724,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>574449</v>
+        <v>574737</v>
       </c>
       <c r="R156" t="n">
-        <v>7013223</v>
+        <v>7013245</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17883,27 +17883,27 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125195571</v>
+        <v>125195570</v>
       </c>
       <c r="B158" t="n">
-        <v>57651</v>
+        <v>58019</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -17912,21 +17912,24 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>574586</v>
+        <v>574471</v>
       </c>
       <c r="R158" t="n">
-        <v>7013007</v>
+        <v>7013223</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -17985,27 +17988,27 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125195570</v>
+        <v>125195571</v>
       </c>
       <c r="B159" t="n">
-        <v>58019</v>
+        <v>57651</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -18014,24 +18017,21 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574471</v>
+        <v>574586</v>
       </c>
       <c r="R159" t="n">
-        <v>7013223</v>
+        <v>7013007</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18093,7 +18093,7 @@
         <v>125195550</v>
       </c>
       <c r="B160" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>125195552</v>
       </c>
       <c r="B164" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -16898,10 +16898,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125195553</v>
+        <v>125195555</v>
       </c>
       <c r="B148" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16909,34 +16909,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>574733</v>
+        <v>574564</v>
       </c>
       <c r="R148" t="n">
-        <v>7013248</v>
+        <v>7013042</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16969,6 +16974,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16995,10 +17005,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125195555</v>
+        <v>125195553</v>
       </c>
       <c r="B149" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17006,39 +17016,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>574564</v>
+        <v>574733</v>
       </c>
       <c r="R149" t="n">
-        <v>7013042</v>
+        <v>7013248</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -17071,11 +17076,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18483,10 +18483,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125195552</v>
+        <v>125195562</v>
       </c>
       <c r="B164" t="n">
-        <v>91227</v>
+        <v>80070</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18494,21 +18494,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18518,10 +18518,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574471</v>
+        <v>574563</v>
       </c>
       <c r="R164" t="n">
-        <v>7013223</v>
+        <v>7013060</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18580,10 +18580,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125195562</v>
+        <v>125195552</v>
       </c>
       <c r="B165" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18591,21 +18591,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18615,10 +18615,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574563</v>
+        <v>574471</v>
       </c>
       <c r="R165" t="n">
-        <v>7013060</v>
+        <v>7013223</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY165"/>
+  <dimension ref="A1:AY167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18675,6 +18675,222 @@
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>126054152</v>
+      </c>
+      <c r="B166" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>574594</v>
+      </c>
+      <c r="R166" t="n">
+        <v>7013007</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Vuxen individ sågs och ungar hördes i bohålet</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>126053988</v>
+      </c>
+      <c r="B167" t="n">
+        <v>57512</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>100136</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Lappuggla</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Strix nebulosa</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>575004</v>
+      </c>
+      <c r="R167" t="n">
+        <v>7012974</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Ugglan sågs och stannade kvar i området. Såg inget bo men den hoade lite hotfullt så möjligt att bo fanns</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18680,7 +18680,7 @@
         <v>126054152</v>
       </c>
       <c r="B166" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>126053988</v>
       </c>
       <c r="B167" t="n">
-        <v>57512</v>
+        <v>57513</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18680,7 +18680,7 @@
         <v>126054152</v>
       </c>
       <c r="B166" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>126053988</v>
       </c>
       <c r="B167" t="n">
-        <v>57513</v>
+        <v>57517</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18680,7 +18680,7 @@
         <v>126054152</v>
       </c>
       <c r="B166" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>126053988</v>
       </c>
       <c r="B167" t="n">
-        <v>57517</v>
+        <v>57518</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -11771,12 +11771,7 @@
         <v>120477401</v>
       </c>
       <c r="B101" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91567</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11802,6 +11797,9 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
@@ -11862,6 +11860,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY167"/>
+  <dimension ref="A1:AY186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11771,7 +11771,7 @@
         <v>120477401</v>
       </c>
       <c r="B101" t="n">
-        <v>91567</v>
+        <v>91572</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -18890,6 +18890,1849 @@
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>128494524</v>
+      </c>
+      <c r="B168" t="n">
+        <v>95710</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>574821</v>
+      </c>
+      <c r="R168" t="n">
+        <v>7013166</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>128494509</v>
+      </c>
+      <c r="B169" t="n">
+        <v>80170</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>574510</v>
+      </c>
+      <c r="R169" t="n">
+        <v>7013219</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>128494525</v>
+      </c>
+      <c r="B170" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>574821</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7013166</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>128494522</v>
+      </c>
+      <c r="B171" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>574726</v>
+      </c>
+      <c r="R171" t="n">
+        <v>7013259</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>128494506</v>
+      </c>
+      <c r="B172" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>574498</v>
+      </c>
+      <c r="R172" t="n">
+        <v>7013253</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>128494515</v>
+      </c>
+      <c r="B173" t="n">
+        <v>80170</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>574634</v>
+      </c>
+      <c r="R173" t="n">
+        <v>7013287</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>128494528</v>
+      </c>
+      <c r="B174" t="n">
+        <v>80170</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>574847</v>
+      </c>
+      <c r="R174" t="n">
+        <v>7013166</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>128494529</v>
+      </c>
+      <c r="B175" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>574847</v>
+      </c>
+      <c r="R175" t="n">
+        <v>7013166</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>128494505</v>
+      </c>
+      <c r="B176" t="n">
+        <v>80136</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>574498</v>
+      </c>
+      <c r="R176" t="n">
+        <v>7013253</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>128494502</v>
+      </c>
+      <c r="B177" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>574457</v>
+      </c>
+      <c r="R177" t="n">
+        <v>7013134</v>
+      </c>
+      <c r="S177" t="n">
+        <v>10</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>128494516</v>
+      </c>
+      <c r="B178" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>574634</v>
+      </c>
+      <c r="R178" t="n">
+        <v>7013287</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>128494497</v>
+      </c>
+      <c r="B179" t="n">
+        <v>80136</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>574786</v>
+      </c>
+      <c r="R179" t="n">
+        <v>7013056</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>128494510</v>
+      </c>
+      <c r="B180" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>574510</v>
+      </c>
+      <c r="R180" t="n">
+        <v>7013219</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>128494498</v>
+      </c>
+      <c r="B181" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>574786</v>
+      </c>
+      <c r="R181" t="n">
+        <v>7013056</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>128494526</v>
+      </c>
+      <c r="B182" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>574821</v>
+      </c>
+      <c r="R182" t="n">
+        <v>7013166</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>128494520</v>
+      </c>
+      <c r="B183" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>574709</v>
+      </c>
+      <c r="R183" t="n">
+        <v>7013249</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>128494514</v>
+      </c>
+      <c r="B184" t="n">
+        <v>80136</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>574634</v>
+      </c>
+      <c r="R184" t="n">
+        <v>7013287</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>128494521</v>
+      </c>
+      <c r="B185" t="n">
+        <v>91561</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>48</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>574726</v>
+      </c>
+      <c r="R185" t="n">
+        <v>7013259</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>128494513</v>
+      </c>
+      <c r="B186" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Prästflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>574580</v>
+      </c>
+      <c r="R186" t="n">
+        <v>7013209</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -11771,7 +11771,7 @@
         <v>120477401</v>
       </c>
       <c r="B101" t="n">
-        <v>91572</v>
+        <v>91664</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18989,27 +18989,27 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494509</v>
+        <v>128494522</v>
       </c>
       <c r="B169" t="n">
-        <v>80170</v>
+        <v>79083</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574510</v>
+        <v>574726</v>
       </c>
       <c r="R169" t="n">
-        <v>7013219</v>
+        <v>7013259</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,32 +19086,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494525</v>
+        <v>128494509</v>
       </c>
       <c r="B170" t="n">
-        <v>80135</v>
+        <v>80223</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574821</v>
+        <v>574510</v>
       </c>
       <c r="R170" t="n">
-        <v>7013166</v>
+        <v>7013219</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,10 +19183,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494522</v>
+        <v>128494525</v>
       </c>
       <c r="B171" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19194,21 +19194,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574726</v>
+        <v>574821</v>
       </c>
       <c r="R171" t="n">
-        <v>7013259</v>
+        <v>7013166</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19283,7 +19283,7 @@
         <v>128494506</v>
       </c>
       <c r="B172" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>128494515</v>
       </c>
       <c r="B173" t="n">
-        <v>80170</v>
+        <v>80223</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>128494528</v>
       </c>
       <c r="B174" t="n">
-        <v>80170</v>
+        <v>80223</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>128494529</v>
       </c>
       <c r="B175" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>128494505</v>
       </c>
       <c r="B176" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>128494502</v>
       </c>
       <c r="B177" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>128494516</v>
       </c>
       <c r="B178" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>128494497</v>
       </c>
       <c r="B179" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>128494510</v>
       </c>
       <c r="B180" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>128494498</v>
       </c>
       <c r="B181" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128494526</v>
       </c>
       <c r="B182" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>128494520</v>
       </c>
       <c r="B183" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>128494514</v>
       </c>
       <c r="B184" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91561</v>
+        <v>91653</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>128494513</v>
       </c>
       <c r="B186" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18989,27 +18989,27 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494522</v>
+        <v>128494509</v>
       </c>
       <c r="B169" t="n">
-        <v>79083</v>
+        <v>80223</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574726</v>
+        <v>574510</v>
       </c>
       <c r="R169" t="n">
-        <v>7013259</v>
+        <v>7013219</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,32 +19086,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494509</v>
+        <v>128494525</v>
       </c>
       <c r="B170" t="n">
-        <v>80223</v>
+        <v>80188</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574510</v>
+        <v>574821</v>
       </c>
       <c r="R170" t="n">
-        <v>7013219</v>
+        <v>7013166</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,10 +19183,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494525</v>
+        <v>128494522</v>
       </c>
       <c r="B171" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19194,21 +19194,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574821</v>
+        <v>574726</v>
       </c>
       <c r="R171" t="n">
-        <v>7013166</v>
+        <v>7013259</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19765,10 +19765,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128494502</v>
+        <v>128494497</v>
       </c>
       <c r="B177" t="n">
-        <v>80188</v>
+        <v>80189</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19776,21 +19776,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>574457</v>
+        <v>574786</v>
       </c>
       <c r="R177" t="n">
-        <v>7013134</v>
+        <v>7013056</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19862,7 +19862,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128494516</v>
+        <v>128494502</v>
       </c>
       <c r="B178" t="n">
         <v>80188</v>
@@ -19897,10 +19897,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>574634</v>
+        <v>574457</v>
       </c>
       <c r="R178" t="n">
-        <v>7013287</v>
+        <v>7013134</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494497</v>
+        <v>128494516</v>
       </c>
       <c r="B179" t="n">
-        <v>80189</v>
+        <v>80188</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19970,21 +19970,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574786</v>
+        <v>574634</v>
       </c>
       <c r="R179" t="n">
-        <v>7013056</v>
+        <v>7013287</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95803</v>
+        <v>95809</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18989,27 +18989,27 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494509</v>
+        <v>128494522</v>
       </c>
       <c r="B169" t="n">
-        <v>80223</v>
+        <v>79087</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574510</v>
+        <v>574726</v>
       </c>
       <c r="R169" t="n">
-        <v>7013219</v>
+        <v>7013259</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,32 +19086,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494525</v>
+        <v>128494509</v>
       </c>
       <c r="B170" t="n">
-        <v>80188</v>
+        <v>80227</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574821</v>
+        <v>574510</v>
       </c>
       <c r="R170" t="n">
-        <v>7013166</v>
+        <v>7013219</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,10 +19183,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494522</v>
+        <v>128494525</v>
       </c>
       <c r="B171" t="n">
-        <v>79083</v>
+        <v>80192</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19194,21 +19194,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574726</v>
+        <v>574821</v>
       </c>
       <c r="R171" t="n">
-        <v>7013259</v>
+        <v>7013166</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19283,7 +19283,7 @@
         <v>128494506</v>
       </c>
       <c r="B172" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>128494515</v>
       </c>
       <c r="B173" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>128494528</v>
       </c>
       <c r="B174" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>128494529</v>
       </c>
       <c r="B175" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>128494505</v>
       </c>
       <c r="B176" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>128494497</v>
       </c>
       <c r="B177" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>128494502</v>
       </c>
       <c r="B178" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>128494516</v>
       </c>
       <c r="B179" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>128494510</v>
       </c>
       <c r="B180" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>128494498</v>
       </c>
       <c r="B181" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128494526</v>
       </c>
       <c r="B182" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>128494520</v>
       </c>
       <c r="B183" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>128494514</v>
       </c>
       <c r="B184" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91653</v>
+        <v>91659</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>128494513</v>
       </c>
       <c r="B186" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -11771,7 +11771,7 @@
         <v>120477401</v>
       </c>
       <c r="B101" t="n">
-        <v>91664</v>
+        <v>91676</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95809</v>
+        <v>95815</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18989,27 +18989,27 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494522</v>
+        <v>128494509</v>
       </c>
       <c r="B169" t="n">
-        <v>79087</v>
+        <v>80227</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574726</v>
+        <v>574510</v>
       </c>
       <c r="R169" t="n">
-        <v>7013259</v>
+        <v>7013219</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,32 +19086,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494509</v>
+        <v>128494525</v>
       </c>
       <c r="B170" t="n">
-        <v>80227</v>
+        <v>80192</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574510</v>
+        <v>574821</v>
       </c>
       <c r="R170" t="n">
-        <v>7013219</v>
+        <v>7013166</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,10 +19183,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494525</v>
+        <v>128494522</v>
       </c>
       <c r="B171" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19194,21 +19194,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574821</v>
+        <v>574726</v>
       </c>
       <c r="R171" t="n">
-        <v>7013166</v>
+        <v>7013259</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19765,10 +19765,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128494497</v>
+        <v>128494502</v>
       </c>
       <c r="B177" t="n">
-        <v>80193</v>
+        <v>80192</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19776,21 +19776,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>574786</v>
+        <v>574457</v>
       </c>
       <c r="R177" t="n">
-        <v>7013056</v>
+        <v>7013134</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19862,7 +19862,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128494502</v>
+        <v>128494516</v>
       </c>
       <c r="B178" t="n">
         <v>80192</v>
@@ -19897,10 +19897,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>574457</v>
+        <v>574634</v>
       </c>
       <c r="R178" t="n">
-        <v>7013134</v>
+        <v>7013287</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494516</v>
+        <v>128494497</v>
       </c>
       <c r="B179" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19970,21 +19970,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574634</v>
+        <v>574786</v>
       </c>
       <c r="R179" t="n">
-        <v>7013287</v>
+        <v>7013056</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91659</v>
+        <v>91665</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -19765,10 +19765,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128494502</v>
+        <v>128494497</v>
       </c>
       <c r="B177" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19776,21 +19776,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>574457</v>
+        <v>574786</v>
       </c>
       <c r="R177" t="n">
-        <v>7013134</v>
+        <v>7013056</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19862,7 +19862,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128494516</v>
+        <v>128494502</v>
       </c>
       <c r="B178" t="n">
         <v>80192</v>
@@ -19897,10 +19897,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>574634</v>
+        <v>574457</v>
       </c>
       <c r="R178" t="n">
-        <v>7013287</v>
+        <v>7013134</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494497</v>
+        <v>128494516</v>
       </c>
       <c r="B179" t="n">
-        <v>80193</v>
+        <v>80192</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19970,21 +19970,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574786</v>
+        <v>574634</v>
       </c>
       <c r="R179" t="n">
-        <v>7013056</v>
+        <v>7013287</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -11771,7 +11771,7 @@
         <v>120477401</v>
       </c>
       <c r="B101" t="n">
-        <v>91676</v>
+        <v>91678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>128494509</v>
       </c>
       <c r="B169" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>128494525</v>
       </c>
       <c r="B170" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>128494522</v>
       </c>
       <c r="B171" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>128494506</v>
       </c>
       <c r="B172" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>128494515</v>
       </c>
       <c r="B173" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>128494528</v>
       </c>
       <c r="B174" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>128494529</v>
       </c>
       <c r="B175" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>128494505</v>
       </c>
       <c r="B176" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19765,10 +19765,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128494497</v>
+        <v>128494502</v>
       </c>
       <c r="B177" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19776,21 +19776,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>574786</v>
+        <v>574457</v>
       </c>
       <c r="R177" t="n">
-        <v>7013056</v>
+        <v>7013134</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19862,10 +19862,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128494502</v>
+        <v>128494516</v>
       </c>
       <c r="B178" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19897,10 +19897,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>574457</v>
+        <v>574634</v>
       </c>
       <c r="R178" t="n">
-        <v>7013134</v>
+        <v>7013287</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494516</v>
+        <v>128494497</v>
       </c>
       <c r="B179" t="n">
-        <v>80192</v>
+        <v>80195</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19970,21 +19970,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574634</v>
+        <v>574786</v>
       </c>
       <c r="R179" t="n">
-        <v>7013287</v>
+        <v>7013056</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20059,7 +20059,7 @@
         <v>128494510</v>
       </c>
       <c r="B180" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>128494498</v>
       </c>
       <c r="B181" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>128494520</v>
       </c>
       <c r="B183" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>128494514</v>
       </c>
       <c r="B184" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91665</v>
+        <v>91667</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>128494513</v>
       </c>
       <c r="B186" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18989,27 +18989,27 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494509</v>
+        <v>128494522</v>
       </c>
       <c r="B169" t="n">
-        <v>80229</v>
+        <v>79089</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574510</v>
+        <v>574726</v>
       </c>
       <c r="R169" t="n">
-        <v>7013219</v>
+        <v>7013259</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,32 +19086,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494525</v>
+        <v>128494509</v>
       </c>
       <c r="B170" t="n">
-        <v>80194</v>
+        <v>80229</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574821</v>
+        <v>574510</v>
       </c>
       <c r="R170" t="n">
-        <v>7013166</v>
+        <v>7013219</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,10 +19183,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494522</v>
+        <v>128494525</v>
       </c>
       <c r="B171" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19194,21 +19194,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574726</v>
+        <v>574821</v>
       </c>
       <c r="R171" t="n">
-        <v>7013259</v>
+        <v>7013166</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19765,10 +19765,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128494502</v>
+        <v>128494497</v>
       </c>
       <c r="B177" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19776,21 +19776,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>574457</v>
+        <v>574786</v>
       </c>
       <c r="R177" t="n">
-        <v>7013134</v>
+        <v>7013056</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494497</v>
+        <v>128494502</v>
       </c>
       <c r="B179" t="n">
-        <v>80195</v>
+        <v>80194</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19970,21 +19970,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574786</v>
+        <v>574457</v>
       </c>
       <c r="R179" t="n">
-        <v>7013056</v>
+        <v>7013134</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -11771,7 +11771,7 @@
         <v>120477401</v>
       </c>
       <c r="B101" t="n">
-        <v>91678</v>
+        <v>91679</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128494516</v>
+        <v>128494502</v>
       </c>
       <c r="B178" t="n">
         <v>80194</v>
@@ -19897,10 +19897,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>574634</v>
+        <v>574457</v>
       </c>
       <c r="R178" t="n">
-        <v>7013287</v>
+        <v>7013134</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19959,7 +19959,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494502</v>
+        <v>128494516</v>
       </c>
       <c r="B179" t="n">
         <v>80194</v>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574457</v>
+        <v>574634</v>
       </c>
       <c r="R179" t="n">
-        <v>7013134</v>
+        <v>7013287</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91667</v>
+        <v>91668</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>128494522</v>
       </c>
       <c r="B169" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>128494509</v>
       </c>
       <c r="B170" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>128494525</v>
       </c>
       <c r="B171" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>128494506</v>
       </c>
       <c r="B172" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>128494515</v>
       </c>
       <c r="B173" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>128494528</v>
       </c>
       <c r="B174" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>128494529</v>
       </c>
       <c r="B175" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>128494505</v>
       </c>
       <c r="B176" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>128494497</v>
       </c>
       <c r="B177" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>128494502</v>
       </c>
       <c r="B178" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>128494516</v>
       </c>
       <c r="B179" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>128494510</v>
       </c>
       <c r="B180" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>128494498</v>
       </c>
       <c r="B181" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128494526</v>
       </c>
       <c r="B182" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>128494520</v>
       </c>
       <c r="B183" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>128494514</v>
       </c>
       <c r="B184" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91668</v>
+        <v>91695</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>128494513</v>
       </c>
       <c r="B186" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -11771,7 +11771,7 @@
         <v>120477401</v>
       </c>
       <c r="B101" t="n">
-        <v>91679</v>
+        <v>91706</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95845</v>
+        <v>95851</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18989,10 +18989,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494522</v>
+        <v>128494525</v>
       </c>
       <c r="B169" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19000,21 +19000,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574726</v>
+        <v>574821</v>
       </c>
       <c r="R169" t="n">
-        <v>7013259</v>
+        <v>7013166</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,27 +19086,27 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494509</v>
+        <v>128494522</v>
       </c>
       <c r="B170" t="n">
-        <v>80256</v>
+        <v>79120</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574510</v>
+        <v>574726</v>
       </c>
       <c r="R170" t="n">
-        <v>7013219</v>
+        <v>7013259</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,32 +19183,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494525</v>
+        <v>128494509</v>
       </c>
       <c r="B171" t="n">
-        <v>80221</v>
+        <v>80260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574821</v>
+        <v>574510</v>
       </c>
       <c r="R171" t="n">
-        <v>7013166</v>
+        <v>7013219</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19283,7 +19283,7 @@
         <v>128494506</v>
       </c>
       <c r="B172" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>128494515</v>
       </c>
       <c r="B173" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>128494528</v>
       </c>
       <c r="B174" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>128494529</v>
       </c>
       <c r="B175" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>128494505</v>
       </c>
       <c r="B176" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>128494497</v>
       </c>
       <c r="B177" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>128494502</v>
       </c>
       <c r="B178" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>128494516</v>
       </c>
       <c r="B179" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>128494510</v>
       </c>
       <c r="B180" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>128494498</v>
       </c>
       <c r="B181" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>128494520</v>
       </c>
       <c r="B183" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>128494514</v>
       </c>
       <c r="B184" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91695</v>
+        <v>91700</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>128494513</v>
       </c>
       <c r="B186" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -11771,7 +11771,7 @@
         <v>120477401</v>
       </c>
       <c r="B101" t="n">
-        <v>91706</v>
+        <v>91716</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95851</v>
+        <v>95858</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18989,32 +18989,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494525</v>
+        <v>128494509</v>
       </c>
       <c r="B169" t="n">
-        <v>80225</v>
+        <v>80260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574821</v>
+        <v>574510</v>
       </c>
       <c r="R169" t="n">
-        <v>7013166</v>
+        <v>7013219</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19183,32 +19183,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494509</v>
+        <v>128494525</v>
       </c>
       <c r="B171" t="n">
-        <v>80260</v>
+        <v>80225</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574510</v>
+        <v>574821</v>
       </c>
       <c r="R171" t="n">
-        <v>7013219</v>
+        <v>7013166</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19862,7 +19862,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128494502</v>
+        <v>128494516</v>
       </c>
       <c r="B178" t="n">
         <v>80225</v>
@@ -19897,10 +19897,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>574457</v>
+        <v>574634</v>
       </c>
       <c r="R178" t="n">
-        <v>7013134</v>
+        <v>7013287</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19959,7 +19959,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494516</v>
+        <v>128494502</v>
       </c>
       <c r="B179" t="n">
         <v>80225</v>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574634</v>
+        <v>574457</v>
       </c>
       <c r="R179" t="n">
-        <v>7013287</v>
+        <v>7013134</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91700</v>
+        <v>91705</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18989,27 +18989,27 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494509</v>
+        <v>128494522</v>
       </c>
       <c r="B169" t="n">
-        <v>80260</v>
+        <v>79120</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574510</v>
+        <v>574726</v>
       </c>
       <c r="R169" t="n">
-        <v>7013219</v>
+        <v>7013259</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,27 +19086,27 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494522</v>
+        <v>128494509</v>
       </c>
       <c r="B170" t="n">
-        <v>79120</v>
+        <v>80260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574726</v>
+        <v>574510</v>
       </c>
       <c r="R170" t="n">
-        <v>7013259</v>
+        <v>7013219</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -19765,10 +19765,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128494497</v>
+        <v>128494502</v>
       </c>
       <c r="B177" t="n">
-        <v>80226</v>
+        <v>80225</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19776,21 +19776,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>574786</v>
+        <v>574457</v>
       </c>
       <c r="R177" t="n">
-        <v>7013056</v>
+        <v>7013134</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494502</v>
+        <v>128494497</v>
       </c>
       <c r="B179" t="n">
-        <v>80225</v>
+        <v>80226</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19970,21 +19970,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574457</v>
+        <v>574786</v>
       </c>
       <c r="R179" t="n">
-        <v>7013134</v>
+        <v>7013056</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18989,27 +18989,27 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494522</v>
+        <v>128494509</v>
       </c>
       <c r="B169" t="n">
-        <v>79120</v>
+        <v>80264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574726</v>
+        <v>574510</v>
       </c>
       <c r="R169" t="n">
-        <v>7013259</v>
+        <v>7013219</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,32 +19086,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494509</v>
+        <v>128494525</v>
       </c>
       <c r="B170" t="n">
-        <v>80260</v>
+        <v>80229</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574510</v>
+        <v>574821</v>
       </c>
       <c r="R170" t="n">
-        <v>7013219</v>
+        <v>7013166</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,10 +19183,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494525</v>
+        <v>128494522</v>
       </c>
       <c r="B171" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19194,21 +19194,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574821</v>
+        <v>574726</v>
       </c>
       <c r="R171" t="n">
-        <v>7013166</v>
+        <v>7013259</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19283,7 +19283,7 @@
         <v>128494506</v>
       </c>
       <c r="B172" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>128494515</v>
       </c>
       <c r="B173" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>128494528</v>
       </c>
       <c r="B174" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>128494529</v>
       </c>
       <c r="B175" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>128494505</v>
       </c>
       <c r="B176" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19765,10 +19765,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128494502</v>
+        <v>128494497</v>
       </c>
       <c r="B177" t="n">
-        <v>80225</v>
+        <v>80230</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19776,21 +19776,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>574457</v>
+        <v>574786</v>
       </c>
       <c r="R177" t="n">
-        <v>7013134</v>
+        <v>7013056</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19862,10 +19862,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128494516</v>
+        <v>128494502</v>
       </c>
       <c r="B178" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19897,10 +19897,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>574634</v>
+        <v>574457</v>
       </c>
       <c r="R178" t="n">
-        <v>7013287</v>
+        <v>7013134</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494497</v>
+        <v>128494516</v>
       </c>
       <c r="B179" t="n">
-        <v>80226</v>
+        <v>80229</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19970,21 +19970,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574786</v>
+        <v>574634</v>
       </c>
       <c r="R179" t="n">
-        <v>7013056</v>
+        <v>7013287</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20059,7 +20059,7 @@
         <v>128494510</v>
       </c>
       <c r="B180" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>128494498</v>
       </c>
       <c r="B181" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128494526</v>
       </c>
       <c r="B182" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>128494520</v>
       </c>
       <c r="B183" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>128494514</v>
       </c>
       <c r="B184" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91705</v>
+        <v>91709</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>128494513</v>
       </c>
       <c r="B186" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -11771,7 +11771,7 @@
         <v>120477401</v>
       </c>
       <c r="B101" t="n">
-        <v>91716</v>
+        <v>91720</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -18989,27 +18989,27 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494509</v>
+        <v>128494522</v>
       </c>
       <c r="B169" t="n">
-        <v>80264</v>
+        <v>79124</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574510</v>
+        <v>574726</v>
       </c>
       <c r="R169" t="n">
-        <v>7013219</v>
+        <v>7013259</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,32 +19086,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494525</v>
+        <v>128494509</v>
       </c>
       <c r="B170" t="n">
-        <v>80229</v>
+        <v>80264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574821</v>
+        <v>574510</v>
       </c>
       <c r="R170" t="n">
-        <v>7013166</v>
+        <v>7013219</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,10 +19183,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494522</v>
+        <v>128494525</v>
       </c>
       <c r="B171" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19194,21 +19194,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574726</v>
+        <v>574821</v>
       </c>
       <c r="R171" t="n">
-        <v>7013259</v>
+        <v>7013166</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18989,10 +18989,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494522</v>
+        <v>128494525</v>
       </c>
       <c r="B169" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19000,21 +19000,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574726</v>
+        <v>574821</v>
       </c>
       <c r="R169" t="n">
-        <v>7013259</v>
+        <v>7013166</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,27 +19086,27 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494509</v>
+        <v>128494522</v>
       </c>
       <c r="B170" t="n">
-        <v>80264</v>
+        <v>79124</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574510</v>
+        <v>574726</v>
       </c>
       <c r="R170" t="n">
-        <v>7013219</v>
+        <v>7013259</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,32 +19183,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494525</v>
+        <v>128494509</v>
       </c>
       <c r="B171" t="n">
-        <v>80229</v>
+        <v>80264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574821</v>
+        <v>574510</v>
       </c>
       <c r="R171" t="n">
-        <v>7013166</v>
+        <v>7013219</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19765,10 +19765,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128494497</v>
+        <v>128494502</v>
       </c>
       <c r="B177" t="n">
-        <v>80230</v>
+        <v>80229</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19776,21 +19776,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>574786</v>
+        <v>574457</v>
       </c>
       <c r="R177" t="n">
-        <v>7013056</v>
+        <v>7013134</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19862,7 +19862,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128494502</v>
+        <v>128494516</v>
       </c>
       <c r="B178" t="n">
         <v>80229</v>
@@ -19897,10 +19897,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>574457</v>
+        <v>574634</v>
       </c>
       <c r="R178" t="n">
-        <v>7013134</v>
+        <v>7013287</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128494516</v>
+        <v>128494497</v>
       </c>
       <c r="B179" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19970,21 +19970,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574634</v>
+        <v>574786</v>
       </c>
       <c r="R179" t="n">
-        <v>7013287</v>
+        <v>7013056</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -18895,7 +18895,7 @@
         <v>128494524</v>
       </c>
       <c r="B168" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18989,32 +18989,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128494525</v>
+        <v>128494509</v>
       </c>
       <c r="B169" t="n">
-        <v>80229</v>
+        <v>80169</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19024,10 +19024,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574821</v>
+        <v>574510</v>
       </c>
       <c r="R169" t="n">
-        <v>7013166</v>
+        <v>7013219</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19086,10 +19086,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128494522</v>
+        <v>128494525</v>
       </c>
       <c r="B170" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19097,21 +19097,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19121,10 +19121,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574726</v>
+        <v>574821</v>
       </c>
       <c r="R170" t="n">
-        <v>7013259</v>
+        <v>7013166</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19183,27 +19183,27 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128494509</v>
+        <v>128494522</v>
       </c>
       <c r="B171" t="n">
-        <v>80264</v>
+        <v>79029</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574510</v>
+        <v>574726</v>
       </c>
       <c r="R171" t="n">
-        <v>7013219</v>
+        <v>7013259</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19283,7 +19283,7 @@
         <v>128494506</v>
       </c>
       <c r="B172" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>128494515</v>
       </c>
       <c r="B173" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>128494528</v>
       </c>
       <c r="B174" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>128494529</v>
       </c>
       <c r="B175" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>128494505</v>
       </c>
       <c r="B176" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>128494502</v>
       </c>
       <c r="B177" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>128494516</v>
       </c>
       <c r="B178" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>128494497</v>
       </c>
       <c r="B179" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>128494510</v>
       </c>
       <c r="B180" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>128494498</v>
       </c>
       <c r="B181" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128494526</v>
       </c>
       <c r="B182" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>128494520</v>
       </c>
       <c r="B183" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>128494514</v>
       </c>
       <c r="B184" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>128494521</v>
       </c>
       <c r="B185" t="n">
-        <v>91709</v>
+        <v>91714</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>128494513</v>
       </c>
       <c r="B186" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2024 artfynd.xlsx
+++ b/artfynd/A 42099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY201"/>
+  <dimension ref="A1:AZ201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494521</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475751</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482863</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476454</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478002</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478878</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482523</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482660</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195559</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1676,6 +1726,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477401</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1800,6 +1855,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55773992</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,6 +1967,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478069</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2004,6 +2069,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478431</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478767</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478974</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2295,6 +2375,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120479509</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2392,6 +2477,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120479582</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2489,6 +2579,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482434</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2586,6 +2681,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482599</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2693,6 +2793,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482763</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2790,6 +2895,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121217723</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2887,6 +2997,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121217724</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2984,6 +3099,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478169</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3081,6 +3201,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195547</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3178,6 +3303,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195548</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3275,6 +3405,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195550</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3372,6 +3507,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195551</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3469,6 +3609,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195552</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3566,6 +3711,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195553</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3673,6 +3823,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478036</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3770,6 +3925,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478407</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3877,6 +4037,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483094</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3984,6 +4149,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478253</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4081,6 +4251,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120481907</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4188,6 +4363,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482642</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4285,6 +4465,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483538</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4392,6 +4577,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475397</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4499,6 +4689,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476199</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4606,6 +4801,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482920</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4703,6 +4903,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483116</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4800,6 +5005,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483166</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4897,6 +5107,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121217729</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4994,6 +5209,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494497</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5091,6 +5311,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494505</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5188,6 +5413,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494514</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5285,6 +5515,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494524</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5392,6 +5627,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475714</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5499,6 +5739,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478128</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5596,6 +5841,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478200</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5703,6 +5953,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478232</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5810,6 +6065,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478274</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5917,6 +6177,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120479650</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6024,6 +6289,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475677</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6131,6 +6401,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475802</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6238,6 +6513,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477619</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6345,6 +6625,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477715</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6452,6 +6737,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477828</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6559,6 +6849,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478239</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6666,6 +6961,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478428</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6773,6 +7073,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120479001</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6880,6 +7185,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120479575</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6987,6 +7297,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482540</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7094,6 +7409,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483118</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7191,6 +7511,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483505</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7288,6 +7613,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483518</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7385,6 +7715,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494522</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7492,6 +7827,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478804</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7589,6 +7929,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477989</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7686,6 +8031,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195558</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7793,6 +8143,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1994501</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7900,6 +8255,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1994502</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8007,6 +8367,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1994503</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8114,6 +8479,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1994504</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8221,6 +8591,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1994505</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8328,6 +8703,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1994506</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8435,6 +8815,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1994507</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8559,6 +8944,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55773991</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8666,6 +9056,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475469</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8773,6 +9168,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475740</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8880,6 +9280,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475948</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8977,6 +9382,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476091</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9084,6 +9494,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476675</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9191,6 +9606,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476784</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9298,6 +9718,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476831</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9405,6 +9830,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476914</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9512,6 +9942,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477524</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9609,6 +10044,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477985</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9716,6 +10156,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478206</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9823,6 +10268,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478210</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9930,6 +10380,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478226</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10027,6 +10482,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478245</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10134,6 +10594,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478900</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10241,6 +10706,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120480588</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10353,6 +10823,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120480946</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10460,6 +10935,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482873</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10557,6 +11037,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483096</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10654,6 +11139,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483114</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10761,6 +11251,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483136</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10858,6 +11353,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483155</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10955,6 +11455,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758590</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11052,6 +11557,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758591</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11149,6 +11659,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758592</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11246,6 +11761,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758593</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11343,6 +11863,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758596</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11440,6 +11965,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758597</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11537,6 +12067,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758608</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11634,6 +12169,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758610</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11731,6 +12271,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758611</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11828,6 +12373,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758612</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11925,6 +12475,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120758613</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12022,6 +12577,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478171</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12119,6 +12679,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195562</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12216,6 +12781,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195563</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12313,6 +12883,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195564</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12410,6 +12985,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195565</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12507,6 +13087,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195566</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12604,6 +13189,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195567</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12701,6 +13291,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195568</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12798,6 +13393,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195569</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12895,6 +13495,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494498</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12992,6 +13597,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494502</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13089,6 +13699,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494506</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13186,6 +13801,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494510</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13283,6 +13903,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494513</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13380,6 +14005,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494516</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13477,6 +14107,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494520</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13574,6 +14209,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494525</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13671,6 +14311,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494529</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13768,6 +14413,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712555</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13865,6 +14515,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712556</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13962,6 +14617,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475679</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14059,6 +14719,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475673</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14156,6 +14821,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494509</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14253,6 +14923,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494515</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14350,6 +15025,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494528</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14462,6 +15142,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475719</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14564,6 +15249,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476175</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14676,6 +15366,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476839</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14788,6 +15483,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477787</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14900,6 +15600,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120479013</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15002,6 +15707,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120481387</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15114,6 +15824,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483427</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15216,6 +15931,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195556</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15318,6 +16038,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195557</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15415,6 +16140,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494526</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15527,6 +16257,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475858</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15639,6 +16374,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475921</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15756,6 +16496,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476541</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15868,6 +16613,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476542</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15980,6 +16730,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476584</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16092,6 +16847,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476601</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16204,6 +16964,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476791</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16316,6 +17081,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477573</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16428,6 +17198,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477678</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16540,6 +17315,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477743</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16657,6 +17437,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477886</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16769,6 +17554,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477919</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16881,6 +17671,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477938</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16993,6 +17788,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477974</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17105,6 +17905,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477975</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17212,6 +18017,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478039</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17324,6 +18134,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478091</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17431,6 +18246,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478207</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17543,6 +18363,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478597</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17655,6 +18480,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120479683</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17767,6 +18597,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482411</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17879,6 +18714,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482757</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17991,6 +18831,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482861</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18088,6 +18933,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482864</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18200,6 +19050,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483075</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18312,6 +19167,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483092</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18424,6 +19284,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483119</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18521,6 +19386,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121217742</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18628,6 +19498,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478170</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18735,6 +19610,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478173</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18842,6 +19722,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478174</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18949,6 +19834,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478175</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19056,6 +19946,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478176</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19163,6 +20058,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478177</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19270,6 +20170,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478178</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19377,6 +20282,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478179</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19484,6 +20394,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478180</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19591,6 +20506,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478181</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19693,6 +20613,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195554</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19800,6 +20725,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195555</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19910,6 +20840,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195561</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20012,6 +20947,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195571</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20122,6 +21062,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126054152</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20224,6 +21169,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678437</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20326,6 +21276,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712549</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20432,6 +21387,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126053988</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20544,6 +21504,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120475741</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20656,6 +21621,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476955</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20761,6 +21731,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195570</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20873,6 +21848,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478086</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20994,6 +21974,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477951</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21105,6 +22090,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477400</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21221,6 +22211,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478035</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21318,6 +22313,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482317</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21415,8 +22415,215 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483141</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>